--- a/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
+++ b/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
@@ -7513,10 +7513,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G79" s="22" t="n"/>
-      <c r="H79" s="23" t="n"/>
-      <c r="I79" s="22" t="n"/>
-      <c r="J79" s="23" t="n"/>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0</t>
+        </is>
+      </c>
+      <c r="H79" s="23">
+        <f>IF(LEN(G79)=0,"",IF(ISNUMBER(SEARCH(",",G79)),LEN(SUBSTITUTE(G79,",","xx"))-LEN(G79)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>83,83</t>
+        </is>
+      </c>
+      <c r="J79" s="23">
+        <f>IF(LEN(I79)=0,"",IF(ISNUMBER(SEARCH(",",I79)),LEN(SUBSTITUTE(I79,",","xx"))-LEN(I79)+1,1))</f>
+        <v/>
+      </c>
       <c r="K79" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -7527,9 +7541,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M79" s="39" t="n"/>
-      <c r="N79" s="39" t="n"/>
-      <c r="O79" s="21" t="n"/>
+      <c r="M79" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="21">
+        <f>IF(AND(N79&lt;0.05,OR(AND(L79="升高改善",M79&gt;0),AND(L79="降低改善",M79&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P79" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第8页，印刷页8；上方面板 Amber/Regina；实心方形（Child w/ ASD，独立接受游戏邀请的步骤）；实心三角形为 Typical Peer。</t>
@@ -7537,17 +7558,17 @@
       </c>
       <c r="Q79" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R79" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S79" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段两个图示点与正文报告不一致，尚不能判定图或文字何者有误，需核实维持期数据。</t>
+          <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。图文不一致：维持期图上2个方块均为83%（第18、19次；与三角形部分重叠，按方块上缘推算），正文报告Regina维持75%。按图取值。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -7756,10 +7777,24 @@
           <t>Baseline（基线期） vs VM（视频示范）</t>
         </is>
       </c>
-      <c r="G82" s="22" t="n"/>
-      <c r="H82" s="23" t="n"/>
-      <c r="I82" s="22" t="n"/>
-      <c r="J82" s="23" t="n"/>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H82" s="23">
+        <f>IF(LEN(G82)=0,"",IF(ISNUMBER(SEARCH(",",G82)),LEN(SUBSTITUTE(G82,",","xx"))-LEN(G82)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>58,100,100,83</t>
+        </is>
+      </c>
+      <c r="J82" s="23">
+        <f>IF(LEN(I82)=0,"",IF(ISNUMBER(SEARCH(",",I82)),LEN(SUBSTITUTE(I82,",","xx"))-LEN(I82)+1,1))</f>
+        <v/>
+      </c>
       <c r="K82" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -7770,9 +7805,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M82" s="39" t="n"/>
-      <c r="N82" s="39" t="n"/>
-      <c r="O82" s="21" t="n"/>
+      <c r="M82" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="21">
+        <f>IF(AND(N82&lt;0.05,OR(AND(L82="升高改善",M82&gt;0),AND(L82="降低改善",M82&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P82" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第8页，印刷页8；下方面板 Milo/Xane；实心方形（Child w/ ASD，独立接受游戏邀请的步骤）；实心三角形为 Typical Peer。</t>
@@ -7780,17 +7822,17 @@
       </c>
       <c r="Q82" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R82" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S82" s="18" t="inlineStr">
         <is>
-          <t>待审核：首个干预观察点的图示读值与正文描述不一致，需核实该点后确认完整干预序列。</t>
+          <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。基线5次探测（第1、2、3、7、11次）均为0。干预期按矢量阶段线为第12–15次4点：58,100,100,83。图文不一致：第1个干预点图上为58%（约为7/12步），正文写60%；第15次的83%按阶段线属于干预期，而正文说“维持83%”。按图取值。</t>
         </is>
       </c>
     </row>
@@ -7825,10 +7867,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G83" s="22" t="n"/>
-      <c r="H83" s="23" t="n"/>
-      <c r="I83" s="22" t="n"/>
-      <c r="J83" s="23" t="n"/>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H83" s="23">
+        <f>IF(LEN(G83)=0,"",IF(ISNUMBER(SEARCH(",",G83)),LEN(SUBSTITUTE(G83,",","xx"))-LEN(G83)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>92,100</t>
+        </is>
+      </c>
+      <c r="J83" s="23">
+        <f>IF(LEN(I83)=0,"",IF(ISNUMBER(SEARCH(",",I83)),LEN(SUBSTITUTE(I83,",","xx"))-LEN(I83)+1,1))</f>
+        <v/>
+      </c>
       <c r="K83" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -7839,9 +7895,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M83" s="39" t="n"/>
-      <c r="N83" s="39" t="n"/>
-      <c r="O83" s="21" t="n"/>
+      <c r="M83" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="21">
+        <f>IF(AND(N83&lt;0.05,OR(AND(L83="升高改善",M83&gt;0),AND(L83="降低改善",M83&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P83" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第8页，印刷页8；下方面板 Milo/Xane；实心方形（Child w/ ASD，独立接受游戏邀请的步骤）；实心三角形为 Typical Peer。</t>
@@ -7849,17 +7912,17 @@
       </c>
       <c r="Q83" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R83" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S83" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段两个图示点与正文报告的水平不一致，需核实原始观察记录和维持期数值。</t>
+          <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。维持期按矢量阶段线为第18、19次：92,100（第18次方块与三角形重叠，按方块上缘推算）。图文不一致：正文报告Xane维持83%，图上维持期为92、100。按图取值。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -14108,10 +14171,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G156" s="33" t="n"/>
-      <c r="H156" s="34" t="n"/>
-      <c r="I156" s="33" t="n"/>
-      <c r="J156" s="34" t="n"/>
+      <c r="G156" s="33" t="inlineStr">
+        <is>
+          <t>8.0,5.0,36.2,6.6,52.4,10.5</t>
+        </is>
+      </c>
+      <c r="H156" s="34">
+        <f>IF(LEN(G156)=0,"",IF(ISNUMBER(SEARCH(",",G156)),LEN(SUBSTITUTE(G156,",","xx"))-LEN(G156)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I156" s="33" t="inlineStr">
+        <is>
+          <t>47.4,29.2,60.0,50.0,52.8,31.6,70.0,79.2</t>
+        </is>
+      </c>
+      <c r="J156" s="34">
+        <f>IF(LEN(I156)=0,"",IF(ISNUMBER(SEARCH(",",I156)),LEN(SUBSTITUTE(I156,",","xx"))-LEN(I156)+1,1))</f>
+        <v/>
+      </c>
       <c r="K156" s="13" t="inlineStr">
         <is>
           <t>%</t>
@@ -14122,9 +14199,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M156" s="38" t="n"/>
-      <c r="N156" s="38" t="n"/>
-      <c r="O156" s="16" t="n"/>
+      <c r="M156" s="38" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N156" s="38" t="n">
+        <v>0.347558036741169</v>
+      </c>
+      <c r="O156" s="16">
+        <f>IF(AND(N156&lt;0.05,OR(AND(L156="升高改善",M156&gt;0),AND(L156="降低改善",M156&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P156" s="13" t="inlineStr">
         <is>
           <t>Figure 1；PDF第7页／印刷第7页；第1（上）面板（James）；黑色实心圆、实线连接；灰三角为Intervention fidelity，排除。</t>
@@ -14132,17 +14216,17 @@
       </c>
       <c r="Q156" s="13" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R156" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S156" s="13" t="inlineStr">
         <is>
-          <t>待审核：基线第11次观察的图示读值超出正文报告范围，图文最大值冲突，需核实该点。</t>
+          <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。图文不一致：基线第5点（约第11次）图上为52.4%，超出正文范围5–36%；但含此点的基线均值19.8%与正文均值20%一致，说明正文范围有误。干预8点均值52.5%、范围29.2–79.2%，与正文53%（29–79%）一致。按图取值。</t>
         </is>
       </c>
     </row>
@@ -14177,10 +14261,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G157" s="22" t="n"/>
-      <c r="H157" s="23" t="n"/>
-      <c r="I157" s="22" t="n"/>
-      <c r="J157" s="23" t="n"/>
+      <c r="G157" s="22" t="inlineStr">
+        <is>
+          <t>8.0,5.0,36.2,6.6,52.4,10.5</t>
+        </is>
+      </c>
+      <c r="H157" s="23">
+        <f>IF(LEN(G157)=0,"",IF(ISNUMBER(SEARCH(",",G157)),LEN(SUBSTITUTE(G157,",","xx"))-LEN(G157)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I157" s="22" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="J157" s="23">
+        <f>IF(LEN(I157)=0,"",IF(ISNUMBER(SEARCH(",",I157)),LEN(SUBSTITUTE(I157,",","xx"))-LEN(I157)+1,1))</f>
+        <v/>
+      </c>
       <c r="K157" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -14191,9 +14289,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M157" s="39" t="n"/>
-      <c r="N157" s="39" t="n"/>
-      <c r="O157" s="21" t="n"/>
+      <c r="M157" s="39" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N157" s="39" t="n">
+        <v>0.347558036741169</v>
+      </c>
+      <c r="O157" s="21">
+        <f>IF(AND(N157&lt;0.05,OR(AND(L157="升高改善",M157&gt;0),AND(L157="降低改善",M157&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P157" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第7页／印刷第7页；第1（上）面板（James）；黑色实心圆、实线连接；维持为最右单点；灰三角为Intervention fidelity，排除。</t>
@@ -14201,17 +14306,17 @@
       </c>
       <c r="Q157" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R157" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S157" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线第11次观察的图示读值超出正文报告范围，图文最大值冲突，需核实该点。</t>
+          <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。基线同D0155（基线第5点52.4%超出正文范围，见D0155）。维持探测1次8.4%，与正文8%一致。维持期只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -14418,10 +14523,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G160" s="22" t="n"/>
-      <c r="H160" s="23" t="n"/>
-      <c r="I160" s="22" t="n"/>
-      <c r="J160" s="23" t="n"/>
+      <c r="G160" s="22" t="inlineStr">
+        <is>
+          <t>53.5,36.6,55.9,89.9,68.3</t>
+        </is>
+      </c>
+      <c r="H160" s="23">
+        <f>IF(LEN(G160)=0,"",IF(ISNUMBER(SEARCH(",",G160)),LEN(SUBSTITUTE(G160,",","xx"))-LEN(G160)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I160" s="22" t="inlineStr">
+        <is>
+          <t>81.8,84.9,89.9,89.2</t>
+        </is>
+      </c>
+      <c r="J160" s="23">
+        <f>IF(LEN(I160)=0,"",IF(ISNUMBER(SEARCH(",",I160)),LEN(SUBSTITUTE(I160,",","xx"))-LEN(I160)+1,1))</f>
+        <v/>
+      </c>
       <c r="K160" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -14432,9 +14551,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M160" s="39" t="n"/>
-      <c r="N160" s="39" t="n"/>
-      <c r="O160" s="21" t="n"/>
+      <c r="M160" s="39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N160" s="39" t="n">
+        <v>0.1416446902951368</v>
+      </c>
+      <c r="O160" s="21">
+        <f>IF(AND(N160&lt;0.05,OR(AND(L160="升高改善",M160&gt;0),AND(L160="降低改善",M160&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P160" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第7页／印刷第7页；第4（下）面板（Sam）；黑色实心圆、实线连接；灰三角为Intervention fidelity，排除。</t>
@@ -14442,17 +14568,17 @@
       </c>
       <c r="Q160" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R160" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S160" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预第39次观察的图示读值低于正文报告范围，图文最小值冲突，需核实该点。</t>
+          <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。基线5点均值60.8%、范围36.6–89.9%，与正文61%（37–90%）一致。图文不一致：干预第1点（第39次）图上为81.8%，低于正文范围85–90%；干预均值86.5%与正文86%一致。按图取值。</t>
         </is>
       </c>
     </row>
@@ -14745,10 +14871,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G164" s="22" t="n"/>
-      <c r="H164" s="23" t="n"/>
-      <c r="I164" s="22" t="n"/>
-      <c r="J164" s="23" t="n"/>
+      <c r="G164" s="22" t="inlineStr">
+        <is>
+          <t>0.0,81.0,43.5,70.0,80.0,91.3</t>
+        </is>
+      </c>
+      <c r="H164" s="23">
+        <f>IF(LEN(G164)=0,"",IF(ISNUMBER(SEARCH(",",G164)),LEN(SUBSTITUTE(G164,",","xx"))-LEN(G164)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I164" s="22" t="inlineStr">
+        <is>
+          <t>43.6,65.2,60.0,40.6</t>
+        </is>
+      </c>
+      <c r="J164" s="23">
+        <f>IF(LEN(I164)=0,"",IF(ISNUMBER(SEARCH(",",I164)),LEN(SUBSTITUTE(I164,",","xx"))-LEN(I164)+1,1))</f>
+        <v/>
+      </c>
       <c r="K164" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -14759,9 +14899,16 @@
           <t>降低改善</t>
         </is>
       </c>
-      <c r="M164" s="39" t="n"/>
-      <c r="N164" s="39" t="n"/>
-      <c r="O164" s="21" t="n"/>
+      <c r="M164" s="39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N164" s="39" t="n">
+        <v>0.09087393998624903</v>
+      </c>
+      <c r="O164" s="21">
+        <f>IF(AND(N164&lt;0.05,OR(AND(L164="升高改善",M164&gt;0),AND(L164="降低改善",M164&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P164" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第8页／印刷第8页；第3面板（Edward）；黑色实心圆、实线连接。</t>
@@ -14769,17 +14916,17 @@
       </c>
       <c r="Q164" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R164" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S164" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线及干预图示均值与正文不符，且正文干预均值不在其所报范围内，尚无法定位具体错误。</t>
+          <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。读Figure 2（PDF第8页）。图文不一致：基线均值图上61.0%、正文65%（范围0–92%与图一致）；干预均值图上52.4%，正文写22%，但正文给的范围41–65%与图一致，正文均值22%本身不在其范围内，应为正文笔误。按图取值。</t>
         </is>
       </c>
     </row>
@@ -14814,10 +14961,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G165" s="22" t="n"/>
-      <c r="H165" s="23" t="n"/>
-      <c r="I165" s="22" t="n"/>
-      <c r="J165" s="23" t="n"/>
+      <c r="G165" s="22" t="inlineStr">
+        <is>
+          <t>16.0,51.6,31.9,6.6,24.9</t>
+        </is>
+      </c>
+      <c r="H165" s="23">
+        <f>IF(LEN(G165)=0,"",IF(ISNUMBER(SEARCH(",",G165)),LEN(SUBSTITUTE(G165,",","xx"))-LEN(G165)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I165" s="22" t="inlineStr">
+        <is>
+          <t>38.9,22.5,7.4,29.7</t>
+        </is>
+      </c>
+      <c r="J165" s="23">
+        <f>IF(LEN(I165)=0,"",IF(ISNUMBER(SEARCH(",",I165)),LEN(SUBSTITUTE(I165,",","xx"))-LEN(I165)+1,1))</f>
+        <v/>
+      </c>
       <c r="K165" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -14828,9 +14989,16 @@
           <t>降低改善</t>
         </is>
       </c>
-      <c r="M165" s="39" t="n"/>
-      <c r="N165" s="39" t="n"/>
-      <c r="O165" s="21" t="n"/>
+      <c r="M165" s="39" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N165" s="39" t="n">
+        <v>0.624206114766406</v>
+      </c>
+      <c r="O165" s="21">
+        <f>IF(AND(N165&lt;0.05,OR(AND(L165="升高改善",M165&gt;0),AND(L165="降低改善",M165&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P165" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第8页／印刷第8页；第4（下）面板（Sam）；黑色实心圆、实线连接。</t>
@@ -14838,17 +15006,17 @@
       </c>
       <c r="Q165" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R165" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S165" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线第22次观察的图示读值超出正文报告范围，图文最大值冲突，需核实该点。</t>
+          <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。读Figure 2（PDF第8页）。图文不一致：基线第2点（第22次）图上为51.6%，超出正文范围7–32%；但含此点的基线均值26.2%与正文26%一致。干预4点均值24.6%、范围7.4–38.9%，与正文25%（7.5–39%）一致。按图取值。</t>
         </is>
       </c>
     </row>
@@ -15227,10 +15395,24 @@
           <t>Baseline（基线期） vs Intervention- PMI（同伴介入干预期）</t>
         </is>
       </c>
-      <c r="G170" s="33" t="n"/>
-      <c r="H170" s="34" t="n"/>
-      <c r="I170" s="33" t="n"/>
-      <c r="J170" s="34" t="n"/>
+      <c r="G170" s="33" t="inlineStr">
+        <is>
+          <t>6,7,7,8</t>
+        </is>
+      </c>
+      <c r="H170" s="34">
+        <f>IF(LEN(G170)=0,"",IF(ISNUMBER(SEARCH(",",G170)),LEN(SUBSTITUTE(G170,",","xx"))-LEN(G170)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I170" s="33" t="inlineStr">
+        <is>
+          <t>4,5,3,2,2,3,2,2</t>
+        </is>
+      </c>
+      <c r="J170" s="34">
+        <f>IF(LEN(I170)=0,"",IF(ISNUMBER(SEARCH(",",I170)),LEN(SUBSTITUTE(I170,",","xx"))-LEN(I170)+1,1))</f>
+        <v/>
+      </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
           <t>错误次数</t>
@@ -15241,9 +15423,16 @@
           <t>降低改善</t>
         </is>
       </c>
-      <c r="M170" s="38" t="n"/>
-      <c r="N170" s="38" t="n"/>
-      <c r="O170" s="16" t="n"/>
+      <c r="M170" s="38" t="n">
+        <v>0.9128709291752769</v>
+      </c>
+      <c r="N170" s="38" t="n">
+        <v>0.07095149242730563</v>
+      </c>
+      <c r="O170" s="16">
+        <f>IF(AND(N170&lt;0.05,OR(AND(L170="升高改善",M170&gt;0),AND(L170="降低改善",M170&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P170" s="3" t="inlineStr">
         <is>
           <t>Figure 1；PDF第7页，印刷页7；上方面板 Subject-Verb Agreement；实心圆形；纵轴 Number of errors。</t>
@@ -15251,17 +15440,17 @@
       </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R170" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S170" s="3" t="inlineStr">
         <is>
-          <t>待审核：干预图有8个观察点，正文同时写8天和5次，观测点数及各次记录的对应关系需核实。</t>
+          <t>Claude补提取（以图为准）：读PDF第7页Figure 1（300 dpi渲染），逐像素检测实心圆，按纵轴刻度标签换算，读数均为整数。图上干预期8点，均值2.875，与正文/表3均值2.9、范围2–5一致；正文“8天（5次40分钟课）”的次数说法与点数不符，按图取8点。基线与D0170相同。</t>
         </is>
       </c>
     </row>
@@ -15562,10 +15751,24 @@
           <t>Baseline（基线期） vs Intervention- PMI（同伴介入干预期）</t>
         </is>
       </c>
-      <c r="G174" s="22" t="n"/>
-      <c r="H174" s="23" t="n"/>
-      <c r="I174" s="22" t="n"/>
-      <c r="J174" s="23" t="n"/>
+      <c r="G174" s="22" t="inlineStr">
+        <is>
+          <t>5,4,6,6,5,6,8,7,6,7,7,6,6,8,7,5,6</t>
+        </is>
+      </c>
+      <c r="H174" s="23">
+        <f>IF(LEN(G174)=0,"",IF(ISNUMBER(SEARCH(",",G174)),LEN(SUBSTITUTE(G174,",","xx"))-LEN(G174)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I174" s="22" t="inlineStr">
+        <is>
+          <t>6,4,3,3,2,3,2</t>
+        </is>
+      </c>
+      <c r="J174" s="23">
+        <f>IF(LEN(I174)=0,"",IF(ISNUMBER(SEARCH(",",I174)),LEN(SUBSTITUTE(I174,",","xx"))-LEN(I174)+1,1))</f>
+        <v/>
+      </c>
       <c r="K174" s="8" t="inlineStr">
         <is>
           <t>错误次数</t>
@@ -15576,9 +15779,16 @@
           <t>降低改善</t>
         </is>
       </c>
-      <c r="M174" s="39" t="n"/>
-      <c r="N174" s="39" t="n"/>
-      <c r="O174" s="21" t="n"/>
+      <c r="M174" s="39" t="n">
+        <v>0.2761530448893886</v>
+      </c>
+      <c r="N174" s="39" t="n">
+        <v>0.1523786670550124</v>
+      </c>
+      <c r="O174" s="21">
+        <f>IF(AND(N174&lt;0.05,OR(AND(L174="升高改善",M174&gt;0),AND(L174="降低改善",M174&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P174" s="8" t="inlineStr">
         <is>
           <t>Figure 1；PDF第7页，印刷页7；下方面板 Punctuation；实心圆形；纵轴 Number of errors。</t>
@@ -15586,17 +15796,17 @@
       </c>
       <c r="Q174" s="8" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R174" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S174" s="8" t="inlineStr">
         <is>
-          <t>待审核：干预图有7个观察点，正文同时写7天和8次，观测点数及各次记录的对应关系需核实。</t>
+          <t>Claude补提取（以图为准）：读PDF第7页Figure 1（300 dpi渲染），逐像素检测实心圆，按纵轴刻度标签换算，读数均为整数。图上干预期7点，均值3.29，范围2–6；正文/表3报告均值3.2、范围2–6，正文写“7天8次”。点数与均值和正文略有出入，无法定位，按图取7点。基线与D0174相同。</t>
         </is>
       </c>
     </row>
@@ -17805,10 +18015,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G200" s="22" t="n"/>
-      <c r="H200" s="23" t="n"/>
-      <c r="I200" s="22" t="n"/>
-      <c r="J200" s="23" t="n"/>
+      <c r="G200" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H200" s="23">
+        <f>IF(LEN(G200)=0,"",IF(ISNUMBER(SEARCH(",",G200)),LEN(SUBSTITUTE(G200,",","xx"))-LEN(G200)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I200" s="22" t="inlineStr">
+        <is>
+          <t>100,26.1,38.1,100</t>
+        </is>
+      </c>
+      <c r="J200" s="23">
+        <f>IF(LEN(I200)=0,"",IF(ISNUMBER(SEARCH(",",I200)),LEN(SUBSTITUTE(I200,",","xx"))-LEN(I200)+1,1))</f>
+        <v/>
+      </c>
       <c r="K200" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -17819,9 +18043,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M200" s="39" t="n"/>
-      <c r="N200" s="39" t="n"/>
-      <c r="O200" s="21" t="n"/>
+      <c r="M200" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" s="21">
+        <f>IF(AND(N200&lt;0.05,OR(AND(L200="升高改善",M200&gt;0),AND(L200="降低改善",M200&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P200" s="18" t="inlineStr">
         <is>
           <t>Figure 1；PDF第6页，印刷页76；下方面板 Dyad 3（Robert）；实心黑色菱形、左纵轴（Target child responses）；空心圆形及右纵轴为同伴发起。</t>
@@ -17829,17 +18060,17 @@
       </c>
       <c r="Q200" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R200" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S200" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预第14、15次观察的图示读值与正文报告的范围及均值不一致，需核实这两个观察点。</t>
+          <t>Claude补提取（以图为准）：从PDF第6页内嵌原图（1900×2053像素）检测实心菱形（左纵轴，目标儿童回应百分比），按Dyad 3面板刻度（5.395像素/单位）换算。基线9次探测（第1、2、4–9、12次）均为0。图文不一致：干预第14、15次图上为26.1%、38.1%；正文报告均值70.75%、范围33.3–100%，与同伴邀请次数（3次、4次）推算的33.3%、50%相符，图上两点可能绘制有误。按图取值；两种读法下干预期均全部高于基线，Tau-U不受影响。</t>
         </is>
       </c>
     </row>
@@ -20551,10 +20782,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G233" s="33" t="n"/>
-      <c r="H233" s="34" t="n"/>
-      <c r="I233" s="33" t="n"/>
-      <c r="J233" s="34" t="n"/>
+      <c r="G233" s="33" t="inlineStr">
+        <is>
+          <t>0,6,6</t>
+        </is>
+      </c>
+      <c r="H233" s="34">
+        <f>IF(LEN(G233)=0,"",IF(ISNUMBER(SEARCH(",",G233)),LEN(SUBSTITUTE(G233,",","xx"))-LEN(G233)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I233" s="33" t="inlineStr">
+        <is>
+          <t>33,40,66,86,93,100,100,100</t>
+        </is>
+      </c>
+      <c r="J233" s="34">
+        <f>IF(LEN(I233)=0,"",IF(ISNUMBER(SEARCH(",",I233)),LEN(SUBSTITUTE(I233,",","xx"))-LEN(I233)+1,1))</f>
+        <v/>
+      </c>
       <c r="K233" s="13" t="inlineStr">
         <is>
           <t>%</t>
@@ -20565,9 +20810,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M233" s="38" t="n"/>
-      <c r="N233" s="38" t="n"/>
-      <c r="O233" s="16" t="n"/>
+      <c r="M233" s="38" t="n">
+        <v>0.816496580927726</v>
+      </c>
+      <c r="N233" s="38" t="n">
+        <v>0.2206713619198469</v>
+      </c>
+      <c r="O233" s="16">
+        <f>IF(AND(N233&lt;0.05,OR(AND(L233="升高改善",M233&gt;0),AND(L233="降低改善",M233&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P233" s="13" t="inlineStr">
         <is>
           <t>Figure 1，PDF第27页／印刷页645；Murat 上方面板；纵轴“Correct response percentage”，实心菱形；Baseline与Intervention使用连线，Maintenance为右侧未连接的3个菱形（正文说明干预后1、2、4周，PDF第28页／646）。</t>
@@ -20575,17 +20827,17 @@
       </c>
       <c r="Q233" s="13" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R233" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S233" s="13" t="inlineStr">
         <is>
-          <t>待审核：基线三个图示点的均值与正文报告不一致，尚不能确定哪个点或文字记录有误，需核实整个基线。</t>
+          <t>Claude补提取（以图为准）：Figure 1为PDF矢量图，直接读取Murat面板数据折线顶点的PDF坐标。注意纵轴从−10开始（刻度−10,0,10,…,100），按0与100刻度线换算。基线0,6,6与土耳其文正文（第1次0%，第2、3次6%）一致；英文摘要段写基线均值2%（范围0–6%），按图均值为4%，属图文不一致，按图取值。干预8点均值77.25%，与正文77%（33–100%）一致。原先的“均值不一致”可能是把−10刻度当作0读数所致。</t>
         </is>
       </c>
     </row>
@@ -20620,10 +20872,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G234" s="22" t="n"/>
-      <c r="H234" s="23" t="n"/>
-      <c r="I234" s="22" t="n"/>
-      <c r="J234" s="23" t="n"/>
+      <c r="G234" s="22" t="inlineStr">
+        <is>
+          <t>0,6,6</t>
+        </is>
+      </c>
+      <c r="H234" s="23">
+        <f>IF(LEN(G234)=0,"",IF(ISNUMBER(SEARCH(",",G234)),LEN(SUBSTITUTE(G234,",","xx"))-LEN(G234)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I234" s="22" t="inlineStr">
+        <is>
+          <t>100,100,100</t>
+        </is>
+      </c>
+      <c r="J234" s="23">
+        <f>IF(LEN(I234)=0,"",IF(ISNUMBER(SEARCH(",",I234)),LEN(SUBSTITUTE(I234,",","xx"))-LEN(I234)+1,1))</f>
+        <v/>
+      </c>
       <c r="K234" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -20634,9 +20900,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M234" s="39" t="n"/>
-      <c r="N234" s="39" t="n"/>
-      <c r="O234" s="21" t="n"/>
+      <c r="M234" s="39" t="n">
+        <v>0.816496580927726</v>
+      </c>
+      <c r="N234" s="39" t="n">
+        <v>0.2206713619198469</v>
+      </c>
+      <c r="O234" s="21">
+        <f>IF(AND(N234&lt;0.05,OR(AND(L234="升高改善",M234&gt;0),AND(L234="降低改善",M234&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P234" s="18" t="inlineStr">
         <is>
           <t>Figure 1，PDF第27页／印刷页645；Murat 上方面板；纵轴“Correct response percentage”，实心菱形；Baseline与Intervention使用连线，Maintenance为右侧未连接的3个菱形（正文说明干预后1、2、4周，PDF第28页／646）。</t>
@@ -20644,17 +20917,17 @@
       </c>
       <c r="Q234" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R234" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S234" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线三个图示点的均值与正文报告不一致，尚不能确定哪个点或文字记录有误，需核实整个基线。</t>
+          <t>Claude补提取（以图为准）：Figure 1为PDF矢量图，直接读取Murat面板数据折线顶点的PDF坐标。注意纵轴从−10开始（刻度−10,0,10,…,100），按0与100刻度线换算。基线同D0232。维持3次均为100%，与正文一致。</t>
         </is>
       </c>
     </row>
@@ -25534,10 +25807,24 @@
           <t>Post-Training（培训后阶段） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G291" s="22" t="n"/>
-      <c r="H291" s="23" t="n"/>
-      <c r="I291" s="22" t="n"/>
-      <c r="J291" s="23" t="n"/>
+      <c r="G291" s="22" t="inlineStr">
+        <is>
+          <t>20,25,20,30,30,30,30,30,50,50,30,50,50,50</t>
+        </is>
+      </c>
+      <c r="H291" s="23">
+        <f>IF(LEN(G291)=0,"",IF(ISNUMBER(SEARCH(",",G291)),LEN(SUBSTITUTE(G291,",","xx"))-LEN(G291)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I291" s="22" t="inlineStr">
+        <is>
+          <t>90,75,80,80,80</t>
+        </is>
+      </c>
+      <c r="J291" s="23">
+        <f>IF(LEN(I291)=0,"",IF(ISNUMBER(SEARCH(",",I291)),LEN(SUBSTITUTE(I291,",","xx"))-LEN(I291)+1,1))</f>
+        <v/>
+      </c>
       <c r="K291" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -25550,7 +25837,10 @@
       </c>
       <c r="M291" s="39" t="n"/>
       <c r="N291" s="39" t="n"/>
-      <c r="O291" s="21" t="n"/>
+      <c r="O291" s="21">
+        <f>IF(AND(N291&lt;0.05,OR(AND(L291="升高改善",M291&gt;0),AND(L291="降低改善",M291&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P291" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第18页，印刷页18 of 28；从上到下第3个Child 3面板；纵轴Percentage of Unprompted Correct Child Responses；目标情境为实心菱形，按Post-Training与Maintenance阶段竖线定位。</t>
@@ -25558,17 +25848,17 @@
       </c>
       <c r="Q291" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R291" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S291" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段五个图示点与正文报告的数值范围冲突，无法定位具体错误点，需核实完整维持序列。</t>
+          <t>Claude补提取（以图为准）：从PDF第18页内嵌原图（1456×2825像素）检测Child 3面板实心菱形，按该面板0与100位置换算。前段与D0289相同（Post-Training阶段，按一览表约定作为对照段）。维持期为第37、40、42、45、48次5点：90,75,80,80,80，均值81%，与正文M=81%一致；正文范围写60–100%，图上为75–90%，属图文不一致，按图取值。第34、39次圆点为泛化探测，未计入。前段为Post-Training，与同组D0285–D0289保持一致，暂不检验基线趋势（τ、p留空）；是否对030-A的前段做趋势检验待作者确定（如做，此行τ=0.767、p=0.001，需校正）。</t>
         </is>
       </c>
     </row>
@@ -28255,7 +28545,11 @@
           <t>已提取</t>
         </is>
       </c>
-      <c r="S322" s="8" t="n"/>
+      <c r="S322" s="8" t="inlineStr">
+        <is>
+          <t>【Claude复核提示】基线第4次实心圆按矢量形状判断应为3（GPT记为2）：该处圆在上、方块在下，方块为回应=2。按3计，两次基线的发起均值为0.82，按2计为0.73，正文报告0.9（0–3）。建议核对，数值未改。</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="60" customHeight="1">
       <c r="A323" s="7" t="inlineStr">
@@ -28427,7 +28721,11 @@
           <t>已提取</t>
         </is>
       </c>
-      <c r="S324" s="8" t="n"/>
+      <c r="S324" s="8" t="inlineStr">
+        <is>
+          <t>【Claude复核提示】基线第4次发起值同D0321，可能应为3而非2，建议核对，数值未改。</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="60" customHeight="1">
       <c r="A325" s="7" t="inlineStr">
@@ -28721,10 +29019,24 @@
           <t>Baseline (first phase)（第一次基线期） vs Intervention (first phase)（第一次干预期）</t>
         </is>
       </c>
-      <c r="G328" s="22" t="n"/>
-      <c r="H328" s="23" t="n"/>
-      <c r="I328" s="22" t="n"/>
-      <c r="J328" s="23" t="n"/>
+      <c r="G328" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,2,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H328" s="23">
+        <f>IF(LEN(G328)=0,"",IF(ISNUMBER(SEARCH(",",G328)),LEN(SUBSTITUTE(G328,",","xx"))-LEN(G328)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I328" s="22" t="inlineStr">
+        <is>
+          <t>44,24,16,5,22,26,15</t>
+        </is>
+      </c>
+      <c r="J328" s="23">
+        <f>IF(LEN(I328)=0,"",IF(ISNUMBER(SEARCH(",",I328)),LEN(SUBSTITUTE(I328,",","xx"))-LEN(I328)+1,1))</f>
+        <v/>
+      </c>
       <c r="K328" s="8" t="inlineStr">
         <is>
           <t>次/10分钟</t>
@@ -28735,9 +29047,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M328" s="39" t="n"/>
-      <c r="N328" s="39" t="n"/>
-      <c r="O328" s="21" t="n"/>
+      <c r="M328" s="39" t="n">
+        <v>-0.07142857142857142</v>
+      </c>
+      <c r="N328" s="39" t="n">
+        <v>0.8272593465627113</v>
+      </c>
+      <c r="O328" s="21">
+        <f>IF(AND(N328&lt;0.05,OR(AND(L328="升高改善",M328&gt;0),AND(L328="降低改善",M328&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P328" s="8" t="inlineStr">
         <is>
           <t>Figure 1；PDF第9页，印刷页9；从上至下第2个Emmett面板；实心方块；图例Responses；空心标记代表与novel peer的泛化观测；按两组Baseline/Intervention竖线区分第一/第二次阶段。</t>
@@ -28745,17 +29064,17 @@
       </c>
       <c r="Q328" s="8" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R328" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S328" s="8" t="inlineStr">
         <is>
-          <t>待审核：基线第4次社交回应的图示读值超出正文报告范围，需核实该点后确认所用基线。</t>
+          <t>Claude补提取（以图为准）：从PDF第9页内嵌原图（1070×1290像素）逐像素检测Emmett面板的实心方块（社交回应），纵轴按PDF中刻度标签位置换算（5.75像素/单位）。第一次基线8点（第1–4、6–9次；第5次为空心泛化探测，未计入）。第4次两个符号重叠：上方为圆（发起=3），下方为方块（回应=2），按形状区分。由此回应基线范围0–2，与正文“0.4次（0–2）”一致，原先所说的“超出正文范围”是把两个符号认反了。第一次干预期7点（第14、17次为泛化探测，未计入），第13次方块与圆重叠，按方块下缘推算为5；与第二次干预期合计14点均值18.0，与正文“18次（5–44）”一致。</t>
         </is>
       </c>
     </row>
@@ -28876,10 +29195,24 @@
           <t>Baseline (first phase)（第一次基线期） vs 6 week follow-up（6周追踪）</t>
         </is>
       </c>
-      <c r="G330" s="22" t="n"/>
-      <c r="H330" s="23" t="n"/>
-      <c r="I330" s="22" t="n"/>
-      <c r="J330" s="23" t="n"/>
+      <c r="G330" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,2,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H330" s="23">
+        <f>IF(LEN(G330)=0,"",IF(ISNUMBER(SEARCH(",",G330)),LEN(SUBSTITUTE(G330,",","xx"))-LEN(G330)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I330" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J330" s="23">
+        <f>IF(LEN(I330)=0,"",IF(ISNUMBER(SEARCH(",",I330)),LEN(SUBSTITUTE(I330,",","xx"))-LEN(I330)+1,1))</f>
+        <v/>
+      </c>
       <c r="K330" s="8" t="inlineStr">
         <is>
           <t>次/10分钟</t>
@@ -28890,9 +29223,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M330" s="39" t="n"/>
-      <c r="N330" s="39" t="n"/>
-      <c r="O330" s="21" t="n"/>
+      <c r="M330" s="39" t="n">
+        <v>-0.07142857142857142</v>
+      </c>
+      <c r="N330" s="39" t="n">
+        <v>0.8272593465627113</v>
+      </c>
+      <c r="O330" s="21">
+        <f>IF(AND(N330&lt;0.05,OR(AND(L330="升高改善",M330&gt;0),AND(L330="降低改善",M330&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P330" s="8" t="inlineStr">
         <is>
           <t>Figure 1；PDF第9页，印刷页9；从上至下第2个Emmett面板；实心方块；图例Responses；空心标记代表与novel peer的泛化观测；右侧6 week follow-up区域。</t>
@@ -28900,17 +29240,17 @@
       </c>
       <c r="Q330" s="8" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R330" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S330" s="8" t="inlineStr">
         <is>
-          <t>待审核：基线第4次社交回应的图示读值超出正文报告范围，需核实该点后确认所用基线。</t>
+          <t>Claude补提取（以图为准）：从PDF第9页内嵌原图（1070×1290像素）逐像素检测Emmett面板的实心方块（社交回应），纵轴按PDF中刻度标签位置换算（5.75像素/单位）。基线同D0327。6周追踪的常规会话最右侧实心方块与实心圆重叠，按方块上缘推算为10（圆为9）；与新同伴的泛化追踪为18，两者均值14、范围10–18，与正文一致。追踪只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -31199,18 +31539,32 @@
       </c>
       <c r="E357" s="13" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>干预</t>
         </is>
       </c>
       <c r="F357" s="29" t="inlineStr">
         <is>
-          <t>待审核：Baseline（基线期） / VP Intervention（视频提示干预） / Maintenance（维持期）（原图阶段词；归属未定）</t>
-        </is>
-      </c>
-      <c r="G357" s="33" t="n"/>
-      <c r="H357" s="34" t="n"/>
-      <c r="I357" s="33" t="n"/>
-      <c r="J357" s="34" t="n"/>
+          <t>Baseline（基线期） vs VP Intervention（视频提示干预）</t>
+        </is>
+      </c>
+      <c r="G357" s="33" t="inlineStr">
+        <is>
+          <t>33,25,25,10,30,30</t>
+        </is>
+      </c>
+      <c r="H357" s="34">
+        <f>IF(LEN(G357)=0,"",IF(ISNUMBER(SEARCH(",",G357)),LEN(SUBSTITUTE(G357,",","xx"))-LEN(G357)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I357" s="33" t="inlineStr">
+        <is>
+          <t>60,70,90,80,75,100</t>
+        </is>
+      </c>
+      <c r="J357" s="34">
+        <f>IF(LEN(I357)=0,"",IF(ISNUMBER(SEARCH(",",I357)),LEN(SUBSTITUTE(I357,",","xx"))-LEN(I357)+1,1))</f>
+        <v/>
+      </c>
       <c r="K357" s="13" t="inlineStr">
         <is>
           <t>%</t>
@@ -31221,9 +31575,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M357" s="38" t="n"/>
-      <c r="N357" s="38" t="n"/>
-      <c r="O357" s="16" t="n"/>
+      <c r="M357" s="38" t="n">
+        <v>-0.07161148740394328</v>
+      </c>
+      <c r="N357" s="38" t="n">
+        <v>0.8454939839779005</v>
+      </c>
+      <c r="O357" s="16">
+        <f>IF(AND(N357&lt;0.05,OR(AND(L357="升高改善",M357&gt;0),AND(L357="降低改善",M357&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P357" s="13" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；从上至下第3个Mallory Skill 1面板；实心圆为Baseline、VP Intervention和Maintenance数据；空心方块为generalization mean data，非逐次测量；纵轴Percent of Correct Responses。</t>
@@ -31231,17 +31592,17 @@
       </c>
       <c r="Q357" s="13" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R357" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S357" s="13" t="inlineStr">
         <is>
-          <t>待审核：图中阶段线分出6个干预点和5个维持点，正文对应为9个和2个，干预与维持边界尚未确定。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mallory技能1：基线6点均值25.5%，与正文25.5%（10–33%）一致。图文不一致：图上虚线把干预分为6点、维持5点（80,90,100,95,100）；正文干预均值82.78%正是图上干预6点加维持前3点共9点的均值，维持“95–100%”对应最后2点，说明正文的阶段划分与图不同。按图取干预6点。原比较类型“待审核”改为干预比较；如需维持效应，可另加一行：基线 vs 维持80,90,100,95,100。</t>
         </is>
       </c>
     </row>
@@ -31268,18 +31629,32 @@
       </c>
       <c r="E358" s="18" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>干预</t>
         </is>
       </c>
       <c r="F358" s="30" t="inlineStr">
         <is>
-          <t>待审核：Baseline（基线期） / VP Intervention（视频提示干预） / Maintenance（维持期）（原图阶段词；归属未定）</t>
-        </is>
-      </c>
-      <c r="G358" s="22" t="n"/>
-      <c r="H358" s="23" t="n"/>
-      <c r="I358" s="22" t="n"/>
-      <c r="J358" s="23" t="n"/>
+          <t>Baseline（基线期） vs VP Intervention（视频提示干预）</t>
+        </is>
+      </c>
+      <c r="G358" s="22" t="inlineStr">
+        <is>
+          <t>40,20,20,20,10,0,40,40</t>
+        </is>
+      </c>
+      <c r="H358" s="23">
+        <f>IF(LEN(G358)=0,"",IF(ISNUMBER(SEARCH(",",G358)),LEN(SUBSTITUTE(G358,",","xx"))-LEN(G358)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I358" s="22" t="inlineStr">
+        <is>
+          <t>60,60,100,100</t>
+        </is>
+      </c>
+      <c r="J358" s="23">
+        <f>IF(LEN(I358)=0,"",IF(ISNUMBER(SEARCH(",",I358)),LEN(SUBSTITUTE(I358,",","xx"))-LEN(I358)+1,1))</f>
+        <v/>
+      </c>
       <c r="K358" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -31290,9 +31665,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M358" s="39" t="n"/>
-      <c r="N358" s="39" t="n"/>
-      <c r="O358" s="21" t="n"/>
+      <c r="M358" s="39" t="n">
+        <v>-0.08058229640253801</v>
+      </c>
+      <c r="N358" s="39" t="n">
+        <v>0.7928489826282048</v>
+      </c>
+      <c r="O358" s="21">
+        <f>IF(AND(N358&lt;0.05,OR(AND(L358="升高改善",M358&gt;0),AND(L358="降低改善",M358&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P358" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；从上至下第4个Mallory Skill 2面板；实心圆为Baseline、VP Intervention和Maintenance数据；空心方块为generalization mean data，非逐次测量；纵轴Percent of Correct Responses。</t>
@@ -31300,17 +31682,17 @@
       </c>
       <c r="Q358" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R358" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S358" s="18" t="inlineStr">
         <is>
-          <t>待审核：图中干预与维持点数为4个和2个，正文对应为5个和1个，且基线均值与正文不符、横轴未标会话号。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mallory技能2：基线8点（空心方块为泛化探测，未计入），均值23.75%，正文21.22%（0–40%）。干预4点均值80%，正文84%（60–100%），正文均值与图上干预4点加维持第1点共5点的均值一致；横轴未标会话号，不影响Tau-U。图文不一致，按图取值。原比较类型“待审核”改为干预比较；维持期图上为100,100（另1个空心方块60%为泛化探测）。</t>
         </is>
       </c>
     </row>
@@ -31337,18 +31719,32 @@
       </c>
       <c r="E359" s="18" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>干预</t>
         </is>
       </c>
       <c r="F359" s="30" t="inlineStr">
         <is>
-          <t>待审核：Baseline（基线期） / VP Intervention（视频提示干预） / Maintenance（维持期）（原图阶段词；归属未定）</t>
-        </is>
-      </c>
-      <c r="G359" s="22" t="n"/>
-      <c r="H359" s="23" t="n"/>
-      <c r="I359" s="22" t="n"/>
-      <c r="J359" s="23" t="n"/>
+          <t>Baseline（基线期） vs VP Intervention（视频提示干预）</t>
+        </is>
+      </c>
+      <c r="G359" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H359" s="23">
+        <f>IF(LEN(G359)=0,"",IF(ISNUMBER(SEARCH(",",G359)),LEN(SUBSTITUTE(G359,",","xx"))-LEN(G359)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I359" s="22" t="inlineStr">
+        <is>
+          <t>10,80,80,100,100</t>
+        </is>
+      </c>
+      <c r="J359" s="23">
+        <f>IF(LEN(I359)=0,"",IF(ISNUMBER(SEARCH(",",I359)),LEN(SUBSTITUTE(I359,",","xx"))-LEN(I359)+1,1))</f>
+        <v/>
+      </c>
       <c r="K359" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -31359,9 +31755,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M359" s="39" t="n"/>
-      <c r="N359" s="39" t="n"/>
-      <c r="O359" s="21" t="n"/>
+      <c r="M359" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O359" s="21">
+        <f>IF(AND(N359&lt;0.05,OR(AND(L359="升高改善",M359&gt;0),AND(L359="降低改善",M359&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P359" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；从上至下第5个Mateo Skill 1面板；实心圆为Baseline、VP Intervention和Maintenance数据；空心方块为generalization mean data，非逐次测量；纵轴Percent of Correct Responses。</t>
@@ -31369,17 +31772,17 @@
       </c>
       <c r="Q359" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R359" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S359" s="18" t="inlineStr">
         <is>
-          <t>待审核：方法称未测维持，图末两点却被结果段描述为追踪数据，阶段归属矛盾，需确认干预与维持边界。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mateo技能1：基线9点均为0；干预5点均值74%，与正文74%（10–100%）一致。图文不一致：正文基线均值1%（范围0–10%），图上基线全为0；正文称未测维持，但图上虚线后有2点（100,90，均值95%，与结果段“维持95%”一致）。按图取值。原比较类型“待审核”改为干预比较；如需维持效应，可另加一行：基线 vs 维持100,90。</t>
         </is>
       </c>
     </row>
@@ -31414,10 +31817,24 @@
           <t>Baseline（基线期） vs VP Intervention（视频提示干预）</t>
         </is>
       </c>
-      <c r="G360" s="22" t="n"/>
-      <c r="H360" s="23" t="n"/>
-      <c r="I360" s="22" t="n"/>
-      <c r="J360" s="23" t="n"/>
+      <c r="G360" s="22" t="inlineStr">
+        <is>
+          <t>12,12,0,0,40,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H360" s="23">
+        <f>IF(LEN(G360)=0,"",IF(ISNUMBER(SEARCH(",",G360)),LEN(SUBSTITUTE(G360,",","xx"))-LEN(G360)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I360" s="22" t="inlineStr">
+        <is>
+          <t>31,60,60,60</t>
+        </is>
+      </c>
+      <c r="J360" s="23">
+        <f>IF(LEN(I360)=0,"",IF(ISNUMBER(SEARCH(",",I360)),LEN(SUBSTITUTE(I360,",","xx"))-LEN(I360)+1,1))</f>
+        <v/>
+      </c>
       <c r="K360" s="18" t="inlineStr">
         <is>
           <t>%</t>
@@ -31428,9 +31845,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M360" s="39" t="n"/>
-      <c r="N360" s="39" t="n"/>
-      <c r="O360" s="21" t="n"/>
+      <c r="M360" s="39" t="n">
+        <v>-0.4662524041201569</v>
+      </c>
+      <c r="N360" s="39" t="n">
+        <v>0.09284922807157968</v>
+      </c>
+      <c r="O360" s="21">
+        <f>IF(AND(N360&lt;0.05,OR(AND(L360="升高改善",M360&gt;0),AND(L360="降低改善",M360&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P360" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；从上至下第6个Mateo Skill 2面板；实心圆为Baseline、VP Intervention和Maintenance数据；空心方块为generalization mean data，非逐次测量；纵轴Percent of Correct Responses。</t>
@@ -31438,17 +31862,17 @@
       </c>
       <c r="Q360" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R360" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S360" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线图示均值与正文报告不一致，无法定位具体错误点，且横轴未印会话数字，确切会话号需核实。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mateo技能2：基线10点（横轴未标会话号，只按先后取值），均值6.4%；正文基线均值7.9%（0–40%），图文不一致，无法定位，按图取值。干预4点：图上第1点约31%，正文干预均值52.5%（30–60%）对应第1点为30%，差1个百分点，不影响Tau-U。</t>
         </is>
       </c>
     </row>
@@ -32519,10 +32943,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G373" s="22" t="n"/>
-      <c r="H373" s="23" t="n"/>
-      <c r="I373" s="22" t="n"/>
-      <c r="J373" s="23" t="n"/>
+      <c r="G373" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H373" s="23">
+        <f>IF(LEN(G373)=0,"",IF(ISNUMBER(SEARCH(",",G373)),LEN(SUBSTITUTE(G373,",","xx"))-LEN(G373)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I373" s="22" t="inlineStr">
+        <is>
+          <t>12,20,11,6,20</t>
+        </is>
+      </c>
+      <c r="J373" s="23">
+        <f>IF(LEN(I373)=0,"",IF(ISNUMBER(SEARCH(",",I373)),LEN(SUBSTITUTE(I373,",","xx"))-LEN(I373)+1,1))</f>
+        <v/>
+      </c>
       <c r="K373" s="18" t="inlineStr">
         <is>
           <t>次数/观察期</t>
@@ -32533,9 +32971,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M373" s="39" t="n"/>
-      <c r="N373" s="39" t="n"/>
-      <c r="O373" s="21" t="n"/>
+      <c r="M373" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N373" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O373" s="21">
+        <f>IF(AND(N373&lt;0.05,OR(AND(L373="升高改善",M373&gt;0),AND(L373="降低改善",M373&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P373" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；最上方Dyad A（Aaron）面板；右纵轴Frequency of Communication Opportunities and Child Behavior；实心方块（child target communication behavior）；三角形和圆形为教师/沟通机会数据，不属于本行。Aaron目标原文：Request desired or needed item(s) or action(s) from an adult or peer using three or more spoken words。</t>
@@ -32543,17 +32988,17 @@
       </c>
       <c r="Q373" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R373" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S373" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段五个图示点超出正文报告范围，且相关泛化阶段的图文值疑似对调，需核实阶段和读值。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。基线6点与D0371相同。维持期实心方块为第17、21、25、29、33次：12,20,11,6,20（第33次方块上叠了一个无边框白色圆点，渲染后像空心方块，矢量数据显示为实心方块）。图文不一致：正文报告维持范围9–16，图上为6–20；同图Bryan的数据也与正文范围不符，判断为正文问题，按图取值。</t>
         </is>
       </c>
     </row>
@@ -32588,10 +33033,24 @@
           <t>Baseline (Generalization Probes)（基线期的泛化测查） vs Intervention (Generalization Probes)（干预期的泛化测查）</t>
         </is>
       </c>
-      <c r="G374" s="22" t="n"/>
-      <c r="H374" s="23" t="n"/>
-      <c r="I374" s="22" t="n"/>
-      <c r="J374" s="23" t="n"/>
+      <c r="G374" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H374" s="23">
+        <f>IF(LEN(G374)=0,"",IF(ISNUMBER(SEARCH(",",G374)),LEN(SUBSTITUTE(G374,",","xx"))-LEN(G374)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I374" s="22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J374" s="23">
+        <f>IF(LEN(I374)=0,"",IF(ISNUMBER(SEARCH(",",I374)),LEN(SUBSTITUTE(I374,",","xx"))-LEN(I374)+1,1))</f>
+        <v/>
+      </c>
       <c r="K374" s="18" t="inlineStr">
         <is>
           <t>次数/观察期</t>
@@ -32602,9 +33061,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M374" s="39" t="n"/>
-      <c r="N374" s="39" t="n"/>
-      <c r="O374" s="21" t="n"/>
+      <c r="M374" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O374" s="21">
+        <f>IF(AND(N374&lt;0.05,OR(AND(L374="升高改善",M374&gt;0),AND(L374="降低改善",M374&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P374" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；最上方Dyad A（Aaron）面板；右纵轴Frequency of Communication Opportunities and Child Behavior；空心方块（child behavior generalization probes）；三角形和圆形为教师/沟通机会数据，不属于本行。Aaron目标原文：Request desired or needed item(s) or action(s) from an adult or peer using three or more spoken words。</t>
@@ -32612,17 +33078,17 @@
       </c>
       <c r="Q374" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R374" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S374" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预期与维持期的泛化图示值和正文所述疑似对调，尚需确认两个探测点的数值及阶段归属。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。泛化探测（空心方块）：基线第5次为0，干预期第16次为13。图文不一致：正文写“干预期10、维持期13”，图上干预期为13、维持期为10，两者疑似对调；按图取值。两段均只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -32657,10 +33123,24 @@
           <t>Baseline (Generalization Probes)（基线期的泛化测查） vs Maintenance (Generalization Probes)（维持期的泛化测查）</t>
         </is>
       </c>
-      <c r="G375" s="22" t="n"/>
-      <c r="H375" s="23" t="n"/>
-      <c r="I375" s="22" t="n"/>
-      <c r="J375" s="23" t="n"/>
+      <c r="G375" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H375" s="23">
+        <f>IF(LEN(G375)=0,"",IF(ISNUMBER(SEARCH(",",G375)),LEN(SUBSTITUTE(G375,",","xx"))-LEN(G375)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I375" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J375" s="23">
+        <f>IF(LEN(I375)=0,"",IF(ISNUMBER(SEARCH(",",I375)),LEN(SUBSTITUTE(I375,",","xx"))-LEN(I375)+1,1))</f>
+        <v/>
+      </c>
       <c r="K375" s="18" t="inlineStr">
         <is>
           <t>次数/观察期</t>
@@ -32671,9 +33151,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M375" s="39" t="n"/>
-      <c r="N375" s="39" t="n"/>
-      <c r="O375" s="21" t="n"/>
+      <c r="M375" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N375" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O375" s="21">
+        <f>IF(AND(N375&lt;0.05,OR(AND(L375="升高改善",M375&gt;0),AND(L375="降低改善",M375&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P375" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第9页，所查看图页未标印刷页码；最上方Dyad A（Aaron）面板；右纵轴Frequency of Communication Opportunities and Child Behavior；空心方块（child behavior generalization probes）；三角形和圆形为教师/沟通机会数据，不属于本行。Aaron目标原文：Request desired or needed item(s) or action(s) from an adult or peer using three or more spoken words。</t>
@@ -32681,17 +33168,17 @@
       </c>
       <c r="Q375" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R375" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S375" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预期与维持期的泛化图示值和正文所述疑似对调，尚需确认两个探测点的数值及阶段归属。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。泛化探测：基线第5次为0，维持期第34次为10。图文不一致：正文写维持期13，图上为10（与干预期数值疑似对调，见D0373）；按图取值。两段均只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
     </row>
@@ -37628,10 +38115,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G433" s="33" t="n"/>
-      <c r="H433" s="34" t="n"/>
-      <c r="I433" s="33" t="n"/>
-      <c r="J433" s="34" t="n"/>
+      <c r="G433" s="33" t="inlineStr">
+        <is>
+          <t>20,35,30,25,15,40,45,40,40</t>
+        </is>
+      </c>
+      <c r="H433" s="34">
+        <f>IF(LEN(G433)=0,"",IF(ISNUMBER(SEARCH(",",G433)),LEN(SUBSTITUTE(G433,",","xx"))-LEN(G433)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I433" s="33" t="inlineStr">
+        <is>
+          <t>70,80,90,100,90,120,135,150,140,160,175,180,190,175,180,190,220,250</t>
+        </is>
+      </c>
+      <c r="J433" s="34">
+        <f>IF(LEN(I433)=0,"",IF(ISNUMBER(SEARCH(",",I433)),LEN(SUBSTITUTE(I433,",","xx"))-LEN(I433)+1,1))</f>
+        <v/>
+      </c>
       <c r="K433" s="13" t="inlineStr">
         <is>
           <t>秒</t>
@@ -37642,9 +38143,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M433" s="38" t="n"/>
-      <c r="N433" s="38" t="n"/>
-      <c r="O433" s="16" t="n"/>
+      <c r="M433" s="38" t="n">
+        <v>0.4351941398892446</v>
+      </c>
+      <c r="N433" s="38" t="n">
+        <v>0.110492024055668</v>
+      </c>
+      <c r="O433" s="16">
+        <f>IF(AND(N433&lt;0.05,OR(AND(L433="升高改善",M433&gt;0),AND(L433="降低改善",M433&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P433" s="13" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第14页，印刷页1134；从上至下第1个Fox面板；实心圆连线，纵轴The Duration of Social Interaction (Seconds)；Baseline与Intervention竖虚线两侧。</t>
@@ -37652,17 +38160,17 @@
       </c>
       <c r="Q433" s="13" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R433" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S433" s="13" t="inlineStr">
         <is>
-          <t>待审核：基线社交互动时长的图示最大值超出表1报告范围，图表不一致，需核实最高观察点。</t>
+          <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。Fox基线9点均值32.2，与表1一致；图文不一致：基线第7次图上为45秒，超出表1范围15–40。干预18点均值149.7、范围70–250，与表1一致。按图取值。</t>
         </is>
       </c>
     </row>
@@ -37697,10 +38205,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G434" s="22" t="n"/>
-      <c r="H434" s="23" t="n"/>
-      <c r="I434" s="22" t="n"/>
-      <c r="J434" s="23" t="n"/>
+      <c r="G434" s="22" t="inlineStr">
+        <is>
+          <t>20,35,30,25,15,40,45,40,40</t>
+        </is>
+      </c>
+      <c r="H434" s="23">
+        <f>IF(LEN(G434)=0,"",IF(ISNUMBER(SEARCH(",",G434)),LEN(SUBSTITUTE(G434,",","xx"))-LEN(G434)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I434" s="22" t="inlineStr">
+        <is>
+          <t>170,180,190,190</t>
+        </is>
+      </c>
+      <c r="J434" s="23">
+        <f>IF(LEN(I434)=0,"",IF(ISNUMBER(SEARCH(",",I434)),LEN(SUBSTITUTE(I434,",","xx"))-LEN(I434)+1,1))</f>
+        <v/>
+      </c>
       <c r="K434" s="18" t="inlineStr">
         <is>
           <t>秒</t>
@@ -37711,9 +38233,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M434" s="39" t="n"/>
-      <c r="N434" s="39" t="n"/>
-      <c r="O434" s="21" t="n"/>
+      <c r="M434" s="39" t="n">
+        <v>0.4351941398892446</v>
+      </c>
+      <c r="N434" s="39" t="n">
+        <v>0.110492024055668</v>
+      </c>
+      <c r="O434" s="21">
+        <f>IF(AND(N434&lt;0.05,OR(AND(L434="升高改善",M434&gt;0),AND(L434="降低改善",M434&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P434" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第14页，印刷页1134；从上至下第1个Fox面板；实心圆连线，纵轴The Duration of Social Interaction (Seconds)；右侧Maintenance区域。</t>
@@ -37721,17 +38250,17 @@
       </c>
       <c r="Q434" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R434" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S434" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线社交互动时长的图示最大值超出表1报告范围，图表不一致，需核实最高观察点。</t>
+          <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。基线同D0432（第7次45秒超出表1范围）。维持4点均值182.5、范围170–190，与表1一致。</t>
         </is>
       </c>
     </row>
@@ -37766,10 +38295,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G435" s="22" t="n"/>
-      <c r="H435" s="23" t="n"/>
-      <c r="I435" s="22" t="n"/>
-      <c r="J435" s="23" t="n"/>
+      <c r="G435" s="22" t="inlineStr">
+        <is>
+          <t>2,3,3,5,4,3,4,4,4</t>
+        </is>
+      </c>
+      <c r="H435" s="23">
+        <f>IF(LEN(G435)=0,"",IF(ISNUMBER(SEARCH(",",G435)),LEN(SUBSTITUTE(G435,",","xx"))-LEN(G435)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I435" s="22" t="inlineStr">
+        <is>
+          <t>6,6,8,7,8,8,9,9,8,8,9,7,8,9,8,9,10,10</t>
+        </is>
+      </c>
+      <c r="J435" s="23">
+        <f>IF(LEN(I435)=0,"",IF(ISNUMBER(SEARCH(",",I435)),LEN(SUBSTITUTE(I435,",","xx"))-LEN(I435)+1,1))</f>
+        <v/>
+      </c>
       <c r="K435" s="18" t="inlineStr">
         <is>
           <t>次数</t>
@@ -37780,9 +38323,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M435" s="39" t="n"/>
-      <c r="N435" s="39" t="n"/>
-      <c r="O435" s="21" t="n"/>
+      <c r="M435" s="39" t="n">
+        <v>0.4811252243246881</v>
+      </c>
+      <c r="N435" s="39" t="n">
+        <v>0.09284922807157968</v>
+      </c>
+      <c r="O435" s="21">
+        <f>IF(AND(N435&lt;0.05,OR(AND(L435="升高改善",M435&gt;0),AND(L435="降低改善",M435&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P435" s="18" t="inlineStr">
         <is>
           <t>Fig. 2；PDF第16页，印刷页1136；从上至下第1个Fox面板；黑色实心方块，图例Initiations；Baseline与Intervention竖虚线两侧。</t>
@@ -37790,17 +38340,17 @@
       </c>
       <c r="Q435" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R435" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S435" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线第4次观察的图示读值与表1范围冲突，正文范围却支持图示，原文内部不一致，需核实该点。</t>
+          <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。Fox基线9点均值3.56，与表1均值3.60一致；图文不一致：基线第4次图上为5，超出表1范围2–4（正文范围支持图示）。干预18点均值8.17、范围6–10，与表1（8.20，6–10）一致。按图取值。</t>
         </is>
       </c>
     </row>
@@ -37835,10 +38385,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G436" s="22" t="n"/>
-      <c r="H436" s="23" t="n"/>
-      <c r="I436" s="22" t="n"/>
-      <c r="J436" s="23" t="n"/>
+      <c r="G436" s="22" t="inlineStr">
+        <is>
+          <t>2,3,3,5,4,3,4,4,4</t>
+        </is>
+      </c>
+      <c r="H436" s="23">
+        <f>IF(LEN(G436)=0,"",IF(ISNUMBER(SEARCH(",",G436)),LEN(SUBSTITUTE(G436,",","xx"))-LEN(G436)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I436" s="22" t="inlineStr">
+        <is>
+          <t>7,8,7,7</t>
+        </is>
+      </c>
+      <c r="J436" s="23">
+        <f>IF(LEN(I436)=0,"",IF(ISNUMBER(SEARCH(",",I436)),LEN(SUBSTITUTE(I436,",","xx"))-LEN(I436)+1,1))</f>
+        <v/>
+      </c>
       <c r="K436" s="18" t="inlineStr">
         <is>
           <t>次数</t>
@@ -37849,9 +38413,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M436" s="39" t="n"/>
-      <c r="N436" s="39" t="n"/>
-      <c r="O436" s="21" t="n"/>
+      <c r="M436" s="39" t="n">
+        <v>0.4811252243246881</v>
+      </c>
+      <c r="N436" s="39" t="n">
+        <v>0.09284922807157968</v>
+      </c>
+      <c r="O436" s="21">
+        <f>IF(AND(N436&lt;0.05,OR(AND(L436="升高改善",M436&gt;0),AND(L436="降低改善",M436&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P436" s="18" t="inlineStr">
         <is>
           <t>Fig. 2；PDF第16页，印刷页1136；从上至下第1个Fox面板；黑色实心方块，图例Initiations；右侧Maintenance区域。</t>
@@ -37859,17 +38430,17 @@
       </c>
       <c r="Q436" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R436" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S436" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线第4次观察的图示读值与表1范围冲突，正文范围却支持图示，原文内部不一致，需核实该点。</t>
+          <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。基线同D0434。维持4点均值7.25、范围7–8，与表1（7.20，7–8）一致。</t>
         </is>
       </c>
     </row>
@@ -38076,10 +38647,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G439" s="22" t="n"/>
-      <c r="H439" s="23" t="n"/>
-      <c r="I439" s="22" t="n"/>
-      <c r="J439" s="23" t="n"/>
+      <c r="G439" s="22" t="inlineStr">
+        <is>
+          <t>20,15,15,25,20,20,15,25,20,25,25,25</t>
+        </is>
+      </c>
+      <c r="H439" s="23">
+        <f>IF(LEN(G439)=0,"",IF(ISNUMBER(SEARCH(",",G439)),LEN(SUBSTITUTE(G439,",","xx"))-LEN(G439)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I439" s="22" t="inlineStr">
+        <is>
+          <t>55,60,65,85,95,110,100,150,120,160,180,175,190,220,250</t>
+        </is>
+      </c>
+      <c r="J439" s="23">
+        <f>IF(LEN(I439)=0,"",IF(ISNUMBER(SEARCH(",",I439)),LEN(SUBSTITUTE(I439,",","xx"))-LEN(I439)+1,1))</f>
+        <v/>
+      </c>
       <c r="K439" s="18" t="inlineStr">
         <is>
           <t>秒</t>
@@ -38090,9 +38675,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M439" s="39" t="n"/>
-      <c r="N439" s="39" t="n"/>
-      <c r="O439" s="21" t="n"/>
+      <c r="M439" s="39" t="n">
+        <v>0.4847779606994154</v>
+      </c>
+      <c r="N439" s="39" t="n">
+        <v>0.04634124184080035</v>
+      </c>
+      <c r="O439" s="21">
+        <f>IF(AND(N439&lt;0.05,OR(AND(L439="升高改善",M439&gt;0),AND(L439="降低改善",M439&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P439" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第14页，印刷页1134；从上至下第2个Sam面板；实心圆连线，纵轴The Duration of Social Interaction (Seconds)；Baseline与Intervention竖虚线两侧。</t>
@@ -38100,17 +38692,17 @@
       </c>
       <c r="Q439" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R439" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S439" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线图示均值及范围与表1不符，干预末段图示值又超出表1上限，无法定位错误来源，需核实两段数据。</t>
+          <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。图文不一致：Sam基线12点均值20.8、范围15–25，表1报告28.7（15–40）；干预15点均值134.3、范围55–250，表1报告133.3（55–200）。表1中Sam基线的均值、SD、范围与Fox高度相似，可能有抄录错误。按图取值。</t>
         </is>
       </c>
     </row>
@@ -38145,10 +38737,24 @@
           <t>Baseline（基线期） vs Maintenance（维持期）</t>
         </is>
       </c>
-      <c r="G440" s="22" t="n"/>
-      <c r="H440" s="23" t="n"/>
-      <c r="I440" s="22" t="n"/>
-      <c r="J440" s="23" t="n"/>
+      <c r="G440" s="22" t="inlineStr">
+        <is>
+          <t>20,15,15,25,20,20,15,25,20,25,25,25</t>
+        </is>
+      </c>
+      <c r="H440" s="23">
+        <f>IF(LEN(G440)=0,"",IF(ISNUMBER(SEARCH(",",G440)),LEN(SUBSTITUTE(G440,",","xx"))-LEN(G440)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I440" s="22" t="inlineStr">
+        <is>
+          <t>200,170,180,200</t>
+        </is>
+      </c>
+      <c r="J440" s="23">
+        <f>IF(LEN(I440)=0,"",IF(ISNUMBER(SEARCH(",",I440)),LEN(SUBSTITUTE(I440,",","xx"))-LEN(I440)+1,1))</f>
+        <v/>
+      </c>
       <c r="K440" s="18" t="inlineStr">
         <is>
           <t>秒</t>
@@ -38159,9 +38765,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M440" s="39" t="n"/>
-      <c r="N440" s="39" t="n"/>
-      <c r="O440" s="21" t="n"/>
+      <c r="M440" s="39" t="n">
+        <v>0.4847779606994154</v>
+      </c>
+      <c r="N440" s="39" t="n">
+        <v>0.04634124184080035</v>
+      </c>
+      <c r="O440" s="21">
+        <f>IF(AND(N440&lt;0.05,OR(AND(L440="升高改善",M440&gt;0),AND(L440="降低改善",M440&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P440" s="18" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第14页，印刷页1134；从上至下第2个Sam面板；实心圆连线，纵轴The Duration of Social Interaction (Seconds)；右侧Maintenance区域。</t>
@@ -38169,17 +38782,17 @@
       </c>
       <c r="Q440" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R440" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S440" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线及维持阶段的图示均值、范围均与表1报告不一致，无法定位具体错误点，需核实两个阶段。</t>
+          <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。基线同D0438。图文不一致：维持4点均值187.5、范围170–200，表1报告170（160–180）。按图取值。</t>
         </is>
       </c>
     </row>
@@ -38902,10 +39515,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G449" s="22" t="n"/>
-      <c r="H449" s="23" t="n"/>
-      <c r="I449" s="22" t="n"/>
-      <c r="J449" s="23" t="n"/>
+      <c r="G449" s="22" t="inlineStr">
+        <is>
+          <t>1,2,2,3,2,3,3,2,4,3,4,3,2,3,3,3,3</t>
+        </is>
+      </c>
+      <c r="H449" s="23">
+        <f>IF(LEN(G449)=0,"",IF(ISNUMBER(SEARCH(",",G449)),LEN(SUBSTITUTE(G449,",","xx"))-LEN(G449)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I449" s="22" t="inlineStr">
+        <is>
+          <t>5,6,5,6,8,8,7,8,8,9</t>
+        </is>
+      </c>
+      <c r="J449" s="23">
+        <f>IF(LEN(I449)=0,"",IF(ISNUMBER(SEARCH(",",I449)),LEN(SUBSTITUTE(I449,",","xx"))-LEN(I449)+1,1))</f>
+        <v/>
+      </c>
       <c r="K449" s="18" t="inlineStr">
         <is>
           <t>次数</t>
@@ -38916,9 +39543,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M449" s="39" t="n"/>
-      <c r="N449" s="39" t="n"/>
-      <c r="O449" s="21" t="n"/>
+      <c r="M449" s="39" t="n">
+        <v>0.4090233075190866</v>
+      </c>
+      <c r="N449" s="39" t="n">
+        <v>0.03991058571027136</v>
+      </c>
+      <c r="O449" s="21">
+        <f>IF(AND(N449&lt;0.05,OR(AND(L449="升高改善",M449&gt;0),AND(L449="降低改善",M449&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P449" s="18" t="inlineStr">
         <is>
           <t>Fig. 2；PDF第16页，印刷页1136；从上至下第3个Nia面板；浅灰圆点及浅灰连线，图例Responses；Baseline与Intervention竖虚线两侧。</t>
@@ -38926,17 +39560,17 @@
       </c>
       <c r="Q449" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R449" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S449" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预图可见10个观察点，其均值与表1报告不符，尚不能判断具体哪些点或表值有误。</t>
+          <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。基线17点与D0449相同。图文不一致：干预10点均值7.0，表1报告7.70（范围5–9与图一致），无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
     </row>
@@ -39057,10 +39691,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G451" s="33" t="n"/>
-      <c r="H451" s="34" t="n"/>
-      <c r="I451" s="33" t="n"/>
-      <c r="J451" s="34" t="n"/>
+      <c r="G451" s="33" t="inlineStr">
+        <is>
+          <t>0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H451" s="34">
+        <f>IF(LEN(G451)=0,"",IF(ISNUMBER(SEARCH(",",G451)),LEN(SUBSTITUTE(G451,",","xx"))-LEN(G451)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I451" s="33" t="inlineStr">
+        <is>
+          <t>100,88,100,100,100,100,100,80,90,100,87,53,65,60,75,100,55,100,100,73,93,80,80,100,92,100,85,100,70,95</t>
+        </is>
+      </c>
+      <c r="J451" s="34">
+        <f>IF(LEN(I451)=0,"",IF(ISNUMBER(SEARCH(",",I451)),LEN(SUBSTITUTE(I451,",","xx"))-LEN(I451)+1,1))</f>
+        <v/>
+      </c>
       <c r="K451" s="3" t="inlineStr">
         <is>
           <t>%</t>
@@ -39071,9 +39719,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M451" s="38" t="n"/>
-      <c r="N451" s="38" t="n"/>
-      <c r="O451" s="16" t="n"/>
+      <c r="M451" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N451" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O451" s="16">
+        <f>IF(AND(N451&lt;0.05,OR(AND(L451="升高改善",M451&gt;0),AND(L451="降低改善",M451&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P451" s="3" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第8页，所查看图页未标印刷页码；从上至下第1个Participant One面板；黑色实心方块及实线（Student with ASD）；灰圆及灰虚线为Peer Comparison，不属于本行；纵轴Percentage of Time Engaged。</t>
@@ -39081,17 +39736,17 @@
       </c>
       <c r="Q451" s="3" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R451" s="35" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S451" s="3" t="inlineStr">
         <is>
-          <t>待审核：图1被试1和被试2与正文对应的基线均值及干预最小值疑似互换，需先核实被试与曲线的对应关系。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取黑色实心方块（Student with ASD）的PDF坐标，按各面板0与100位置换算后取整；缺失的观测为学生缺勤（图注）。Participant One面板：基线4点均为0，干预30点均值87.4%、最小值53%。图文不一致：正文写被试1基线1%（0–5%）、干预范围47–100%，与图上Participant Two面板的数值对应，被试1、2在正文中疑似对调。按图（面板标签）取值。</t>
         </is>
       </c>
     </row>
@@ -39213,10 +39868,24 @@
           <t>Baseline（基线期） vs Intervention（干预期）</t>
         </is>
       </c>
-      <c r="G453" s="22" t="n"/>
-      <c r="H453" s="23" t="n"/>
-      <c r="I453" s="22" t="n"/>
-      <c r="J453" s="23" t="n"/>
+      <c r="G453" s="22" t="inlineStr">
+        <is>
+          <t>0,5,0,0</t>
+        </is>
+      </c>
+      <c r="H453" s="23">
+        <f>IF(LEN(G453)=0,"",IF(ISNUMBER(SEARCH(",",G453)),LEN(SUBSTITUTE(G453,",","xx"))-LEN(G453)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I453" s="22" t="inlineStr">
+        <is>
+          <t>88,80,80,100,100,97,100,67,100,100,55,47,87,80,60,70,77,100,100,85,100,100,80,100,100,94,100,70,100,100</t>
+        </is>
+      </c>
+      <c r="J453" s="23">
+        <f>IF(LEN(I453)=0,"",IF(ISNUMBER(SEARCH(",",I453)),LEN(SUBSTITUTE(I453,",","xx"))-LEN(I453)+1,1))</f>
+        <v/>
+      </c>
       <c r="K453" s="8" t="inlineStr">
         <is>
           <t>%</t>
@@ -39227,9 +39896,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M453" s="39" t="n"/>
-      <c r="N453" s="39" t="n"/>
-      <c r="O453" s="21" t="n"/>
+      <c r="M453" s="39" t="n">
+        <v>-0.2357022603955159</v>
+      </c>
+      <c r="N453" s="39" t="n">
+        <v>0.6547208460185769</v>
+      </c>
+      <c r="O453" s="21">
+        <f>IF(AND(N453&lt;0.05,OR(AND(L453="升高改善",M453&gt;0),AND(L453="降低改善",M453&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P453" s="8" t="inlineStr">
         <is>
           <t>Fig. 1；PDF第8页，所查看图页未标印刷页码；从上至下第2个Participant Two面板；黑色实心方块及实线（Student with ASD）；灰圆及灰虚线为Peer Comparison，不属于本行；纵轴Percentage of Time Engaged。</t>
@@ -39237,17 +39913,17 @@
       </c>
       <c r="Q453" s="8" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R453" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S453" s="8" t="inlineStr">
         <is>
-          <t>待审核：图1被试1和被试2与正文对应的基线均值及干预最小值疑似互换，需先核实被试与曲线的对应关系。</t>
+          <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取黑色实心方块（Student with ASD）的PDF坐标，按各面板0与100位置换算后取整；缺失的观测为学生缺勤（图注）。Participant Two面板：基线4点均值1.25%（0–5%），干预30点均值87.2%、最小值47%。图文不一致：正文写被试2基线0%、干预范围53–100%，与图上Participant One面板对应，疑似对调。按图（面板标签）取值。两名被试同为三年级学生，对调对合并效应量和按年龄段分组没有影响。</t>
         </is>
       </c>
     </row>
@@ -44227,10 +44903,24 @@
           <t>BASELINE（基线期） vs SOCIAL REINFORCEMENT &amp; PROMPTING（社会性强化与提示）</t>
         </is>
       </c>
-      <c r="G513" s="22" t="n"/>
-      <c r="H513" s="23" t="n"/>
-      <c r="I513" s="22" t="n"/>
-      <c r="J513" s="23" t="n"/>
+      <c r="G513" s="22" t="inlineStr">
+        <is>
+          <t>4,4,0,1,1</t>
+        </is>
+      </c>
+      <c r="H513" s="23">
+        <f>IF(LEN(G513)=0,"",IF(ISNUMBER(SEARCH(",",G513)),LEN(SUBSTITUTE(G513,",","xx"))-LEN(G513)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I513" s="22" t="inlineStr">
+        <is>
+          <t>27,16,9,20,17,55,38</t>
+        </is>
+      </c>
+      <c r="J513" s="23">
+        <f>IF(LEN(I513)=0,"",IF(ISNUMBER(SEARCH(",",I513)),LEN(SUBSTITUTE(I513,",","xx"))-LEN(I513)+1,1))</f>
+        <v/>
+      </c>
       <c r="K513" s="18" t="inlineStr">
         <is>
           <t>次/30分钟观察</t>
@@ -44241,9 +44931,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M513" s="39" t="n"/>
-      <c r="N513" s="39" t="n"/>
-      <c r="O513" s="21" t="n"/>
+      <c r="M513" s="39" t="n">
+        <v>-0.4472135954999579</v>
+      </c>
+      <c r="N513" s="39" t="n">
+        <v>0.2962698714842864</v>
+      </c>
+      <c r="O513" s="21">
+        <f>IF(AND(N513&lt;0.05,OR(AND(L513="升高改善",M513&gt;0),AND(L513="降低改善",M513&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P513" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第11页／印刷第550页；第2面板（Lena，自上而下）；黑色实心圆＝Shadow Therapist；空心圆＝New Therapist，不计入本行</t>
@@ -44251,17 +44948,17 @@
       </c>
       <c r="Q513" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R513" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S513" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线五个图示点的均值与正文报告不一致，尚不能定位具体错误点，需核实原始基线记录。</t>
+          <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。图文不一致：Lena基线5点为4,4,0,1,1（均值2.0），正文写“0–4次，平均3次”，无法定位，按图取值。干预7点合计182、均值26.0、范围9–55，与正文一致。</t>
         </is>
       </c>
     </row>
@@ -44382,10 +45079,24 @@
           <t>BASELINE（基线期） vs SOCIAL REINFORCEMENT &amp; PROMPTING（社会性强化与提示）</t>
         </is>
       </c>
-      <c r="G515" s="22" t="n"/>
-      <c r="H515" s="23" t="n"/>
-      <c r="I515" s="22" t="n"/>
-      <c r="J515" s="23" t="n"/>
+      <c r="G515" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H515" s="23">
+        <f>IF(LEN(G515)=0,"",IF(ISNUMBER(SEARCH(",",G515)),LEN(SUBSTITUTE(G515,",","xx"))-LEN(G515)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I515" s="22" t="inlineStr">
+        <is>
+          <t>10,2,6,1,18,10,53,48,17,26,18,24</t>
+        </is>
+      </c>
+      <c r="J515" s="23">
+        <f>IF(LEN(I515)=0,"",IF(ISNUMBER(SEARCH(",",I515)),LEN(SUBSTITUTE(I515,",","xx"))-LEN(I515)+1,1))</f>
+        <v/>
+      </c>
       <c r="K515" s="18" t="inlineStr">
         <is>
           <t>次/30分钟观察</t>
@@ -44396,9 +45107,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M515" s="39" t="n"/>
-      <c r="N515" s="39" t="n"/>
-      <c r="O515" s="21" t="n"/>
+      <c r="M515" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N515" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O515" s="21">
+        <f>IF(AND(N515&lt;0.05,OR(AND(L515="升高改善",M515&gt;0),AND(L515="降低改善",M515&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P515" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第11页／印刷第550页；第3面板（Andrew，自上而下）；黑色实心圆＝Shadow Therapist；空心圆＝New Therapist，不计入本行</t>
@@ -44406,17 +45124,17 @@
       </c>
       <c r="Q515" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R515" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S515" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预图示最小值与正文报告的下限不一致，尚不能确定差异来源，需核实对应观察点。</t>
+          <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。图文不一致：Andrew干预第4点（第12次）图上约为1，低于正文报告的下限2（正文范围2–53）；干预12点均值19.4，正文约20。按图取值。</t>
         </is>
       </c>
     </row>
@@ -44538,10 +45256,24 @@
           <t>BASELINE（基线期） vs SOCIAL REINFORCEMENT &amp; PROMPTING（社会性强化与提示）</t>
         </is>
       </c>
-      <c r="G517" s="22" t="n"/>
-      <c r="H517" s="23" t="n"/>
-      <c r="I517" s="22" t="n"/>
-      <c r="J517" s="23" t="n"/>
+      <c r="G517" s="22" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="H517" s="23">
+        <f>IF(LEN(G517)=0,"",IF(ISNUMBER(SEARCH(",",G517)),LEN(SUBSTITUTE(G517,",","xx"))-LEN(G517)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I517" s="22" t="inlineStr">
+        <is>
+          <t>4,6,10,8,16,20,14,18,20,17,23</t>
+        </is>
+      </c>
+      <c r="J517" s="23">
+        <f>IF(LEN(I517)=0,"",IF(ISNUMBER(SEARCH(",",I517)),LEN(SUBSTITUTE(I517,",","xx"))-LEN(I517)+1,1))</f>
+        <v/>
+      </c>
       <c r="K517" s="18" t="inlineStr">
         <is>
           <t>次/30分钟观察</t>
@@ -44552,9 +45284,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M517" s="39" t="n"/>
-      <c r="N517" s="39" t="n"/>
-      <c r="O517" s="21" t="n"/>
+      <c r="M517" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N517" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O517" s="21">
+        <f>IF(AND(N517&lt;0.05,OR(AND(L517="升高改善",M517&gt;0),AND(L517="降低改善",M517&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P517" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第11页／印刷第550页；第4面板（Cory，自上而下）；黑色实心圆＝Shadow Therapist；空心圆＝New Therapist，不计入本行</t>
@@ -44562,17 +45301,17 @@
       </c>
       <c r="Q517" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R517" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S517" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预图示点的均值与正文报告不一致，尚不能判断是读图偏差还是文字误差，需核实干预序列。</t>
+          <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。Cory干预11点均值14.2、范围4–23，与正文（平均14，4–23）一致；最后一点图上约22.4，按正文上限取23。原先所说的均值不一致按此读数不存在。</t>
         </is>
       </c>
     </row>
@@ -45849,7 +46588,7 @@
       </c>
       <c r="S532" s="18" t="inlineStr">
         <is>
-          <t>待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -45918,7 +46657,7 @@
       </c>
       <c r="S533" s="18" t="inlineStr">
         <is>
-          <t>待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
+          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
         </is>
       </c>
     </row>
@@ -45987,7 +46726,7 @@
       </c>
       <c r="S534" s="18" t="inlineStr">
         <is>
-          <t>待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -47752,10 +48491,24 @@
           <t>baseline（基线期） vs intervention（干预期）</t>
         </is>
       </c>
-      <c r="G555" s="22" t="n"/>
-      <c r="H555" s="23" t="n"/>
-      <c r="I555" s="22" t="n"/>
-      <c r="J555" s="23" t="n"/>
+      <c r="G555" s="22" t="inlineStr">
+        <is>
+          <t>8,1,2,6,5,1,1,3,3</t>
+        </is>
+      </c>
+      <c r="H555" s="23">
+        <f>IF(LEN(G555)=0,"",IF(ISNUMBER(SEARCH(",",G555)),LEN(SUBSTITUTE(G555,",","xx"))-LEN(G555)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I555" s="22" t="inlineStr">
+        <is>
+          <t>22,27,22,15,24,11,51,6,29,20,33</t>
+        </is>
+      </c>
+      <c r="J555" s="23">
+        <f>IF(LEN(I555)=0,"",IF(ISNUMBER(SEARCH(",",I555)),LEN(SUBSTITUTE(I555,",","xx"))-LEN(I555)+1,1))</f>
+        <v/>
+      </c>
       <c r="K555" s="18" t="inlineStr">
         <is>
           <t>次/10分钟</t>
@@ -47766,9 +48519,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M555" s="39" t="n"/>
-      <c r="N555" s="39" t="n"/>
-      <c r="O555" s="21" t="n"/>
+      <c r="M555" s="39" t="n">
+        <v>-0.1767766952966369</v>
+      </c>
+      <c r="N555" s="39" t="n">
+        <v>0.5208480313753976</v>
+      </c>
+      <c r="O555" s="21">
+        <f>IF(AND(N555&lt;0.05,OR(AND(L555="升高改善",M555&gt;0),AND(L555="降低改善",M555&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P555" s="18" t="inlineStr">
         <is>
           <t>Figure 2；PDF第18页／稿件印刷Page 18（期刊页码未标）；下面板（Brian）；黑色实心圆、实线连接；阶段名称取自Figure 2图注</t>
@@ -47776,17 +48536,17 @@
       </c>
       <c r="Q555" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R555" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S555" s="18" t="inlineStr">
         <is>
-          <t>待审核：基线9个图示点的均值与正文报告不符，且准确会话号尚未确认，需同时核实基线读值和时间对应。</t>
+          <t>Claude补提取（以图为准）：从PDF第18页内嵌图像逐像素检测Brian面板圆点，按纵轴刻度标签换算（同D0552）；基线第3、4次和第5、6次两两相邻重叠，按合并重心和形状拆分为1,2和6,5。会话号对应不影响Tau-U。图文不一致：基线9点均值3.33，正文报告3.8（范围1–8与图一致），无法定位，按图取值。干预11点均值23.6、范围6–51，与正文一致。</t>
         </is>
       </c>
     </row>
@@ -51125,10 +51885,24 @@
           <t>基线期 vs 干预期</t>
         </is>
       </c>
-      <c r="G596" s="22" t="n"/>
-      <c r="H596" s="23" t="n"/>
-      <c r="I596" s="22" t="n"/>
-      <c r="J596" s="23" t="n"/>
+      <c r="G596" s="22" t="inlineStr">
+        <is>
+          <t>0,1,0,2,1,0,1</t>
+        </is>
+      </c>
+      <c r="H596" s="23">
+        <f>IF(LEN(G596)=0,"",IF(ISNUMBER(SEARCH(",",G596)),LEN(SUBSTITUTE(G596,",","xx"))-LEN(G596)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I596" s="22" t="inlineStr">
+        <is>
+          <t>3,5,6,7,16,8,23,10,14,20,18,18,20,19,15,19</t>
+        </is>
+      </c>
+      <c r="J596" s="23">
+        <f>IF(LEN(I596)=0,"",IF(ISNUMBER(SEARCH(",",I596)),LEN(SUBSTITUTE(I596,",","xx"))-LEN(I596)+1,1))</f>
+        <v/>
+      </c>
       <c r="K596" s="18" t="inlineStr">
         <is>
           <t>次</t>
@@ -51139,9 +51913,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M596" s="39" t="n"/>
-      <c r="N596" s="39" t="n"/>
-      <c r="O596" s="21" t="n"/>
+      <c r="M596" s="39" t="n">
+        <v>0.1690308509457033</v>
+      </c>
+      <c r="N596" s="39" t="n">
+        <v>0.621873424330741</v>
+      </c>
+      <c r="O596" s="21">
+        <f>IF(AND(N596&lt;0.05,OR(AND(L596="升高改善",M596&gt;0),AND(L596="降低改善",M596&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P596" s="18" t="inlineStr">
         <is>
           <t>图1“3名被试社交发起与回应行为频次变化折线图”；PDF第5页，印刷页61；从上至下第3个被试小翰面板；实心圆（发起次数）；纵轴行为次数，横轴观察次数；基线期与干预期。</t>
@@ -51149,17 +51930,17 @@
       </c>
       <c r="Q596" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R596" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S596" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预图连续显示16个观察点，正文却称缺席2次，无法确定缺失会话与图示点的对应关系。</t>
+          <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。干预期图上16点，合计221，221÷16=13.81，与正文均值13.81完全一致，说明作者也按16点计算；正文“小翰缺席2次”与数据点数的矛盾属叙述问题，按图取16点。</t>
         </is>
       </c>
     </row>
@@ -51194,10 +51975,24 @@
           <t>基线期 vs 维持期</t>
         </is>
       </c>
-      <c r="G597" s="22" t="n"/>
-      <c r="H597" s="23" t="n"/>
-      <c r="I597" s="22" t="n"/>
-      <c r="J597" s="23" t="n"/>
+      <c r="G597" s="22" t="inlineStr">
+        <is>
+          <t>0,1,0,2,1,0,1</t>
+        </is>
+      </c>
+      <c r="H597" s="23">
+        <f>IF(LEN(G597)=0,"",IF(ISNUMBER(SEARCH(",",G597)),LEN(SUBSTITUTE(G597,",","xx"))-LEN(G597)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I597" s="22" t="inlineStr">
+        <is>
+          <t>16,18,15,16,17</t>
+        </is>
+      </c>
+      <c r="J597" s="23">
+        <f>IF(LEN(I597)=0,"",IF(ISNUMBER(SEARCH(",",I597)),LEN(SUBSTITUTE(I597,",","xx"))-LEN(I597)+1,1))</f>
+        <v/>
+      </c>
       <c r="K597" s="18" t="inlineStr">
         <is>
           <t>次</t>
@@ -51208,9 +52003,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M597" s="39" t="n"/>
-      <c r="N597" s="39" t="n"/>
-      <c r="O597" s="21" t="n"/>
+      <c r="M597" s="39" t="n">
+        <v>0.1690308509457033</v>
+      </c>
+      <c r="N597" s="39" t="n">
+        <v>0.621873424330741</v>
+      </c>
+      <c r="O597" s="21">
+        <f>IF(AND(N597&lt;0.05,OR(AND(L597="升高改善",M597&gt;0),AND(L597="降低改善",M597&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P597" s="18" t="inlineStr">
         <is>
           <t>图1“3名被试社交发起与回应行为频次变化折线图”；PDF第5页，印刷页61；从上至下第3个被试小翰面板；实心圆（发起次数）；纵轴行为次数，横轴观察次数；右侧维持期。</t>
@@ -51218,17 +52020,17 @@
       </c>
       <c r="Q597" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R597" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S597" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段五个图示点的均值与正文报告不一致，尚无法定位具体错误点，需核实完整维持序列。</t>
+          <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。图文不一致：维持期图上5点均值16.4，正文报告18.4，无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
     </row>
@@ -51263,10 +52065,24 @@
           <t>基线期 vs 干预期</t>
         </is>
       </c>
-      <c r="G598" s="22" t="n"/>
-      <c r="H598" s="23" t="n"/>
-      <c r="I598" s="22" t="n"/>
-      <c r="J598" s="23" t="n"/>
+      <c r="G598" s="22" t="inlineStr">
+        <is>
+          <t>2,2,1,1,2,1,1</t>
+        </is>
+      </c>
+      <c r="H598" s="23">
+        <f>IF(LEN(G598)=0,"",IF(ISNUMBER(SEARCH(",",G598)),LEN(SUBSTITUTE(G598,",","xx"))-LEN(G598)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I598" s="22" t="inlineStr">
+        <is>
+          <t>25,21,33,28,35,35,56,39,51,37,57,61,60,55,66,58</t>
+        </is>
+      </c>
+      <c r="J598" s="23">
+        <f>IF(LEN(I598)=0,"",IF(ISNUMBER(SEARCH(",",I598)),LEN(SUBSTITUTE(I598,",","xx"))-LEN(I598)+1,1))</f>
+        <v/>
+      </c>
       <c r="K598" s="18" t="inlineStr">
         <is>
           <t>次</t>
@@ -51277,9 +52093,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M598" s="39" t="n"/>
-      <c r="N598" s="39" t="n"/>
-      <c r="O598" s="21" t="n"/>
+      <c r="M598" s="39" t="n">
+        <v>-0.5039526306789697</v>
+      </c>
+      <c r="N598" s="39" t="n">
+        <v>0.1572992070502852</v>
+      </c>
+      <c r="O598" s="21">
+        <f>IF(AND(N598&lt;0.05,OR(AND(L598="升高改善",M598&gt;0),AND(L598="降低改善",M598&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P598" s="18" t="inlineStr">
         <is>
           <t>图1“3名被试社交发起与回应行为频次变化折线图”；PDF第5页，印刷页61；从上至下第3个被试小翰面板；实心方块（回应次数）；纵轴行为次数，横轴观察次数；基线期与干预期。</t>
@@ -51287,17 +52110,17 @@
       </c>
       <c r="Q598" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R598" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S598" s="18" t="inlineStr">
         <is>
-          <t>待审核：干预图连续显示16个观察点，正文却称缺席2次，无法确定缺失会话与图示点的对应关系。</t>
+          <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。干预期图上16点，合计717，717÷16=44.81，与正文均值44.81完全一致；正文“缺席2次”与点数的矛盾同D0595，按图取16点。</t>
         </is>
       </c>
     </row>
@@ -51332,10 +52155,24 @@
           <t>基线期 vs 维持期</t>
         </is>
       </c>
-      <c r="G599" s="22" t="n"/>
-      <c r="H599" s="23" t="n"/>
-      <c r="I599" s="22" t="n"/>
-      <c r="J599" s="23" t="n"/>
+      <c r="G599" s="22" t="inlineStr">
+        <is>
+          <t>2,2,1,1,2,1,1</t>
+        </is>
+      </c>
+      <c r="H599" s="23">
+        <f>IF(LEN(G599)=0,"",IF(ISNUMBER(SEARCH(",",G599)),LEN(SUBSTITUTE(G599,",","xx"))-LEN(G599)+1,1))</f>
+        <v/>
+      </c>
+      <c r="I599" s="22" t="inlineStr">
+        <is>
+          <t>33,40,35,38,41</t>
+        </is>
+      </c>
+      <c r="J599" s="23">
+        <f>IF(LEN(I599)=0,"",IF(ISNUMBER(SEARCH(",",I599)),LEN(SUBSTITUTE(I599,",","xx"))-LEN(I599)+1,1))</f>
+        <v/>
+      </c>
       <c r="K599" s="18" t="inlineStr">
         <is>
           <t>次</t>
@@ -51346,9 +52183,16 @@
           <t>升高改善</t>
         </is>
       </c>
-      <c r="M599" s="39" t="n"/>
-      <c r="N599" s="39" t="n"/>
-      <c r="O599" s="21" t="n"/>
+      <c r="M599" s="39" t="n">
+        <v>-0.5039526306789697</v>
+      </c>
+      <c r="N599" s="39" t="n">
+        <v>0.1572992070502852</v>
+      </c>
+      <c r="O599" s="21">
+        <f>IF(AND(N599&lt;0.05,OR(AND(L599="升高改善",M599&gt;0),AND(L599="降低改善",M599&lt;0))),"校正","不校正")</f>
+        <v/>
+      </c>
       <c r="P599" s="18" t="inlineStr">
         <is>
           <t>图1“3名被试社交发起与回应行为频次变化折线图”；PDF第5页，印刷页61；从上至下第3个被试小翰面板；实心方块（回应次数）；纵轴行为次数，横轴观察次数；右侧维持期。</t>
@@ -51356,17 +52200,17 @@
       </c>
       <c r="Q599" s="18" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="R599" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>Claude补提取</t>
         </is>
       </c>
       <c r="S599" s="18" t="inlineStr">
         <is>
-          <t>待审核：维持阶段五个图示点的均值与正文报告不一致，尚无法定位具体错误点，需核实完整维持序列。</t>
+          <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。图文不一致：维持期图上5点均值37.4，正文报告38，无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
     </row>
@@ -51385,7 +52229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -51496,6 +52340,90 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr"/>
+      <c r="B10" s="43" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>第二轮补提取（以图为准）</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>用户确定：图文数值不一致时以图为准；点数、阶段归属、被试对应不清时，按图上的数据点和阶段线取值；实在模糊、看不清的不提取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>补提取范围</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>40行：张晓敏2026 4行、013-A 2行、009-A 3行、011-A 5行、021-A 1行、025-A 2行、030-A 1行、035-A 2行、039-A 3行、036-A 4行、044-A 7行、046-A 2行、22 Mason 2014 Brian 1行、09 Gena 2006 3行。每行备注写明读图方法、正文报告的数值和差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>未提取</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>17 Kern 2006的D0531–D0533：扫描图，数据点小而密集，按“看不清就空着”不填，备注已注明。比较方式待作者确定的22行（022-A、03 Blair、24 Morrison、017-A）本轮未动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>改动比较类型的行</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>036-A的D0356、D0357、D0358原比较类型为“待审核”，按图上阶段线改为“干预”（Baseline vs VP Intervention）；维持期数值写在备注中，如需维持效应可另加行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>对GPT已填行的提示</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>D0321、D0323（035-A Emmett发起）：基线第4次按符号形状判断可能应为3而非2，只在备注中提示，数值未改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>读图方法</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>矢量图（011-A、025-A、036-A、039-A、046-A）直接读取PDF中数据符号的坐标；位图按灰度识别符号并逐像素取中心，用刻度线或刻度标签换算；重叠或被遮挡的符号用可见边缘加符号半径推算。09 Gena 2006原图分辨率低（1个单位约1.5像素），落在两个整数中间的点参照正文均值或范围取整。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
+++ b/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
@@ -46583,12 +46583,12 @@
       </c>
       <c r="R532" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>不纳入</t>
         </is>
       </c>
       <c r="S532" s="18" t="inlineStr">
         <is>
-          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -46652,12 +46652,12 @@
       </c>
       <c r="R533" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>不纳入</t>
         </is>
       </c>
       <c r="S533" s="18" t="inlineStr">
         <is>
-          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
+          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
         </is>
       </c>
     </row>
@@ -46721,12 +46721,12 @@
       </c>
       <c r="R534" s="24" t="inlineStr">
         <is>
-          <t>待审核</t>
+          <t>不纳入</t>
         </is>
       </c>
       <c r="S534" s="18" t="inlineStr">
         <is>
-          <t>【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -52229,7 +52229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52424,6 +52424,18 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Kern不纳入</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>作者决定：17 Kern 2006的D0531（Ben）、D0532（Phillip）、D0533（Lucas）三行因扫描图模糊不纳入，审核状态改为“不纳入”，数值保持空白。D0530（Eric，GPT已填）未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
+++ b/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
@@ -46583,12 +46583,12 @@
       </c>
       <c r="R532" s="24" t="inlineStr">
         <is>
-          <t>不纳入</t>
+          <t>待审核</t>
         </is>
       </c>
       <c r="S532" s="18" t="inlineStr">
         <is>
-          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -46652,12 +46652,12 @@
       </c>
       <c r="R533" s="24" t="inlineStr">
         <is>
-          <t>不纳入</t>
+          <t>待审核</t>
         </is>
       </c>
       <c r="S533" s="18" t="inlineStr">
         <is>
-          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
+          <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
         </is>
       </c>
     </row>
@@ -46721,12 +46721,12 @@
       </c>
       <c r="R534" s="24" t="inlineStr">
         <is>
-          <t>不纳入</t>
+          <t>待审核</t>
         </is>
       </c>
       <c r="S534" s="18" t="inlineStr">
         <is>
-          <t>【不纳入】作者决定：17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行不纳入Tau-U计算。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
+          <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
     </row>
@@ -52427,12 +52427,12 @@
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>Kern不纳入</t>
+          <t>Kern待审核</t>
         </is>
       </c>
       <c r="B18" s="43" t="inlineStr">
         <is>
-          <t>作者决定：17 Kern 2006的D0531（Ben）、D0532（Phillip）、D0533（Lucas）三行因扫描图模糊不纳入，审核状态改为“不纳入”，数值保持空白。D0530（Eric，GPT已填）未改动。</t>
+          <t>17 Kern 2006的D0531（Ben）、D0532（Phillip）、D0533（Lucas）三行因扫描图模糊暂不提取，审核状态为“待审核”，数值保持空白。D0530（Eric，GPT已填）未改动。</t>
         </is>
       </c>
     </row>

--- a/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
+++ b/Tau-U计算前准备数据_完整版_中英对照_网格版_Claude补提取版.xlsx
@@ -127,7 +127,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
@@ -256,6 +256,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S599"/>
+  <dimension ref="A1:U599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -626,6 +635,8 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -724,6 +735,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="T1" s="44" t="inlineStr">
+        <is>
+          <t>是否纳入计算</t>
+        </is>
+      </c>
+      <c r="U1" s="44" t="inlineStr">
+        <is>
+          <t>不纳入或待定原因</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -814,6 +835,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T2" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U2" s="45" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -904,6 +931,16 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T3" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U3" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -994,6 +1031,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T4" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U4" s="46" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1084,6 +1127,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T5" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U5" s="46" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1174,6 +1223,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T6" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U6" s="46" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1264,6 +1319,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T7" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U7" s="46" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -1351,6 +1412,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成；前段合并Baseline及Comparison内baseline条件，不合并检验基线趋势。</t>
         </is>
       </c>
+      <c r="T8" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U8" s="45" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
@@ -1438,6 +1505,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成；前段合并Baseline及Comparison内baseline条件，不合并检验基线趋势。</t>
         </is>
       </c>
+      <c r="T9" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U9" s="46" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1528,6 +1601,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T10" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U10" s="45" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1618,6 +1697,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T11" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U11" s="46" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1708,6 +1793,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T12" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U12" s="46" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1798,6 +1889,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T13" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U13" s="46" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -1888,6 +1985,12 @@
           <t>Claude补提取：从PDF内嵌图像（1760×2443像素）逐像素检测实心圆，按纵轴刻度换算；被空心点遮挡的实心点，用可见边缘加圆点半径（约12像素）反推圆心。第12、19次实心点与空心点重叠，按可见上缘推算为40、62。基线沿用D0014。</t>
         </is>
       </c>
+      <c r="T14" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U14" s="46" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1978,6 +2081,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T15" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U15" s="46" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -2068,6 +2177,12 @@
           <t>Claude补提取：从PDF内嵌图像（1760×2443像素）逐像素检测实心圆，按纵轴刻度换算；被空心点遮挡的实心点，用可见边缘加圆点半径（约12像素）反推圆心。第8、9次按可见下缘推算为29、31；第16、19次实心点完全被0处空心点覆盖，连线落在0，记0。基线沿用D0016。</t>
         </is>
       </c>
+      <c r="T16" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U16" s="46" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -2158,6 +2273,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T17" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U17" s="46" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -2248,6 +2369,12 @@
           <t>Claude补提取：从PDF内嵌图像（1760×2443像素）逐像素检测实心圆，按纵轴刻度换算；被空心点遮挡的实心点，用可见边缘加圆点半径（约12像素）反推圆心。第10、23次按可见下缘推算为22、6。基线沿用D0018。</t>
         </is>
       </c>
+      <c r="T18" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U18" s="46" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -2338,6 +2465,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T19" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U19" s="46" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -2428,6 +2561,12 @@
           <t>Claude补提取：从PDF内嵌图像（1760×2443像素）逐像素检测实心圆，按纵轴刻度换算；被空心点遮挡的实心点，用可见边缘加圆点半径（约12像素）反推圆心。第11次按可见上缘推算为45；第14次实心点被0处空心点覆盖，连线落在0，记0。基线沿用D0020。</t>
         </is>
       </c>
+      <c r="T20" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U20" s="46" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -2518,6 +2657,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T21" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U21" s="46" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -2608,6 +2753,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T22" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U22" s="45" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -2698,6 +2849,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T23" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U23" s="46" t="n"/>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2788,6 +2945,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T24" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U24" s="45" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -2878,6 +3041,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T25" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U25" s="46" t="n"/>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -2968,6 +3137,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T26" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U26" s="46" t="n"/>
     </row>
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -3058,6 +3233,12 @@
           <t>数值沿用Claude；原文名称、图位核对及基线趋势计算由GPT完成。</t>
         </is>
       </c>
+      <c r="T27" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U27" s="46" t="n"/>
     </row>
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -3148,6 +3329,12 @@
           <t>Claude补提取：从PDF内嵌高分辨率图像（6041×8449像素）检测方块中心，按纵轴11个刻度线性换算。与横轴重叠的第1、2、3、5次方块，用方块上缘加半边长（约40像素）推算中心。正文只报告三项基线均值均≤19%，与图不冲突。</t>
         </is>
       </c>
+      <c r="T28" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U28" s="46" t="n"/>
     </row>
     <row r="29" ht="27" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -3238,6 +3425,12 @@
           <t>Claude补提取：同D0027，基线与D0027相同；维持期4点直接检测方块中心。</t>
         </is>
       </c>
+      <c r="T29" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U29" s="46" t="n"/>
     </row>
     <row r="30" ht="27" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
@@ -3324,6 +3517,12 @@
         </is>
       </c>
       <c r="S30" s="13" t="n"/>
+      <c r="T30" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U30" s="45" t="n"/>
     </row>
     <row r="31" ht="27" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -3410,6 +3609,12 @@
         </is>
       </c>
       <c r="S31" s="18" t="n"/>
+      <c r="T31" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U31" s="46" t="n"/>
     </row>
     <row r="32" ht="27" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
@@ -3497,6 +3702,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T32" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U32" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="27" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
@@ -3584,6 +3799,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T33" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U33" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="27" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
@@ -3670,6 +3895,12 @@
         </is>
       </c>
       <c r="S34" s="18" t="n"/>
+      <c r="T34" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U34" s="46" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
@@ -3756,6 +3987,12 @@
         </is>
       </c>
       <c r="S35" s="18" t="n"/>
+      <c r="T35" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U35" s="46" t="n"/>
     </row>
     <row r="36" ht="27" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
@@ -3843,6 +4080,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T36" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U36" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="27" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
@@ -3930,6 +4177,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T37" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U37" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="27" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
@@ -4017,6 +4274,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T38" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U38" s="46" t="n"/>
     </row>
     <row r="39" ht="27" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
@@ -4104,6 +4367,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T39" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U39" s="46" t="n"/>
     </row>
     <row r="40" ht="27" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
@@ -4191,6 +4460,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T40" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U40" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
@@ -4278,6 +4557,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T41" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U41" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
@@ -4365,6 +4654,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T42" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U42" s="46" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
@@ -4452,6 +4747,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T43" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U43" s="46" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
@@ -4539,6 +4840,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T44" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U44" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
@@ -4626,6 +4937,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T45" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U45" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
@@ -4712,6 +5033,12 @@
         </is>
       </c>
       <c r="S46" s="18" t="n"/>
+      <c r="T46" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U46" s="46" t="n"/>
     </row>
     <row r="47" ht="27" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
@@ -4798,6 +5125,12 @@
         </is>
       </c>
       <c r="S47" s="18" t="n"/>
+      <c r="T47" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U47" s="46" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
@@ -4885,6 +5218,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T48" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U48" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
@@ -4972,6 +5315,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T49" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U49" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
@@ -5058,6 +5411,12 @@
         </is>
       </c>
       <c r="S50" s="18" t="n"/>
+      <c r="T50" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U50" s="46" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="17" t="inlineStr">
@@ -5144,6 +5503,12 @@
         </is>
       </c>
       <c r="S51" s="18" t="n"/>
+      <c r="T51" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U51" s="46" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
@@ -5231,6 +5596,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T52" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U52" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="17" t="inlineStr">
@@ -5318,6 +5693,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T53" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U53" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="27" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
@@ -5404,6 +5789,12 @@
         </is>
       </c>
       <c r="S54" s="18" t="n"/>
+      <c r="T54" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U54" s="46" t="n"/>
     </row>
     <row r="55" ht="27" customHeight="1">
       <c r="A55" s="17" t="inlineStr">
@@ -5490,6 +5881,12 @@
         </is>
       </c>
       <c r="S55" s="18" t="n"/>
+      <c r="T55" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U55" s="46" t="n"/>
     </row>
     <row r="56" ht="27" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
@@ -5577,6 +5974,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T56" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U56" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="27" customHeight="1">
       <c r="A57" s="17" t="inlineStr">
@@ -5664,6 +6071,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T57" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U57" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
@@ -5750,6 +6167,12 @@
         </is>
       </c>
       <c r="S58" s="18" t="n"/>
+      <c r="T58" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U58" s="46" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="17" t="inlineStr">
@@ -5836,6 +6259,12 @@
         </is>
       </c>
       <c r="S59" s="18" t="n"/>
+      <c r="T59" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U59" s="46" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
@@ -5923,6 +6352,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T60" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U60" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
@@ -6010,6 +6449,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T61" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U61" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="27" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
@@ -6097,6 +6546,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T62" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U62" s="46" t="n"/>
     </row>
     <row r="63" ht="27" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
@@ -6184,6 +6639,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T63" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U63" s="46" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
@@ -6271,6 +6732,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T64" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U64" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="17" t="inlineStr">
@@ -6358,6 +6829,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T65" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U65" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -6445,6 +6926,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T66" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U66" s="45" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -6532,6 +7019,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T67" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U67" s="46" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="12" t="inlineStr">
@@ -6618,6 +7111,12 @@
         </is>
       </c>
       <c r="S68" s="13" t="n"/>
+      <c r="T68" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U68" s="45" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="17" t="inlineStr">
@@ -6704,6 +7203,12 @@
         </is>
       </c>
       <c r="S69" s="18" t="n"/>
+      <c r="T69" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U69" s="46" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
@@ -6790,6 +7295,12 @@
         </is>
       </c>
       <c r="S70" s="18" t="n"/>
+      <c r="T70" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U70" s="46" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="17" t="inlineStr">
@@ -6876,6 +7387,12 @@
         </is>
       </c>
       <c r="S71" s="18" t="n"/>
+      <c r="T71" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U71" s="46" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
@@ -6962,6 +7479,12 @@
         </is>
       </c>
       <c r="S72" s="18" t="n"/>
+      <c r="T72" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U72" s="46" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="17" t="inlineStr">
@@ -7048,6 +7571,12 @@
         </is>
       </c>
       <c r="S73" s="18" t="n"/>
+      <c r="T73" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U73" s="46" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -7134,6 +7663,12 @@
         </is>
       </c>
       <c r="S74" s="3" t="n"/>
+      <c r="T74" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U74" s="45" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -7220,6 +7755,12 @@
         </is>
       </c>
       <c r="S75" s="8" t="n"/>
+      <c r="T75" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U75" s="46" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -7307,6 +7848,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T76" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U76" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -7394,6 +7945,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T77" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U77" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段1点，后段5点）</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="12" t="inlineStr">
@@ -7481,6 +8042,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T78" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U78" s="45" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="17" t="inlineStr">
@@ -7571,6 +8138,12 @@
           <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。图文不一致：维持期图上2个方块均为83%（第18、19次；与三角形部分重叠，按方块上缘推算），正文报告Regina维持75%。按图取值。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T79" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U79" s="46" t="n"/>
     </row>
     <row r="80" ht="27" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
@@ -7658,6 +8231,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T80" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U80" s="46" t="n"/>
     </row>
     <row r="81" ht="27" customHeight="1">
       <c r="A81" s="17" t="inlineStr">
@@ -7745,6 +8324,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T81" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U81" s="46" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
@@ -7835,6 +8420,12 @@
           <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。基线5次探测（第1、2、3、7、11次）均为0。干预期按矢量阶段线为第12–15次4点：58,100,100,83。图文不一致：第1个干预点图上为58%（约为7/12步），正文写60%；第15次的83%按阶段线属于干预期，而正文说“维持83%”。按图取值。</t>
         </is>
       </c>
+      <c r="T82" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U82" s="46" t="n"/>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="17" t="inlineStr">
@@ -7925,6 +8516,12 @@
           <t>Claude补提取（以图为准）：从PDF第8页内嵌原图（836×1403像素）逐像素检测实心方块（Child w/ ASD），按纵轴刻度（4像素/单位）换算；阶段线为PDF矢量叠加层，干预与维持分界位于第16、17次之间（三个面板共用）。维持期按矢量阶段线为第18、19次：92,100（第18次方块与三角形重叠，按方块上缘推算）。图文不一致：正文报告Xane维持83%，图上维持期为92、100。按图取值。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T83" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U83" s="46" t="n"/>
     </row>
     <row r="84" ht="27" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -8011,6 +8608,12 @@
         </is>
       </c>
       <c r="S84" s="3" t="n"/>
+      <c r="T84" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U84" s="45" t="n"/>
     </row>
     <row r="85" ht="27" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -8098,6 +8701,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T85" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U85" s="46" t="n"/>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -8184,6 +8793,12 @@
         </is>
       </c>
       <c r="S86" s="8" t="n"/>
+      <c r="T86" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U86" s="46" t="n"/>
     </row>
     <row r="87" ht="27" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -8270,6 +8885,12 @@
         </is>
       </c>
       <c r="S87" s="8" t="n"/>
+      <c r="T87" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U87" s="46" t="n"/>
     </row>
     <row r="88" ht="27" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -8357,6 +8978,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T88" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U88" s="46" t="n"/>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -8443,6 +9070,12 @@
         </is>
       </c>
       <c r="S89" s="8" t="n"/>
+      <c r="T89" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U89" s="46" t="n"/>
     </row>
     <row r="90" ht="27" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -8529,6 +9162,12 @@
         </is>
       </c>
       <c r="S90" s="8" t="n"/>
+      <c r="T90" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U90" s="46" t="n"/>
     </row>
     <row r="91" ht="27" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -8616,6 +9255,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T91" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U91" s="46" t="n"/>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
@@ -8702,6 +9347,12 @@
         </is>
       </c>
       <c r="S92" s="8" t="n"/>
+      <c r="T92" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U92" s="46" t="n"/>
     </row>
     <row r="93" ht="27" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -8788,6 +9439,12 @@
         </is>
       </c>
       <c r="S93" s="8" t="n"/>
+      <c r="T93" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U93" s="46" t="n"/>
     </row>
     <row r="94" ht="27" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
@@ -8875,6 +9532,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T94" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U94" s="46" t="n"/>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -8961,6 +9624,12 @@
         </is>
       </c>
       <c r="S95" s="8" t="n"/>
+      <c r="T95" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U95" s="46" t="n"/>
     </row>
     <row r="96" ht="27" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
@@ -9047,6 +9716,12 @@
         </is>
       </c>
       <c r="S96" s="8" t="n"/>
+      <c r="T96" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U96" s="46" t="n"/>
     </row>
     <row r="97" ht="27" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -9134,6 +9809,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T97" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U97" s="46" t="n"/>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
@@ -9220,6 +9901,12 @@
         </is>
       </c>
       <c r="S98" s="8" t="n"/>
+      <c r="T98" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U98" s="46" t="n"/>
     </row>
     <row r="99" ht="27" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -9307,6 +9994,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T99" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U99" s="46" t="n"/>
     </row>
     <row r="100" ht="27" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
@@ -9394,6 +10087,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T100" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U100" s="46" t="n"/>
     </row>
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -9481,6 +10180,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T101" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U101" s="46" t="n"/>
     </row>
     <row r="102" ht="27" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
@@ -9567,6 +10272,12 @@
         </is>
       </c>
       <c r="S102" s="8" t="n"/>
+      <c r="T102" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U102" s="46" t="n"/>
     </row>
     <row r="103" ht="27" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -9654,6 +10365,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T103" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U103" s="46" t="n"/>
     </row>
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
@@ -9740,6 +10457,12 @@
         </is>
       </c>
       <c r="S104" s="8" t="n"/>
+      <c r="T104" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U104" s="46" t="n"/>
     </row>
     <row r="105" ht="27" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -9826,6 +10549,12 @@
         </is>
       </c>
       <c r="S105" s="8" t="n"/>
+      <c r="T105" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U105" s="46" t="n"/>
     </row>
     <row r="106" ht="27" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
@@ -9913,6 +10642,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T106" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U106" s="46" t="n"/>
     </row>
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -9999,6 +10734,12 @@
         </is>
       </c>
       <c r="S107" s="8" t="n"/>
+      <c r="T107" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U107" s="46" t="n"/>
     </row>
     <row r="108" ht="27" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
@@ -10085,6 +10826,12 @@
         </is>
       </c>
       <c r="S108" s="8" t="n"/>
+      <c r="T108" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U108" s="46" t="n"/>
     </row>
     <row r="109" ht="27" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -10172,6 +10919,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T109" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U109" s="46" t="n"/>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
@@ -10258,6 +11011,12 @@
         </is>
       </c>
       <c r="S110" s="8" t="n"/>
+      <c r="T110" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U110" s="46" t="n"/>
     </row>
     <row r="111" ht="27" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -10345,6 +11104,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T111" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U111" s="46" t="n"/>
     </row>
     <row r="112" ht="27" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
@@ -10431,6 +11196,12 @@
         </is>
       </c>
       <c r="S112" s="8" t="n"/>
+      <c r="T112" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U112" s="46" t="n"/>
     </row>
     <row r="113" ht="27" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -10518,6 +11289,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T113" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U113" s="46" t="n"/>
     </row>
     <row r="114" ht="27" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
@@ -10604,6 +11381,12 @@
         </is>
       </c>
       <c r="S114" s="8" t="n"/>
+      <c r="T114" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U114" s="46" t="n"/>
     </row>
     <row r="115" ht="27" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -10691,6 +11474,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T115" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U115" s="46" t="n"/>
     </row>
     <row r="116" ht="27" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -10777,6 +11566,12 @@
         </is>
       </c>
       <c r="S116" s="8" t="n"/>
+      <c r="T116" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U116" s="46" t="n"/>
     </row>
     <row r="117" ht="27" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -10863,6 +11658,12 @@
         </is>
       </c>
       <c r="S117" s="8" t="n"/>
+      <c r="T117" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U117" s="46" t="n"/>
     </row>
     <row r="118" ht="27" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
@@ -10949,6 +11750,12 @@
         </is>
       </c>
       <c r="S118" s="8" t="n"/>
+      <c r="T118" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U118" s="46" t="n"/>
     </row>
     <row r="119" ht="27" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -11035,6 +11842,12 @@
         </is>
       </c>
       <c r="S119" s="8" t="n"/>
+      <c r="T119" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U119" s="46" t="n"/>
     </row>
     <row r="120" ht="27" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
@@ -11122,6 +11935,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T120" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U120" s="46" t="n"/>
     </row>
     <row r="121" ht="27" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -11208,6 +12027,12 @@
         </is>
       </c>
       <c r="S121" s="8" t="n"/>
+      <c r="T121" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U121" s="46" t="n"/>
     </row>
     <row r="122" ht="27" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
@@ -11295,6 +12120,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T122" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U122" s="46" t="n"/>
     </row>
     <row r="123" ht="27" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -11381,6 +12212,12 @@
         </is>
       </c>
       <c r="S123" s="8" t="n"/>
+      <c r="T123" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U123" s="46" t="n"/>
     </row>
     <row r="124" ht="27" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
@@ -11467,6 +12304,12 @@
         </is>
       </c>
       <c r="S124" s="8" t="n"/>
+      <c r="T124" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U124" s="46" t="n"/>
     </row>
     <row r="125" ht="27" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -11553,6 +12396,12 @@
         </is>
       </c>
       <c r="S125" s="8" t="n"/>
+      <c r="T125" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U125" s="46" t="n"/>
     </row>
     <row r="126" ht="27" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
@@ -11639,6 +12488,12 @@
         </is>
       </c>
       <c r="S126" s="8" t="n"/>
+      <c r="T126" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U126" s="46" t="n"/>
     </row>
     <row r="127" ht="27" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -11725,6 +12580,12 @@
         </is>
       </c>
       <c r="S127" s="8" t="n"/>
+      <c r="T127" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U127" s="46" t="n"/>
     </row>
     <row r="128" ht="27" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
@@ -11811,6 +12672,12 @@
         </is>
       </c>
       <c r="S128" s="8" t="n"/>
+      <c r="T128" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U128" s="46" t="n"/>
     </row>
     <row r="129" ht="27" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -11897,6 +12764,12 @@
         </is>
       </c>
       <c r="S129" s="8" t="n"/>
+      <c r="T129" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U129" s="46" t="n"/>
     </row>
     <row r="130" ht="27" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
@@ -11983,6 +12856,12 @@
         </is>
       </c>
       <c r="S130" s="8" t="n"/>
+      <c r="T130" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U130" s="46" t="n"/>
     </row>
     <row r="131" ht="27" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -12069,6 +12948,12 @@
         </is>
       </c>
       <c r="S131" s="8" t="n"/>
+      <c r="T131" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U131" s="46" t="n"/>
     </row>
     <row r="132" ht="27" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
@@ -12155,6 +13040,12 @@
         </is>
       </c>
       <c r="S132" s="8" t="n"/>
+      <c r="T132" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U132" s="46" t="n"/>
     </row>
     <row r="133" ht="27" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -12241,6 +13132,12 @@
         </is>
       </c>
       <c r="S133" s="8" t="n"/>
+      <c r="T133" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U133" s="46" t="n"/>
     </row>
     <row r="134" ht="27" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
@@ -12327,6 +13224,12 @@
         </is>
       </c>
       <c r="S134" s="8" t="n"/>
+      <c r="T134" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U134" s="46" t="n"/>
     </row>
     <row r="135" ht="27" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -12413,6 +13316,12 @@
         </is>
       </c>
       <c r="S135" s="8" t="n"/>
+      <c r="T135" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U135" s="46" t="n"/>
     </row>
     <row r="136" ht="27" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -12499,6 +13408,12 @@
         </is>
       </c>
       <c r="S136" s="8" t="n"/>
+      <c r="T136" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U136" s="46" t="n"/>
     </row>
     <row r="137" ht="27" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -12585,6 +13500,12 @@
         </is>
       </c>
       <c r="S137" s="8" t="n"/>
+      <c r="T137" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U137" s="46" t="n"/>
     </row>
     <row r="138" ht="27" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
@@ -12672,6 +13593,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T138" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U138" s="46" t="n"/>
     </row>
     <row r="139" ht="27" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -12759,6 +13686,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T139" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U139" s="46" t="n"/>
     </row>
     <row r="140" ht="27" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
@@ -12846,6 +13779,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T140" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U140" s="46" t="n"/>
     </row>
     <row r="141" ht="27" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -12932,6 +13871,12 @@
         </is>
       </c>
       <c r="S141" s="8" t="n"/>
+      <c r="T141" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U141" s="46" t="n"/>
     </row>
     <row r="142" ht="27" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
@@ -13019,6 +13964,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T142" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U142" s="46" t="n"/>
     </row>
     <row r="143" ht="27" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -13105,6 +14056,12 @@
         </is>
       </c>
       <c r="S143" s="8" t="n"/>
+      <c r="T143" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U143" s="46" t="n"/>
     </row>
     <row r="144" ht="27" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
@@ -13191,6 +14148,12 @@
         </is>
       </c>
       <c r="S144" s="8" t="n"/>
+      <c r="T144" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U144" s="46" t="n"/>
     </row>
     <row r="145" ht="27" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -13278,6 +14241,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T145" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U145" s="46" t="n"/>
     </row>
     <row r="146" ht="27" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
@@ -13364,6 +14333,12 @@
         </is>
       </c>
       <c r="S146" s="8" t="n"/>
+      <c r="T146" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U146" s="46" t="n"/>
     </row>
     <row r="147" ht="27" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -13450,6 +14425,12 @@
         </is>
       </c>
       <c r="S147" s="8" t="n"/>
+      <c r="T147" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U147" s="46" t="n"/>
     </row>
     <row r="148" ht="27" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
@@ -13536,6 +14517,12 @@
         </is>
       </c>
       <c r="S148" s="8" t="n"/>
+      <c r="T148" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U148" s="46" t="n"/>
     </row>
     <row r="149" ht="27" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -13622,6 +14609,12 @@
         </is>
       </c>
       <c r="S149" s="8" t="n"/>
+      <c r="T149" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U149" s="46" t="n"/>
     </row>
     <row r="150" ht="27" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
@@ -13708,6 +14701,12 @@
         </is>
       </c>
       <c r="S150" s="8" t="n"/>
+      <c r="T150" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U150" s="46" t="n"/>
     </row>
     <row r="151" ht="27" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -13795,6 +14794,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T151" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U151" s="46" t="n"/>
     </row>
     <row r="152" ht="27" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
@@ -13881,6 +14886,12 @@
         </is>
       </c>
       <c r="S152" s="8" t="n"/>
+      <c r="T152" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U152" s="46" t="n"/>
     </row>
     <row r="153" ht="27" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -13967,6 +14978,12 @@
         </is>
       </c>
       <c r="S153" s="8" t="n"/>
+      <c r="T153" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U153" s="46" t="n"/>
     </row>
     <row r="154" ht="27" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -14053,6 +15070,12 @@
         </is>
       </c>
       <c r="S154" s="8" t="n"/>
+      <c r="T154" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U154" s="46" t="n"/>
     </row>
     <row r="155" ht="27" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -14139,6 +15162,12 @@
         </is>
       </c>
       <c r="S155" s="8" t="n"/>
+      <c r="T155" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U155" s="46" t="n"/>
     </row>
     <row r="156" ht="36" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
@@ -14229,6 +15258,12 @@
           <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。图文不一致：基线第5点（约第11次）图上为52.4%，超出正文范围5–36%；但含此点的基线均值19.8%与正文均值20%一致，说明正文范围有误。干预8点均值52.5%、范围29.2–79.2%，与正文53%（29–79%）一致。按图取值。</t>
         </is>
       </c>
+      <c r="T156" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U156" s="45" t="n"/>
     </row>
     <row r="157" ht="36" customHeight="1">
       <c r="A157" s="17" t="inlineStr">
@@ -14319,6 +15354,12 @@
           <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。基线同D0155（基线第5点52.4%超出正文范围，见D0155）。维持探测1次8.4%，与正文8%一致。维持期只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T157" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U157" s="46" t="n"/>
     </row>
     <row r="158" ht="36" customHeight="1">
       <c r="A158" s="17" t="inlineStr">
@@ -14405,6 +15446,12 @@
         </is>
       </c>
       <c r="S158" s="18" t="n"/>
+      <c r="T158" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U158" s="46" t="n"/>
     </row>
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="17" t="inlineStr">
@@ -14491,6 +15538,12 @@
         </is>
       </c>
       <c r="S159" s="18" t="n"/>
+      <c r="T159" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U159" s="46" t="n"/>
     </row>
     <row r="160" ht="36" customHeight="1">
       <c r="A160" s="17" t="inlineStr">
@@ -14581,6 +15634,12 @@
           <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。基线5点均值60.8%、范围36.6–89.9%，与正文61%（37–90%）一致。图文不一致：干预第1点（第39次）图上为81.8%，低于正文范围85–90%；干预均值86.5%与正文86%一致。按图取值。</t>
         </is>
       </c>
+      <c r="T160" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U160" s="46" t="n"/>
     </row>
     <row r="161" ht="36" customHeight="1">
       <c r="A161" s="17" t="inlineStr">
@@ -14667,6 +15726,12 @@
         </is>
       </c>
       <c r="S161" s="18" t="n"/>
+      <c r="T161" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U161" s="46" t="n"/>
     </row>
     <row r="162" ht="36" customHeight="1">
       <c r="A162" s="17" t="inlineStr">
@@ -14753,6 +15818,12 @@
         </is>
       </c>
       <c r="S162" s="18" t="n"/>
+      <c r="T162" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U162" s="46" t="n"/>
     </row>
     <row r="163" ht="36" customHeight="1">
       <c r="A163" s="17" t="inlineStr">
@@ -14839,6 +15910,12 @@
         </is>
       </c>
       <c r="S163" s="18" t="n"/>
+      <c r="T163" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U163" s="46" t="n"/>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="17" t="inlineStr">
@@ -14929,6 +16006,12 @@
           <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。读Figure 2（PDF第8页）。图文不一致：基线均值图上61.0%、正文65%（范围0–92%与图一致）；干预均值图上52.4%，正文写22%，但正文给的范围41–65%与图一致，正文均值22%本身不在其范围内，应为正文笔误。按图取值。</t>
         </is>
       </c>
+      <c r="T164" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U164" s="46" t="n"/>
     </row>
     <row r="165" ht="36" customHeight="1">
       <c r="A165" s="17" t="inlineStr">
@@ -15019,6 +16102,12 @@
           <t>Claude补提取（以图为准）：Figure为PDF矢量图，直接读取实心圆的PDF坐标，按各面板纵轴（0%至100%）线性换算，保留1位小数；同法复核GPT已填的Aaron、Edward、James离任务数据，结果一致。读Figure 2（PDF第8页）。图文不一致：基线第2点（第22次）图上为51.6%，超出正文范围7–32%；但含此点的基线均值26.2%与正文26%一致。干预4点均值24.6%、范围7.4–38.9%，与正文25%（7.5–39%）一致。按图取值。</t>
         </is>
       </c>
+      <c r="T165" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U165" s="46" t="n"/>
     </row>
     <row r="166" ht="36" customHeight="1">
       <c r="A166" s="17" t="inlineStr">
@@ -15105,6 +16194,12 @@
         </is>
       </c>
       <c r="S166" s="18" t="n"/>
+      <c r="T166" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U166" s="46" t="n"/>
     </row>
     <row r="167" ht="36" customHeight="1">
       <c r="A167" s="17" t="inlineStr">
@@ -15191,6 +16286,12 @@
         </is>
       </c>
       <c r="S167" s="18" t="n"/>
+      <c r="T167" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U167" s="46" t="n"/>
     </row>
     <row r="168" ht="36" customHeight="1">
       <c r="A168" s="17" t="inlineStr">
@@ -15277,6 +16378,12 @@
         </is>
       </c>
       <c r="S168" s="18" t="n"/>
+      <c r="T168" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U168" s="46" t="n"/>
     </row>
     <row r="169" ht="36" customHeight="1">
       <c r="A169" s="17" t="inlineStr">
@@ -15363,6 +16470,12 @@
         </is>
       </c>
       <c r="S169" s="18" t="n"/>
+      <c r="T169" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U169" s="46" t="n"/>
     </row>
     <row r="170" ht="27" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -15453,6 +16566,12 @@
           <t>Claude补提取（以图为准）：读PDF第7页Figure 1（300 dpi渲染），逐像素检测实心圆，按纵轴刻度标签换算，读数均为整数。图上干预期8点，均值2.875，与正文/表3均值2.9、范围2–5一致；正文“8天（5次40分钟课）”的次数说法与点数不符，按图取8点。基线与D0170相同。</t>
         </is>
       </c>
+      <c r="T170" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U170" s="45" t="n"/>
     </row>
     <row r="171" ht="27" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -15543,6 +16662,12 @@
           <t>Claude补提取：读PDF第7页Figure 1（300 dpi渲染），各阶段内先后顺序清楚，Tau-U不需要会话号。基线4点与正文“6–8次，M=7”一致；维持2点与正文“每次2次，M=2”一致。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T171" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U171" s="46" t="n"/>
     </row>
     <row r="172" ht="27" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
@@ -15629,6 +16754,12 @@
         </is>
       </c>
       <c r="S172" s="8" t="n"/>
+      <c r="T172" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U172" s="46" t="n"/>
     </row>
     <row r="173" ht="27" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -15719,6 +16850,12 @@
           <t>Claude补提取：同D0170，基线沿用D0171；维持2点与正文“1–2次”一致。维持期只有2点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T173" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U173" s="46" t="n"/>
     </row>
     <row r="174" ht="27" customHeight="1">
       <c r="A174" s="7" t="inlineStr">
@@ -15809,6 +16946,12 @@
           <t>Claude补提取（以图为准）：读PDF第7页Figure 1（300 dpi渲染），逐像素检测实心圆，按纵轴刻度标签换算，读数均为整数。图上干预期7点，均值3.29，范围2–6；正文/表3报告均值3.2、范围2–6，正文写“7天8次”。点数与均值和正文略有出入，无法定位，按图取7点。基线与D0174相同。</t>
         </is>
       </c>
+      <c r="T174" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U174" s="46" t="n"/>
     </row>
     <row r="175" ht="27" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -15895,6 +17038,12 @@
         </is>
       </c>
       <c r="S175" s="8" t="n"/>
+      <c r="T175" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U175" s="46" t="n"/>
     </row>
     <row r="176" ht="27" customHeight="1">
       <c r="A176" s="12" t="inlineStr">
@@ -15985,6 +17134,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：基线Com连线只连到第4点，其后两个0值方块为Com gen探测。</t>
         </is>
       </c>
+      <c r="T176" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U176" s="45" t="n"/>
     </row>
     <row r="177" ht="27" customHeight="1">
       <c r="A177" s="17" t="inlineStr">
@@ -16075,6 +17230,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：追踪期Com连线经过3个实心方块；第3个位置的方块为空心（Com gen）。追踪期第2点处另有一个浅灰实心三角压在21的方块上，不在Play连线上，未计入，需留意。</t>
         </is>
       </c>
+      <c r="T177" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U177" s="46" t="n"/>
     </row>
     <row r="178" ht="36" customHeight="1">
       <c r="A178" s="17" t="inlineStr">
@@ -16165,6 +17326,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：基线期两次泛化探测（空心方块）均为0；干预期1次泛化探测为14。后段只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T178" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U178" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="36" customHeight="1">
       <c r="A179" s="17" t="inlineStr">
@@ -16255,6 +17426,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：追踪期两次Com gen空心方块为25、29。两段均不足3点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T179" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U179" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="36" customHeight="1">
       <c r="A180" s="17" t="inlineStr">
@@ -16345,6 +17526,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：基线第1点三角被0处方块遮住，Play连线从0起，记0。基线第3点与干预第3点、基线第4点与干预第5点在图上同高，按同值记录。</t>
         </is>
       </c>
+      <c r="T180" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U180" s="46" t="n"/>
     </row>
     <row r="181" ht="36" customHeight="1">
       <c r="A181" s="17" t="inlineStr">
@@ -16435,6 +17622,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：追踪期按Play连线取3点。基线同D0179。</t>
         </is>
       </c>
+      <c r="T181" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U181" s="46" t="n"/>
     </row>
     <row r="182" ht="36" customHeight="1">
       <c r="A182" s="17" t="inlineStr">
@@ -16525,6 +17718,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：基线期两次Play gen空心三角均为0；干预期1次为0。后段只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T182" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U182" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="36" customHeight="1">
       <c r="A183" s="17" t="inlineStr">
@@ -16615,6 +17818,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Jamie面板：追踪期1次Play gen空心三角为39。两段均不足3点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T183" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U183" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="27" customHeight="1">
       <c r="A184" s="17" t="inlineStr">
@@ -16705,6 +17918,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：基线0值空心方块为Com gen探测，未计入。</t>
         </is>
       </c>
+      <c r="T184" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U184" s="46" t="n"/>
     </row>
     <row r="185" ht="27" customHeight="1">
       <c r="A185" s="17" t="inlineStr">
@@ -16795,6 +18014,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：追踪期6个实心方块。</t>
         </is>
       </c>
+      <c r="T185" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U185" s="46" t="n"/>
     </row>
     <row r="186" ht="36" customHeight="1">
       <c r="A186" s="17" t="inlineStr">
@@ -16885,6 +18110,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：基线期两次Com gen空心方块为0、4；追踪期为4、18。两段均不足3点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T186" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U186" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="36" customHeight="1">
       <c r="A187" s="17" t="inlineStr">
@@ -16975,6 +18210,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：基线第1点三角被7处方块遮住，Play连线从7起，记7。</t>
         </is>
       </c>
+      <c r="T187" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U187" s="46" t="n"/>
     </row>
     <row r="188" ht="36" customHeight="1">
       <c r="A188" s="17" t="inlineStr">
@@ -17065,6 +18306,12 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：追踪期第1点三角被61处空心圆（PRT gen）遮住，Play连线从该点起，按圆心记61。</t>
         </is>
       </c>
+      <c r="T188" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U188" s="46" t="n"/>
     </row>
     <row r="189" ht="36" customHeight="1">
       <c r="A189" s="17" t="inlineStr">
@@ -17155,6 +18402,16 @@
           <t>Claude补提取：从PDF第4页内嵌图像（1318×2207像素）按灰度区分符号（Com深灰方块、Play浅灰三角、PRT黑灰圆），按各面板纵轴刻度标签换算。三个面板横轴缩放不一致不影响Tau-U，只按阶段线划分阶段、按阶段内先后取值。Ashley面板：基线期两次Play gen空心三角为25、18；追踪期为18、86。两段均不足3点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T189" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U189" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="27" customHeight="1">
       <c r="A190" s="17" t="inlineStr">
@@ -17241,6 +18498,12 @@
         </is>
       </c>
       <c r="S190" s="18" t="n"/>
+      <c r="T190" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U190" s="46" t="n"/>
     </row>
     <row r="191" ht="27" customHeight="1">
       <c r="A191" s="17" t="inlineStr">
@@ -17327,6 +18590,12 @@
         </is>
       </c>
       <c r="S191" s="18" t="n"/>
+      <c r="T191" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U191" s="46" t="n"/>
     </row>
     <row r="192" ht="36" customHeight="1">
       <c r="A192" s="17" t="inlineStr">
@@ -17413,6 +18682,16 @@
         </is>
       </c>
       <c r="S192" s="18" t="n"/>
+      <c r="T192" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U192" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="27" customHeight="1">
       <c r="A193" s="17" t="inlineStr">
@@ -17499,6 +18778,12 @@
         </is>
       </c>
       <c r="S193" s="18" t="n"/>
+      <c r="T193" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U193" s="46" t="n"/>
     </row>
     <row r="194" ht="27" customHeight="1">
       <c r="A194" s="17" t="inlineStr">
@@ -17585,6 +18870,12 @@
         </is>
       </c>
       <c r="S194" s="18" t="n"/>
+      <c r="T194" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U194" s="46" t="n"/>
     </row>
     <row r="195" ht="36" customHeight="1">
       <c r="A195" s="17" t="inlineStr">
@@ -17671,6 +18962,16 @@
         </is>
       </c>
       <c r="S195" s="18" t="n"/>
+      <c r="T195" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U195" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="36" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -17740,6 +19041,16 @@
           <t>待审核：每次会话同时记录改编与未改编读物的前后测，需先确定比较哪些条件，以及如何对应成对观察。</t>
         </is>
       </c>
+      <c r="T196" s="45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U196" s="45" t="inlineStr">
+        <is>
+          <t>017-A整篇剔除（作者决定）：重复习得设计，无基线期，两个条件都是教学，不适合基线对干预的Tau-U</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="36" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -17809,6 +19120,16 @@
           <t>待审核：每次会话同时记录改编与未改编读物的前后测，需先确定比较哪些条件，以及如何对应成对观察。</t>
         </is>
       </c>
+      <c r="T197" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U197" s="46" t="inlineStr">
+        <is>
+          <t>017-A整篇剔除（作者决定）：重复习得设计，无基线期，两个条件都是教学，不适合基线对干预的Tau-U</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="36" customHeight="1">
       <c r="A198" s="12" t="inlineStr">
@@ -17896,6 +19217,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T198" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U198" s="45" t="n"/>
     </row>
     <row r="199" ht="36" customHeight="1">
       <c r="A199" s="17" t="inlineStr">
@@ -17983,6 +19310,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T199" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U199" s="46" t="n"/>
     </row>
     <row r="200" ht="36" customHeight="1">
       <c r="A200" s="17" t="inlineStr">
@@ -18073,6 +19406,12 @@
           <t>Claude补提取（以图为准）：从PDF第6页内嵌原图（1900×2053像素）检测实心菱形（左纵轴，目标儿童回应百分比），按Dyad 3面板刻度（5.395像素/单位）换算。基线9次探测（第1、2、4–9、12次）均为0。图文不一致：干预第14、15次图上为26.1%、38.1%；正文报告均值70.75%、范围33.3–100%，与同伴邀请次数（3次、4次）推算的33.3%、50%相符，图上两点可能绘制有误。按图取值；两种读法下干预期均全部高于基线，Tau-U不受影响。</t>
         </is>
       </c>
+      <c r="T200" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U200" s="46" t="n"/>
     </row>
     <row r="201" ht="27" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -18159,6 +19498,12 @@
         </is>
       </c>
       <c r="S201" s="3" t="n"/>
+      <c r="T201" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U201" s="45" t="n"/>
     </row>
     <row r="202" ht="36" customHeight="1">
       <c r="A202" s="7" t="inlineStr">
@@ -18246,6 +19591,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T202" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U202" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="27" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -18332,6 +19687,12 @@
         </is>
       </c>
       <c r="S203" s="8" t="n"/>
+      <c r="T203" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U203" s="46" t="n"/>
     </row>
     <row r="204" ht="36" customHeight="1">
       <c r="A204" s="7" t="inlineStr">
@@ -18419,6 +19780,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T204" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U204" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="27" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -18505,6 +19876,12 @@
         </is>
       </c>
       <c r="S205" s="8" t="n"/>
+      <c r="T205" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U205" s="46" t="n"/>
     </row>
     <row r="206" ht="36" customHeight="1">
       <c r="A206" s="7" t="inlineStr">
@@ -18591,6 +19968,12 @@
         </is>
       </c>
       <c r="S206" s="8" t="n"/>
+      <c r="T206" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U206" s="46" t="n"/>
     </row>
     <row r="207" ht="36" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -18677,6 +20060,16 @@
         </is>
       </c>
       <c r="S207" s="8" t="n"/>
+      <c r="T207" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U207" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="27" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
@@ -18764,6 +20157,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T208" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U208" s="46" t="n"/>
     </row>
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
@@ -18851,6 +20250,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T209" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U209" s="46" t="n"/>
     </row>
     <row r="210" ht="36" customHeight="1">
       <c r="A210" s="7" t="inlineStr">
@@ -18938,6 +20343,16 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T210" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U210" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="36" customHeight="1">
       <c r="A211" s="7" t="inlineStr">
@@ -19024,6 +20439,12 @@
         </is>
       </c>
       <c r="S211" s="8" t="n"/>
+      <c r="T211" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U211" s="46" t="n"/>
     </row>
     <row r="212" ht="36" customHeight="1">
       <c r="A212" s="7" t="inlineStr">
@@ -19110,6 +20531,12 @@
         </is>
       </c>
       <c r="S212" s="8" t="n"/>
+      <c r="T212" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U212" s="46" t="n"/>
     </row>
     <row r="213" ht="36" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -19197,6 +20624,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T213" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U213" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="36" customHeight="1">
       <c r="A214" s="7" t="inlineStr">
@@ -19283,6 +20720,12 @@
         </is>
       </c>
       <c r="S214" s="8" t="n"/>
+      <c r="T214" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U214" s="46" t="n"/>
     </row>
     <row r="215" ht="48" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -19369,6 +20812,12 @@
         </is>
       </c>
       <c r="S215" s="8" t="n"/>
+      <c r="T215" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U215" s="46" t="n"/>
     </row>
     <row r="216" ht="36" customHeight="1">
       <c r="A216" s="7" t="inlineStr">
@@ -19455,6 +20904,16 @@
         </is>
       </c>
       <c r="S216" s="8" t="n"/>
+      <c r="T216" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U216" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="36" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
@@ -19541,6 +21000,12 @@
         </is>
       </c>
       <c r="S217" s="8" t="n"/>
+      <c r="T217" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U217" s="46" t="n"/>
     </row>
     <row r="218" ht="48" customHeight="1">
       <c r="A218" s="7" t="inlineStr">
@@ -19627,6 +21092,12 @@
         </is>
       </c>
       <c r="S218" s="8" t="n"/>
+      <c r="T218" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U218" s="46" t="n"/>
     </row>
     <row r="219" ht="36" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -19714,6 +21185,16 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T219" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U219" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="27" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
@@ -19800,6 +21281,12 @@
         </is>
       </c>
       <c r="S220" s="8" t="n"/>
+      <c r="T220" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U220" s="46" t="n"/>
     </row>
     <row r="221" ht="36" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
@@ -19885,6 +21372,16 @@
       <c r="S221" s="8" t="inlineStr">
         <is>
           <t>前段仅1个观察点，无法检验基线趋势。</t>
+        </is>
+      </c>
+      <c r="T221" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U221" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
         </is>
       </c>
     </row>
@@ -19952,6 +21449,16 @@
           <t>待审核：原文对不同儿童平行游戏增加或减少均作积极解释，需先确定改善方向及本行采用的阶段比较。</t>
         </is>
       </c>
+      <c r="T222" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U222" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="27" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -20038,6 +21545,12 @@
         </is>
       </c>
       <c r="S223" s="8" t="n"/>
+      <c r="T223" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U223" s="46" t="n"/>
     </row>
     <row r="224" ht="36" customHeight="1">
       <c r="A224" s="7" t="inlineStr">
@@ -20123,6 +21636,16 @@
       <c r="S224" s="8" t="inlineStr">
         <is>
           <t>前段仅1个观察点，无法检验基线趋势。</t>
+        </is>
+      </c>
+      <c r="T224" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U224" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
         </is>
       </c>
     </row>
@@ -20190,6 +21713,16 @@
           <t>待审核：原文对不同儿童平行游戏增加或减少均作积极解释，需先确定改善方向及本行采用的阶段比较。</t>
         </is>
       </c>
+      <c r="T225" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U225" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="27" customHeight="1">
       <c r="A226" s="7" t="inlineStr">
@@ -20276,6 +21809,12 @@
         </is>
       </c>
       <c r="S226" s="8" t="n"/>
+      <c r="T226" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U226" s="46" t="n"/>
     </row>
     <row r="227" ht="36" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -20362,6 +21901,12 @@
         </is>
       </c>
       <c r="S227" s="8" t="n"/>
+      <c r="T227" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U227" s="46" t="n"/>
     </row>
     <row r="228" ht="36" customHeight="1">
       <c r="A228" s="7" t="inlineStr">
@@ -20448,6 +21993,16 @@
         </is>
       </c>
       <c r="S228" s="8" t="n"/>
+      <c r="T228" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U228" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="36" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
@@ -20513,6 +22068,16 @@
           <t>待审核：原文对不同儿童平行游戏增加或减少均作积极解释，需先确定改善方向及本行采用的阶段比较。</t>
         </is>
       </c>
+      <c r="T229" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U229" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27" customHeight="1">
       <c r="A230" s="7" t="inlineStr">
@@ -20599,6 +22164,12 @@
         </is>
       </c>
       <c r="S230" s="8" t="n"/>
+      <c r="T230" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U230" s="46" t="n"/>
     </row>
     <row r="231" ht="36" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
@@ -20685,6 +22256,12 @@
         </is>
       </c>
       <c r="S231" s="8" t="n"/>
+      <c r="T231" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U231" s="46" t="n"/>
     </row>
     <row r="232" ht="36" customHeight="1">
       <c r="A232" s="7" t="inlineStr">
@@ -20750,6 +22327,16 @@
           <t>待审核：原文对不同儿童平行游戏增加或减少均作积极解释，需先确定改善方向及本行采用的阶段比较。</t>
         </is>
       </c>
+      <c r="T232" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U232" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="60" customHeight="1">
       <c r="A233" s="12" t="inlineStr">
@@ -20840,6 +22427,12 @@
           <t>Claude补提取（以图为准）：Figure 1为PDF矢量图，直接读取Murat面板数据折线顶点的PDF坐标。注意纵轴从−10开始（刻度−10,0,10,…,100），按0与100刻度线换算。基线0,6,6与土耳其文正文（第1次0%，第2、3次6%）一致；英文摘要段写基线均值2%（范围0–6%），按图均值为4%，属图文不一致，按图取值。干预8点均值77.25%，与正文77%（33–100%）一致。原先的“均值不一致”可能是把−10刻度当作0读数所致。</t>
         </is>
       </c>
+      <c r="T233" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U233" s="45" t="n"/>
     </row>
     <row r="234" ht="60" customHeight="1">
       <c r="A234" s="17" t="inlineStr">
@@ -20930,6 +22523,12 @@
           <t>Claude补提取（以图为准）：Figure 1为PDF矢量图，直接读取Murat面板数据折线顶点的PDF坐标。注意纵轴从−10开始（刻度−10,0,10,…,100），按0与100刻度线换算。基线同D0232。维持3次均为100%，与正文一致。</t>
         </is>
       </c>
+      <c r="T234" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U234" s="46" t="n"/>
     </row>
     <row r="235" ht="72" customHeight="1">
       <c r="A235" s="17" t="inlineStr">
@@ -21017,6 +22616,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T235" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U235" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="60" customHeight="1">
       <c r="A236" s="17" t="inlineStr">
@@ -21103,6 +22712,12 @@
         </is>
       </c>
       <c r="S236" s="18" t="n"/>
+      <c r="T236" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U236" s="46" t="n"/>
     </row>
     <row r="237" ht="60" customHeight="1">
       <c r="A237" s="17" t="inlineStr">
@@ -21189,6 +22804,12 @@
         </is>
       </c>
       <c r="S237" s="18" t="n"/>
+      <c r="T237" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U237" s="46" t="n"/>
     </row>
     <row r="238" ht="72" customHeight="1">
       <c r="A238" s="17" t="inlineStr">
@@ -21276,6 +22897,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T238" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U238" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="60" customHeight="1">
       <c r="A239" s="17" t="inlineStr">
@@ -21362,6 +22993,12 @@
         </is>
       </c>
       <c r="S239" s="18" t="n"/>
+      <c r="T239" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U239" s="46" t="n"/>
     </row>
     <row r="240" ht="60" customHeight="1">
       <c r="A240" s="17" t="inlineStr">
@@ -21448,6 +23085,12 @@
         </is>
       </c>
       <c r="S240" s="18" t="n"/>
+      <c r="T240" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U240" s="46" t="n"/>
     </row>
     <row r="241" ht="60" customHeight="1">
       <c r="A241" s="17" t="inlineStr">
@@ -21535,6 +23178,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T241" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U241" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="60" customHeight="1">
       <c r="A242" s="17" t="inlineStr">
@@ -21622,6 +23275,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T242" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U242" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="60" customHeight="1">
       <c r="A243" s="17" t="inlineStr">
@@ -21709,6 +23372,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T243" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U243" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="60" customHeight="1">
       <c r="A244" s="17" t="inlineStr">
@@ -21796,6 +23469,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T244" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U244" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="60" customHeight="1">
       <c r="A245" s="17" t="inlineStr">
@@ -21883,6 +23566,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T245" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U245" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="60" customHeight="1">
       <c r="A246" s="17" t="inlineStr">
@@ -21970,6 +23663,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T246" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U246" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="60" customHeight="1">
       <c r="A247" s="17" t="inlineStr">
@@ -22057,6 +23760,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T247" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U247" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="60" customHeight="1">
       <c r="A248" s="17" t="inlineStr">
@@ -22144,6 +23857,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T248" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U248" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="60" customHeight="1">
       <c r="A249" s="17" t="inlineStr">
@@ -22231,6 +23954,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T249" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U249" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="60" customHeight="1">
       <c r="A250" s="17" t="inlineStr">
@@ -22318,6 +24051,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T250" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U250" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="60" customHeight="1">
       <c r="A251" s="17" t="inlineStr">
@@ -22405,6 +24148,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T251" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U251" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="60" customHeight="1">
       <c r="A252" s="17" t="inlineStr">
@@ -22492,6 +24245,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T252" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U252" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="60" customHeight="1">
       <c r="A253" s="17" t="inlineStr">
@@ -22579,6 +24342,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T253" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U253" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="60" customHeight="1">
       <c r="A254" s="17" t="inlineStr">
@@ -22666,6 +24439,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T254" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U254" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="60" customHeight="1">
       <c r="A255" s="17" t="inlineStr">
@@ -22753,6 +24536,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T255" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U255" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="60" customHeight="1">
       <c r="A256" s="17" t="inlineStr">
@@ -22840,6 +24633,16 @@
           <t>【建议剔除】这是孤独症儿童对同组普通同伴目标职业的“观察学习”前测、后测各1次，不是本研究的目标技能，也不是单一被试设计的阶段比较，前后各1点无法计算有意义的Tau-U，属误用。　原备注：前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T256" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U256" s="46" t="inlineStr">
+        <is>
+          <t>观察学习单次前测与后测各1点，不是本研究目标技能，也不是阶段比较（GPT误用）</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="36" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
@@ -22926,6 +24729,12 @@
         </is>
       </c>
       <c r="S257" s="3" t="n"/>
+      <c r="T257" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U257" s="45" t="n"/>
     </row>
     <row r="258" ht="36" customHeight="1">
       <c r="A258" s="7" t="inlineStr">
@@ -23012,6 +24821,12 @@
         </is>
       </c>
       <c r="S258" s="8" t="n"/>
+      <c r="T258" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U258" s="46" t="n"/>
     </row>
     <row r="259" ht="36" customHeight="1">
       <c r="A259" s="7" t="inlineStr">
@@ -23098,6 +24913,12 @@
         </is>
       </c>
       <c r="S259" s="8" t="n"/>
+      <c r="T259" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U259" s="46" t="n"/>
     </row>
     <row r="260" ht="36" customHeight="1">
       <c r="A260" s="7" t="inlineStr">
@@ -23184,6 +25005,12 @@
         </is>
       </c>
       <c r="S260" s="8" t="n"/>
+      <c r="T260" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U260" s="46" t="n"/>
     </row>
     <row r="261" ht="36" customHeight="1">
       <c r="A261" s="7" t="inlineStr">
@@ -23270,6 +25097,12 @@
         </is>
       </c>
       <c r="S261" s="8" t="n"/>
+      <c r="T261" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U261" s="46" t="n"/>
     </row>
     <row r="262" ht="36" customHeight="1">
       <c r="A262" s="7" t="inlineStr">
@@ -23356,6 +25189,12 @@
         </is>
       </c>
       <c r="S262" s="8" t="n"/>
+      <c r="T262" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U262" s="46" t="n"/>
     </row>
     <row r="263" ht="36" customHeight="1">
       <c r="A263" s="7" t="inlineStr">
@@ -23442,6 +25281,12 @@
         </is>
       </c>
       <c r="S263" s="8" t="n"/>
+      <c r="T263" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U263" s="46" t="n"/>
     </row>
     <row r="264" ht="36" customHeight="1">
       <c r="A264" s="7" t="inlineStr">
@@ -23528,6 +25373,12 @@
         </is>
       </c>
       <c r="S264" s="8" t="n"/>
+      <c r="T264" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U264" s="46" t="n"/>
     </row>
     <row r="265" ht="36" customHeight="1">
       <c r="A265" s="7" t="inlineStr">
@@ -23614,6 +25465,12 @@
         </is>
       </c>
       <c r="S265" s="8" t="n"/>
+      <c r="T265" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U265" s="46" t="n"/>
     </row>
     <row r="266" ht="36" customHeight="1">
       <c r="A266" s="7" t="inlineStr">
@@ -23700,6 +25557,12 @@
         </is>
       </c>
       <c r="S266" s="8" t="n"/>
+      <c r="T266" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U266" s="46" t="n"/>
     </row>
     <row r="267" ht="36" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -23786,6 +25649,12 @@
         </is>
       </c>
       <c r="S267" s="8" t="n"/>
+      <c r="T267" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U267" s="46" t="n"/>
     </row>
     <row r="268" ht="36" customHeight="1">
       <c r="A268" s="7" t="inlineStr">
@@ -23872,6 +25741,12 @@
         </is>
       </c>
       <c r="S268" s="8" t="n"/>
+      <c r="T268" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U268" s="46" t="n"/>
     </row>
     <row r="269" ht="27" customHeight="1">
       <c r="A269" s="12" t="inlineStr">
@@ -23958,6 +25833,12 @@
         </is>
       </c>
       <c r="S269" s="13" t="n"/>
+      <c r="T269" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U269" s="45" t="n"/>
     </row>
     <row r="270" ht="27" customHeight="1">
       <c r="A270" s="17" t="inlineStr">
@@ -24044,6 +25925,12 @@
         </is>
       </c>
       <c r="S270" s="18" t="n"/>
+      <c r="T270" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U270" s="46" t="n"/>
     </row>
     <row r="271" ht="27" customHeight="1">
       <c r="A271" s="17" t="inlineStr">
@@ -24130,6 +26017,12 @@
         </is>
       </c>
       <c r="S271" s="18" t="n"/>
+      <c r="T271" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U271" s="46" t="n"/>
     </row>
     <row r="272" ht="27" customHeight="1">
       <c r="A272" s="17" t="inlineStr">
@@ -24216,6 +26109,12 @@
         </is>
       </c>
       <c r="S272" s="18" t="n"/>
+      <c r="T272" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U272" s="46" t="n"/>
     </row>
     <row r="273" ht="36" customHeight="1">
       <c r="A273" s="17" t="inlineStr">
@@ -24302,6 +26201,12 @@
         </is>
       </c>
       <c r="S273" s="18" t="n"/>
+      <c r="T273" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U273" s="46" t="n"/>
     </row>
     <row r="274" ht="36" customHeight="1">
       <c r="A274" s="17" t="inlineStr">
@@ -24388,6 +26293,12 @@
         </is>
       </c>
       <c r="S274" s="18" t="n"/>
+      <c r="T274" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U274" s="46" t="n"/>
     </row>
     <row r="275" ht="36" customHeight="1">
       <c r="A275" s="17" t="inlineStr">
@@ -24475,6 +26386,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T275" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U275" s="46" t="n"/>
     </row>
     <row r="276" ht="36" customHeight="1">
       <c r="A276" s="17" t="inlineStr">
@@ -24562,6 +26479,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T276" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U276" s="46" t="n"/>
     </row>
     <row r="277" ht="36" customHeight="1">
       <c r="A277" s="17" t="inlineStr">
@@ -24649,6 +26572,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T277" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U277" s="46" t="n"/>
     </row>
     <row r="278" ht="36" customHeight="1">
       <c r="A278" s="17" t="inlineStr">
@@ -24736,6 +26665,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T278" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U278" s="46" t="n"/>
     </row>
     <row r="279" ht="36" customHeight="1">
       <c r="A279" s="17" t="inlineStr">
@@ -24822,6 +26757,12 @@
         </is>
       </c>
       <c r="S279" s="18" t="n"/>
+      <c r="T279" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U279" s="46" t="n"/>
     </row>
     <row r="280" ht="36" customHeight="1">
       <c r="A280" s="17" t="inlineStr">
@@ -24908,6 +26849,12 @@
         </is>
       </c>
       <c r="S280" s="18" t="n"/>
+      <c r="T280" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U280" s="46" t="n"/>
     </row>
     <row r="281" ht="48" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -24994,6 +26941,12 @@
         </is>
       </c>
       <c r="S281" s="3" t="n"/>
+      <c r="T281" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U281" s="45" t="n"/>
     </row>
     <row r="282" ht="48" customHeight="1">
       <c r="A282" s="7" t="inlineStr">
@@ -25080,6 +27033,12 @@
         </is>
       </c>
       <c r="S282" s="8" t="n"/>
+      <c r="T282" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U282" s="46" t="n"/>
     </row>
     <row r="283" ht="48" customHeight="1">
       <c r="A283" s="7" t="inlineStr">
@@ -25166,6 +27125,12 @@
         </is>
       </c>
       <c r="S283" s="8" t="n"/>
+      <c r="T283" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U283" s="46" t="n"/>
     </row>
     <row r="284" ht="48" customHeight="1">
       <c r="A284" s="12" t="inlineStr">
@@ -25253,6 +27218,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T284" s="45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U284" s="45" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="48" customHeight="1">
       <c r="A285" s="17" t="inlineStr">
@@ -25340,6 +27315,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T285" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U285" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="48" customHeight="1">
       <c r="A286" s="17" t="inlineStr">
@@ -25427,6 +27412,12 @@
           <t>前段为Post-Training，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T286" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U286" s="46" t="n"/>
     </row>
     <row r="287" ht="48" customHeight="1">
       <c r="A287" s="17" t="inlineStr">
@@ -25514,6 +27505,12 @@
           <t>前段为Post-Training，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T287" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U287" s="46" t="n"/>
     </row>
     <row r="288" ht="48" customHeight="1">
       <c r="A288" s="17" t="inlineStr">
@@ -25601,6 +27598,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T288" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U288" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="48" customHeight="1">
       <c r="A289" s="17" t="inlineStr">
@@ -25688,6 +27695,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T289" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U289" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="48" customHeight="1">
       <c r="A290" s="17" t="inlineStr">
@@ -25775,6 +27792,12 @@
           <t>前段为Post-Training，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T290" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U290" s="46" t="n"/>
     </row>
     <row r="291" ht="48" customHeight="1">
       <c r="A291" s="17" t="inlineStr">
@@ -25861,6 +27884,12 @@
           <t>Claude补提取（以图为准）：从PDF第18页内嵌原图（1456×2825像素）检测Child 3面板实心菱形，按该面板0与100位置换算。前段与D0289相同（Post-Training阶段，按一览表约定作为对照段）。维持期为第37、40、42、45、48次5点：90,75,80,80,80，均值81%，与正文M=81%一致；正文范围写60–100%，图上为75–90%，属图文不一致，按图取值。第34、39次圆点为泛化探测，未计入。前段为Post-Training，与同组D0285–D0289保持一致，暂不检验基线趋势（τ、p留空）；是否对030-A的前段做趋势检验待作者确定（如做，此行τ=0.767、p=0.001，需校正）。</t>
         </is>
       </c>
+      <c r="T291" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U291" s="46" t="n"/>
     </row>
     <row r="292" ht="48" customHeight="1">
       <c r="A292" s="17" t="inlineStr">
@@ -25948,6 +27977,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T292" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U292" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="48" customHeight="1">
       <c r="A293" s="17" t="inlineStr">
@@ -26035,6 +28074,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T293" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U293" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="48" customHeight="1">
       <c r="A294" s="17" t="inlineStr">
@@ -26122,6 +28171,12 @@
           <t>前段为Post-Training，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T294" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U294" s="46" t="n"/>
     </row>
     <row r="295" ht="48" customHeight="1">
       <c r="A295" s="17" t="inlineStr">
@@ -26209,6 +28264,12 @@
           <t>前段为Post-Training，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T295" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U295" s="46" t="n"/>
     </row>
     <row r="296" ht="48" customHeight="1">
       <c r="A296" s="17" t="inlineStr">
@@ -26296,6 +28357,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T296" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U296" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="48" customHeight="1">
       <c r="A297" s="17" t="inlineStr">
@@ -26383,6 +28454,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T297" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U297" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="48" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
@@ -26469,6 +28550,12 @@
         </is>
       </c>
       <c r="S298" s="3" t="n"/>
+      <c r="T298" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U298" s="45" t="n"/>
     </row>
     <row r="299" ht="48" customHeight="1">
       <c r="A299" s="7" t="inlineStr">
@@ -26556,6 +28643,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T299" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U299" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段1点，后段4点）</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="48" customHeight="1">
       <c r="A300" s="7" t="inlineStr">
@@ -26642,6 +28739,12 @@
         </is>
       </c>
       <c r="S300" s="8" t="n"/>
+      <c r="T300" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U300" s="46" t="n"/>
     </row>
     <row r="301" ht="48" customHeight="1">
       <c r="A301" s="7" t="inlineStr">
@@ -26728,6 +28831,12 @@
         </is>
       </c>
       <c r="S301" s="8" t="n"/>
+      <c r="T301" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U301" s="46" t="n"/>
     </row>
     <row r="302" ht="48" customHeight="1">
       <c r="A302" s="7" t="inlineStr">
@@ -26815,6 +28924,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T302" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U302" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段1点，后段3点）</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="48" customHeight="1">
       <c r="A303" s="7" t="inlineStr">
@@ -26901,6 +29020,12 @@
         </is>
       </c>
       <c r="S303" s="8" t="n"/>
+      <c r="T303" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U303" s="46" t="n"/>
     </row>
     <row r="304" ht="48" customHeight="1">
       <c r="A304" s="7" t="inlineStr">
@@ -26988,6 +29113,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T304" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U304" s="46" t="n"/>
     </row>
     <row r="305" ht="48" customHeight="1">
       <c r="A305" s="7" t="inlineStr">
@@ -27075,6 +29206,16 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T305" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U305" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段2点，后段3点）</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="48" customHeight="1">
       <c r="A306" s="7" t="inlineStr">
@@ -27162,6 +29303,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T306" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U306" s="46" t="n"/>
     </row>
     <row r="307" ht="48" customHeight="1">
       <c r="A307" s="7" t="inlineStr">
@@ -27248,6 +29395,12 @@
         </is>
       </c>
       <c r="S307" s="8" t="n"/>
+      <c r="T307" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U307" s="46" t="n"/>
     </row>
     <row r="308" ht="48" customHeight="1">
       <c r="A308" s="7" t="inlineStr">
@@ -27335,6 +29488,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T308" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U308" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段1点，后段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="48" customHeight="1">
       <c r="A309" s="7" t="inlineStr">
@@ -27421,6 +29584,12 @@
         </is>
       </c>
       <c r="S309" s="8" t="n"/>
+      <c r="T309" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U309" s="46" t="n"/>
     </row>
     <row r="310" ht="60" customHeight="1">
       <c r="A310" s="7" t="inlineStr">
@@ -27507,6 +29676,12 @@
         </is>
       </c>
       <c r="S310" s="8" t="n"/>
+      <c r="T310" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U310" s="46" t="n"/>
     </row>
     <row r="311" ht="60" customHeight="1">
       <c r="A311" s="7" t="inlineStr">
@@ -27593,6 +29768,12 @@
         </is>
       </c>
       <c r="S311" s="8" t="n"/>
+      <c r="T311" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U311" s="46" t="n"/>
     </row>
     <row r="312" ht="48" customHeight="1">
       <c r="A312" s="7" t="inlineStr">
@@ -27679,6 +29860,12 @@
         </is>
       </c>
       <c r="S312" s="8" t="n"/>
+      <c r="T312" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U312" s="46" t="n"/>
     </row>
     <row r="313" ht="60" customHeight="1">
       <c r="A313" s="7" t="inlineStr">
@@ -27766,6 +29953,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T313" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U313" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="60" customHeight="1">
       <c r="A314" s="7" t="inlineStr">
@@ -27853,6 +30050,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T314" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U314" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="48" customHeight="1">
       <c r="A315" s="7" t="inlineStr">
@@ -27940,6 +30147,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T315" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U315" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="60" customHeight="1">
       <c r="A316" s="7" t="inlineStr">
@@ -28026,6 +30243,12 @@
         </is>
       </c>
       <c r="S316" s="8" t="n"/>
+      <c r="T316" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U316" s="46" t="n"/>
     </row>
     <row r="317" ht="60" customHeight="1">
       <c r="A317" s="7" t="inlineStr">
@@ -28113,6 +30336,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T317" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U317" s="46" t="n"/>
     </row>
     <row r="318" ht="48" customHeight="1">
       <c r="A318" s="7" t="inlineStr">
@@ -28199,6 +30428,12 @@
         </is>
       </c>
       <c r="S318" s="8" t="n"/>
+      <c r="T318" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U318" s="46" t="n"/>
     </row>
     <row r="319" ht="60" customHeight="1">
       <c r="A319" s="7" t="inlineStr">
@@ -28286,6 +30521,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T319" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U319" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="60" customHeight="1">
       <c r="A320" s="7" t="inlineStr">
@@ -28373,6 +30618,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T320" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U320" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="48" customHeight="1">
       <c r="A321" s="7" t="inlineStr">
@@ -28460,6 +30715,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T321" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U321" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="60" customHeight="1">
       <c r="A322" s="7" t="inlineStr">
@@ -28550,6 +30815,12 @@
           <t>【Claude复核提示】基线第4次实心圆按矢量形状判断应为3（GPT记为2）：该处圆在上、方块在下，方块为回应=2。按3计，两次基线的发起均值为0.82，按2计为0.73，正文报告0.9（0–3）。建议核对，数值未改。</t>
         </is>
       </c>
+      <c r="T322" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U322" s="46" t="n"/>
     </row>
     <row r="323" ht="60" customHeight="1">
       <c r="A323" s="7" t="inlineStr">
@@ -28636,6 +30907,12 @@
         </is>
       </c>
       <c r="S323" s="8" t="n"/>
+      <c r="T323" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U323" s="46" t="n"/>
     </row>
     <row r="324" ht="48" customHeight="1">
       <c r="A324" s="7" t="inlineStr">
@@ -28726,6 +31003,12 @@
           <t>【Claude复核提示】基线第4次发起值同D0321，可能应为3而非2，建议核对，数值未改。</t>
         </is>
       </c>
+      <c r="T324" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U324" s="46" t="n"/>
     </row>
     <row r="325" ht="60" customHeight="1">
       <c r="A325" s="7" t="inlineStr">
@@ -28813,6 +31096,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T325" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U325" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="60" customHeight="1">
       <c r="A326" s="7" t="inlineStr">
@@ -28900,6 +31193,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T326" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U326" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="48" customHeight="1">
       <c r="A327" s="7" t="inlineStr">
@@ -28987,6 +31290,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T327" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U327" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="60" customHeight="1">
       <c r="A328" s="7" t="inlineStr">
@@ -29077,6 +31390,12 @@
           <t>Claude补提取（以图为准）：从PDF第9页内嵌原图（1070×1290像素）逐像素检测Emmett面板的实心方块（社交回应），纵轴按PDF中刻度标签位置换算（5.75像素/单位）。第一次基线8点（第1–4、6–9次；第5次为空心泛化探测，未计入）。第4次两个符号重叠：上方为圆（发起=3），下方为方块（回应=2），按形状区分。由此回应基线范围0–2，与正文“0.4次（0–2）”一致，原先所说的“超出正文范围”是把两个符号认反了。第一次干预期7点（第14、17次为泛化探测，未计入），第13次方块与圆重叠，按方块下缘推算为5；与第二次干预期合计14点均值18.0，与正文“18次（5–44）”一致。</t>
         </is>
       </c>
+      <c r="T328" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U328" s="46" t="n"/>
     </row>
     <row r="329" ht="60" customHeight="1">
       <c r="A329" s="7" t="inlineStr">
@@ -29163,6 +31482,12 @@
         </is>
       </c>
       <c r="S329" s="8" t="n"/>
+      <c r="T329" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U329" s="46" t="n"/>
     </row>
     <row r="330" ht="48" customHeight="1">
       <c r="A330" s="7" t="inlineStr">
@@ -29253,6 +31578,12 @@
           <t>Claude补提取（以图为准）：从PDF第9页内嵌原图（1070×1290像素）逐像素检测Emmett面板的实心方块（社交回应），纵轴按PDF中刻度标签位置换算（5.75像素/单位）。基线同D0327。6周追踪的常规会话最右侧实心方块与实心圆重叠，按方块上缘推算为10（圆为9）；与新同伴的泛化追踪为18，两者均值14、范围10–18，与正文一致。追踪只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T330" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U330" s="46" t="n"/>
     </row>
     <row r="331" ht="60" customHeight="1">
       <c r="A331" s="7" t="inlineStr">
@@ -29340,6 +31671,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T331" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U331" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="60" customHeight="1">
       <c r="A332" s="7" t="inlineStr">
@@ -29427,6 +31768,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T332" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U332" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="48" customHeight="1">
       <c r="A333" s="7" t="inlineStr">
@@ -29514,6 +31865,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T333" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U333" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="60" customHeight="1">
       <c r="A334" s="7" t="inlineStr">
@@ -29601,6 +31962,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T334" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U334" s="46" t="n"/>
     </row>
     <row r="335" ht="60" customHeight="1">
       <c r="A335" s="7" t="inlineStr">
@@ -29688,6 +32055,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T335" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U335" s="46" t="n"/>
     </row>
     <row r="336" ht="48" customHeight="1">
       <c r="A336" s="7" t="inlineStr">
@@ -29775,6 +32148,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T336" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U336" s="46" t="n"/>
     </row>
     <row r="337" ht="60" customHeight="1">
       <c r="A337" s="7" t="inlineStr">
@@ -29862,6 +32241,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T337" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U337" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="60" customHeight="1">
       <c r="A338" s="7" t="inlineStr">
@@ -29949,6 +32338,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T338" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U338" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="60" customHeight="1">
       <c r="A339" s="7" t="inlineStr">
@@ -30036,6 +32435,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T339" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U339" s="46" t="n"/>
     </row>
     <row r="340" ht="60" customHeight="1">
       <c r="A340" s="7" t="inlineStr">
@@ -30123,6 +32528,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T340" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U340" s="46" t="n"/>
     </row>
     <row r="341" ht="48" customHeight="1">
       <c r="A341" s="7" t="inlineStr">
@@ -30210,6 +32621,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T341" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U341" s="46" t="n"/>
     </row>
     <row r="342" ht="60" customHeight="1">
       <c r="A342" s="7" t="inlineStr">
@@ -30297,6 +32714,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T342" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U342" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="60" customHeight="1">
       <c r="A343" s="7" t="inlineStr">
@@ -30384,6 +32811,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T343" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U343" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="48" customHeight="1">
       <c r="A344" s="7" t="inlineStr">
@@ -30471,6 +32908,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T344" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U344" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="60" customHeight="1">
       <c r="A345" s="7" t="inlineStr">
@@ -30558,6 +33005,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T345" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U345" s="46" t="n"/>
     </row>
     <row r="346" ht="60" customHeight="1">
       <c r="A346" s="7" t="inlineStr">
@@ -30645,6 +33098,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T346" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U346" s="46" t="n"/>
     </row>
     <row r="347" ht="48" customHeight="1">
       <c r="A347" s="7" t="inlineStr">
@@ -30732,6 +33191,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T347" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U347" s="46" t="n"/>
     </row>
     <row r="348" ht="60" customHeight="1">
       <c r="A348" s="7" t="inlineStr">
@@ -30819,6 +33284,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T348" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U348" s="46" t="n"/>
     </row>
     <row r="349" ht="60" customHeight="1">
       <c r="A349" s="7" t="inlineStr">
@@ -30906,6 +33377,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T349" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U349" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="48" customHeight="1">
       <c r="A350" s="7" t="inlineStr">
@@ -30993,6 +33474,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T350" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U350" s="46" t="n"/>
     </row>
     <row r="351" ht="60" customHeight="1">
       <c r="A351" s="7" t="inlineStr">
@@ -31080,6 +33567,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T351" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U351" s="46" t="n"/>
     </row>
     <row r="352" ht="60" customHeight="1">
       <c r="A352" s="7" t="inlineStr">
@@ -31167,6 +33660,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T352" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U352" s="46" t="n"/>
     </row>
     <row r="353" ht="48" customHeight="1">
       <c r="A353" s="7" t="inlineStr">
@@ -31254,6 +33753,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T353" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U353" s="46" t="n"/>
     </row>
     <row r="354" ht="60" customHeight="1">
       <c r="A354" s="7" t="inlineStr">
@@ -31341,6 +33846,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T354" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U354" s="46" t="n"/>
     </row>
     <row r="355" ht="60" customHeight="1">
       <c r="A355" s="7" t="inlineStr">
@@ -31428,6 +33939,16 @@
           <t>前段仅1个观察点，无法检验基线趋势。</t>
         </is>
       </c>
+      <c r="T355" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U355" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="48" customHeight="1">
       <c r="A356" s="7" t="inlineStr">
@@ -31515,6 +34036,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T356" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U356" s="46" t="n"/>
     </row>
     <row r="357" ht="48" customHeight="1">
       <c r="A357" s="12" t="inlineStr">
@@ -31605,6 +34132,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mallory技能1：基线6点均值25.5%，与正文25.5%（10–33%）一致。图文不一致：图上虚线把干预分为6点、维持5点（80,90,100,95,100）；正文干预均值82.78%正是图上干预6点加维持前3点共9点的均值，维持“95–100%”对应最后2点，说明正文的阶段划分与图不同。按图取干预6点。原比较类型“待审核”改为干预比较；如需维持效应，可另加一行：基线 vs 维持80,90,100,95,100。</t>
         </is>
       </c>
+      <c r="T357" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U357" s="45" t="n"/>
     </row>
     <row r="358" ht="48" customHeight="1">
       <c r="A358" s="17" t="inlineStr">
@@ -31695,6 +34228,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mallory技能2：基线8点（空心方块为泛化探测，未计入），均值23.75%，正文21.22%（0–40%）。干预4点均值80%，正文84%（60–100%），正文均值与图上干预4点加维持第1点共5点的均值一致；横轴未标会话号，不影响Tau-U。图文不一致，按图取值。原比较类型“待审核”改为干预比较；维持期图上为100,100（另1个空心方块60%为泛化探测）。</t>
         </is>
       </c>
+      <c r="T358" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U358" s="46" t="n"/>
     </row>
     <row r="359" ht="48" customHeight="1">
       <c r="A359" s="17" t="inlineStr">
@@ -31785,6 +34324,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mateo技能1：基线9点均为0；干预5点均值74%，与正文74%（10–100%）一致。图文不一致：正文基线均值1%（范围0–10%），图上基线全为0；正文称未测维持，但图上虚线后有2点（100,90，均值95%，与结果段“维持95%”一致）。按图取值。原比较类型“待审核”改为干预比较；如需维持效应，可另加一行：基线 vs 维持100,90。</t>
         </is>
       </c>
+      <c r="T359" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U359" s="46" t="n"/>
     </row>
     <row r="360" ht="48" customHeight="1">
       <c r="A360" s="17" t="inlineStr">
@@ -31875,6 +34420,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取实心圆的PDF坐标，按各面板纵轴刻度线（0与100）换算后取整；阶段按图上的实线（基线→视频提示）和虚线（视频提示→维持）划分。Mateo技能2：基线10点（横轴未标会话号，只按先后取值），均值6.4%；正文基线均值7.9%（0–40%），图文不一致，无法定位，按图取值。干预4点：图上第1点约31%，正文干预均值52.5%（30–60%）对应第1点为30%，差1个百分点，不影响Tau-U。</t>
         </is>
       </c>
+      <c r="T360" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U360" s="46" t="n"/>
     </row>
     <row r="361" ht="48" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
@@ -31961,6 +34512,12 @@
         </is>
       </c>
       <c r="S361" s="3" t="n"/>
+      <c r="T361" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U361" s="45" t="n"/>
     </row>
     <row r="362" ht="48" customHeight="1">
       <c r="A362" s="7" t="inlineStr">
@@ -32048,6 +34605,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T362" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U362" s="46" t="n"/>
     </row>
     <row r="363" ht="48" customHeight="1">
       <c r="A363" s="7" t="inlineStr">
@@ -32134,6 +34697,12 @@
         </is>
       </c>
       <c r="S363" s="8" t="n"/>
+      <c r="T363" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U363" s="46" t="n"/>
     </row>
     <row r="364" ht="48" customHeight="1">
       <c r="A364" s="7" t="inlineStr">
@@ -32221,6 +34790,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T364" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U364" s="46" t="n"/>
     </row>
     <row r="365" ht="48" customHeight="1">
       <c r="A365" s="7" t="inlineStr">
@@ -32307,6 +34882,12 @@
         </is>
       </c>
       <c r="S365" s="8" t="n"/>
+      <c r="T365" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U365" s="46" t="n"/>
     </row>
     <row r="366" ht="48" customHeight="1">
       <c r="A366" s="7" t="inlineStr">
@@ -32394,6 +34975,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T366" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U366" s="46" t="n"/>
     </row>
     <row r="367" ht="48" customHeight="1">
       <c r="A367" s="7" t="inlineStr">
@@ -32480,6 +35067,12 @@
         </is>
       </c>
       <c r="S367" s="8" t="n"/>
+      <c r="T367" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U367" s="46" t="n"/>
     </row>
     <row r="368" ht="48" customHeight="1">
       <c r="A368" s="7" t="inlineStr">
@@ -32566,6 +35159,12 @@
         </is>
       </c>
       <c r="S368" s="8" t="n"/>
+      <c r="T368" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U368" s="46" t="n"/>
     </row>
     <row r="369" ht="48" customHeight="1">
       <c r="A369" s="7" t="inlineStr">
@@ -32652,6 +35251,12 @@
         </is>
       </c>
       <c r="S369" s="8" t="n"/>
+      <c r="T369" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U369" s="46" t="n"/>
     </row>
     <row r="370" ht="48" customHeight="1">
       <c r="A370" s="7" t="inlineStr">
@@ -32738,6 +35343,12 @@
         </is>
       </c>
       <c r="S370" s="8" t="n"/>
+      <c r="T370" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U370" s="46" t="n"/>
     </row>
     <row r="371" ht="48" customHeight="1">
       <c r="A371" s="7" t="inlineStr">
@@ -32824,6 +35435,12 @@
         </is>
       </c>
       <c r="S371" s="8" t="n"/>
+      <c r="T371" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U371" s="46" t="n"/>
     </row>
     <row r="372" ht="72" customHeight="1">
       <c r="A372" s="12" t="inlineStr">
@@ -32911,6 +35528,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T372" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U372" s="45" t="n"/>
     </row>
     <row r="373" ht="72" customHeight="1">
       <c r="A373" s="17" t="inlineStr">
@@ -33001,6 +35624,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。基线6点与D0371相同。维持期实心方块为第17、21、25、29、33次：12,20,11,6,20（第33次方块上叠了一个无边框白色圆点，渲染后像空心方块，矢量数据显示为实心方块）。图文不一致：正文报告维持范围9–16，图上为6–20；同图Bryan的数据也与正文范围不符，判断为正文问题，按图取值。</t>
         </is>
       </c>
+      <c r="T373" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U373" s="46" t="n"/>
     </row>
     <row r="374" ht="72" customHeight="1">
       <c r="A374" s="17" t="inlineStr">
@@ -33091,6 +35720,16 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。泛化探测（空心方块）：基线第5次为0，干预期第16次为13。图文不一致：正文写“干预期10、维持期13”，图上干预期为13、维持期为10，两者疑似对调；按图取值。两段均只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T374" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U374" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="72" customHeight="1">
       <c r="A375" s="17" t="inlineStr">
@@ -33181,6 +35820,16 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取Dyad A实心/空心方块的PDF坐标，按右纵轴（0–25）刻度线换算；干预与维持分界位于第16、17次之间。泛化探测：基线第5次为0，维持期第34次为10。图文不一致：正文写维持期13，图上为10（与干预期数值疑似对调，见D0373）；按图取值。两段均只有1点（&lt;3点规则待定）。</t>
         </is>
       </c>
+      <c r="T375" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U375" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="60" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
@@ -33267,6 +35916,12 @@
         </is>
       </c>
       <c r="S376" s="3" t="n"/>
+      <c r="T376" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U376" s="45" t="n"/>
     </row>
     <row r="377" ht="60" customHeight="1">
       <c r="A377" s="7" t="inlineStr">
@@ -33353,6 +36008,12 @@
         </is>
       </c>
       <c r="S377" s="8" t="n"/>
+      <c r="T377" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U377" s="46" t="n"/>
     </row>
     <row r="378" ht="60" customHeight="1">
       <c r="A378" s="7" t="inlineStr">
@@ -33439,6 +36100,12 @@
         </is>
       </c>
       <c r="S378" s="8" t="n"/>
+      <c r="T378" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U378" s="46" t="n"/>
     </row>
     <row r="379" ht="60" customHeight="1">
       <c r="A379" s="7" t="inlineStr">
@@ -33525,6 +36192,12 @@
         </is>
       </c>
       <c r="S379" s="8" t="n"/>
+      <c r="T379" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U379" s="46" t="n"/>
     </row>
     <row r="380" ht="60" customHeight="1">
       <c r="A380" s="7" t="inlineStr">
@@ -33611,6 +36284,12 @@
         </is>
       </c>
       <c r="S380" s="8" t="n"/>
+      <c r="T380" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U380" s="46" t="n"/>
     </row>
     <row r="381" ht="60" customHeight="1">
       <c r="A381" s="7" t="inlineStr">
@@ -33697,6 +36376,12 @@
         </is>
       </c>
       <c r="S381" s="8" t="n"/>
+      <c r="T381" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U381" s="46" t="n"/>
     </row>
     <row r="382" ht="60" customHeight="1">
       <c r="A382" s="7" t="inlineStr">
@@ -33783,6 +36468,12 @@
         </is>
       </c>
       <c r="S382" s="8" t="n"/>
+      <c r="T382" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U382" s="46" t="n"/>
     </row>
     <row r="383" ht="60" customHeight="1">
       <c r="A383" s="7" t="inlineStr">
@@ -33869,6 +36560,12 @@
         </is>
       </c>
       <c r="S383" s="8" t="n"/>
+      <c r="T383" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U383" s="46" t="n"/>
     </row>
     <row r="384" ht="60" customHeight="1">
       <c r="A384" s="7" t="inlineStr">
@@ -33955,6 +36652,12 @@
         </is>
       </c>
       <c r="S384" s="8" t="n"/>
+      <c r="T384" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U384" s="46" t="n"/>
     </row>
     <row r="385" ht="60" customHeight="1">
       <c r="A385" s="7" t="inlineStr">
@@ -34041,6 +36744,12 @@
         </is>
       </c>
       <c r="S385" s="8" t="n"/>
+      <c r="T385" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U385" s="46" t="n"/>
     </row>
     <row r="386" ht="60" customHeight="1">
       <c r="A386" s="7" t="inlineStr">
@@ -34127,6 +36836,12 @@
         </is>
       </c>
       <c r="S386" s="8" t="n"/>
+      <c r="T386" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U386" s="46" t="n"/>
     </row>
     <row r="387" ht="60" customHeight="1">
       <c r="A387" s="7" t="inlineStr">
@@ -34213,6 +36928,12 @@
         </is>
       </c>
       <c r="S387" s="8" t="n"/>
+      <c r="T387" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U387" s="46" t="n"/>
     </row>
     <row r="388" ht="60" customHeight="1">
       <c r="A388" s="7" t="inlineStr">
@@ -34299,6 +37020,12 @@
         </is>
       </c>
       <c r="S388" s="8" t="n"/>
+      <c r="T388" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U388" s="46" t="n"/>
     </row>
     <row r="389" ht="60" customHeight="1">
       <c r="A389" s="7" t="inlineStr">
@@ -34385,6 +37112,12 @@
         </is>
       </c>
       <c r="S389" s="8" t="n"/>
+      <c r="T389" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U389" s="46" t="n"/>
     </row>
     <row r="390" ht="60" customHeight="1">
       <c r="A390" s="7" t="inlineStr">
@@ -34471,6 +37204,12 @@
         </is>
       </c>
       <c r="S390" s="8" t="n"/>
+      <c r="T390" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U390" s="46" t="n"/>
     </row>
     <row r="391" ht="60" customHeight="1">
       <c r="A391" s="7" t="inlineStr">
@@ -34557,6 +37296,12 @@
         </is>
       </c>
       <c r="S391" s="8" t="n"/>
+      <c r="T391" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U391" s="46" t="n"/>
     </row>
     <row r="392" ht="60" customHeight="1">
       <c r="A392" s="7" t="inlineStr">
@@ -34643,6 +37388,12 @@
         </is>
       </c>
       <c r="S392" s="8" t="n"/>
+      <c r="T392" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U392" s="46" t="n"/>
     </row>
     <row r="393" ht="60" customHeight="1">
       <c r="A393" s="7" t="inlineStr">
@@ -34729,6 +37480,12 @@
         </is>
       </c>
       <c r="S393" s="8" t="n"/>
+      <c r="T393" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U393" s="46" t="n"/>
     </row>
     <row r="394" ht="60" customHeight="1">
       <c r="A394" s="7" t="inlineStr">
@@ -34815,6 +37572,12 @@
         </is>
       </c>
       <c r="S394" s="8" t="n"/>
+      <c r="T394" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U394" s="46" t="n"/>
     </row>
     <row r="395" ht="60" customHeight="1">
       <c r="A395" s="7" t="inlineStr">
@@ -34901,6 +37664,12 @@
         </is>
       </c>
       <c r="S395" s="8" t="n"/>
+      <c r="T395" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U395" s="46" t="n"/>
     </row>
     <row r="396" ht="60" customHeight="1">
       <c r="A396" s="7" t="inlineStr">
@@ -34987,6 +37756,12 @@
         </is>
       </c>
       <c r="S396" s="8" t="n"/>
+      <c r="T396" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U396" s="46" t="n"/>
     </row>
     <row r="397" ht="60" customHeight="1">
       <c r="A397" s="7" t="inlineStr">
@@ -35073,6 +37848,12 @@
         </is>
       </c>
       <c r="S397" s="8" t="n"/>
+      <c r="T397" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U397" s="46" t="n"/>
     </row>
     <row r="398" ht="60" customHeight="1">
       <c r="A398" s="7" t="inlineStr">
@@ -35159,6 +37940,12 @@
         </is>
       </c>
       <c r="S398" s="8" t="n"/>
+      <c r="T398" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U398" s="46" t="n"/>
     </row>
     <row r="399" ht="60" customHeight="1">
       <c r="A399" s="7" t="inlineStr">
@@ -35245,6 +38032,12 @@
         </is>
       </c>
       <c r="S399" s="8" t="n"/>
+      <c r="T399" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U399" s="46" t="n"/>
     </row>
     <row r="400" ht="60" customHeight="1">
       <c r="A400" s="7" t="inlineStr">
@@ -35331,6 +38124,12 @@
         </is>
       </c>
       <c r="S400" s="8" t="n"/>
+      <c r="T400" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U400" s="46" t="n"/>
     </row>
     <row r="401" ht="60" customHeight="1">
       <c r="A401" s="7" t="inlineStr">
@@ -35417,6 +38216,12 @@
         </is>
       </c>
       <c r="S401" s="8" t="n"/>
+      <c r="T401" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U401" s="46" t="n"/>
     </row>
     <row r="402" ht="60" customHeight="1">
       <c r="A402" s="7" t="inlineStr">
@@ -35503,6 +38308,12 @@
         </is>
       </c>
       <c r="S402" s="8" t="n"/>
+      <c r="T402" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U402" s="46" t="n"/>
     </row>
     <row r="403" ht="60" customHeight="1">
       <c r="A403" s="7" t="inlineStr">
@@ -35589,6 +38400,12 @@
         </is>
       </c>
       <c r="S403" s="8" t="n"/>
+      <c r="T403" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U403" s="46" t="n"/>
     </row>
     <row r="404" ht="60" customHeight="1">
       <c r="A404" s="7" t="inlineStr">
@@ -35675,6 +38492,12 @@
         </is>
       </c>
       <c r="S404" s="8" t="n"/>
+      <c r="T404" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U404" s="46" t="n"/>
     </row>
     <row r="405" ht="60" customHeight="1">
       <c r="A405" s="7" t="inlineStr">
@@ -35761,6 +38584,12 @@
         </is>
       </c>
       <c r="S405" s="8" t="n"/>
+      <c r="T405" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U405" s="46" t="n"/>
     </row>
     <row r="406" ht="36" customHeight="1">
       <c r="A406" s="12" t="inlineStr">
@@ -35847,6 +38676,12 @@
         </is>
       </c>
       <c r="S406" s="13" t="n"/>
+      <c r="T406" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U406" s="45" t="n"/>
     </row>
     <row r="407" ht="36" customHeight="1">
       <c r="A407" s="17" t="inlineStr">
@@ -35933,6 +38768,12 @@
         </is>
       </c>
       <c r="S407" s="18" t="n"/>
+      <c r="T407" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U407" s="46" t="n"/>
     </row>
     <row r="408" ht="36" customHeight="1">
       <c r="A408" s="17" t="inlineStr">
@@ -36019,6 +38860,12 @@
         </is>
       </c>
       <c r="S408" s="18" t="n"/>
+      <c r="T408" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U408" s="46" t="n"/>
     </row>
     <row r="409" ht="36" customHeight="1">
       <c r="A409" s="17" t="inlineStr">
@@ -36105,6 +38952,12 @@
         </is>
       </c>
       <c r="S409" s="18" t="n"/>
+      <c r="T409" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U409" s="46" t="n"/>
     </row>
     <row r="410" ht="48" customHeight="1">
       <c r="A410" s="17" t="inlineStr">
@@ -36191,6 +39044,16 @@
         </is>
       </c>
       <c r="S410" s="18" t="n"/>
+      <c r="T410" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U410" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段11点，后段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="36" customHeight="1">
       <c r="A411" s="17" t="inlineStr">
@@ -36277,6 +39140,12 @@
         </is>
       </c>
       <c r="S411" s="18" t="n"/>
+      <c r="T411" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U411" s="46" t="n"/>
     </row>
     <row r="412" ht="36" customHeight="1">
       <c r="A412" s="17" t="inlineStr">
@@ -36363,6 +39232,12 @@
         </is>
       </c>
       <c r="S412" s="18" t="n"/>
+      <c r="T412" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U412" s="46" t="n"/>
     </row>
     <row r="413" ht="36" customHeight="1">
       <c r="A413" s="17" t="inlineStr">
@@ -36449,6 +39324,12 @@
         </is>
       </c>
       <c r="S413" s="18" t="n"/>
+      <c r="T413" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U413" s="46" t="n"/>
     </row>
     <row r="414" ht="36" customHeight="1">
       <c r="A414" s="17" t="inlineStr">
@@ -36535,6 +39416,12 @@
         </is>
       </c>
       <c r="S414" s="18" t="n"/>
+      <c r="T414" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U414" s="46" t="n"/>
     </row>
     <row r="415" ht="36" customHeight="1">
       <c r="A415" s="17" t="inlineStr">
@@ -36621,6 +39508,12 @@
         </is>
       </c>
       <c r="S415" s="18" t="n"/>
+      <c r="T415" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U415" s="46" t="n"/>
     </row>
     <row r="416" ht="36" customHeight="1">
       <c r="A416" s="17" t="inlineStr">
@@ -36707,6 +39600,12 @@
         </is>
       </c>
       <c r="S416" s="18" t="n"/>
+      <c r="T416" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U416" s="46" t="n"/>
     </row>
     <row r="417" ht="36" customHeight="1">
       <c r="A417" s="17" t="inlineStr">
@@ -36793,6 +39692,12 @@
         </is>
       </c>
       <c r="S417" s="18" t="n"/>
+      <c r="T417" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U417" s="46" t="n"/>
     </row>
     <row r="418" ht="48" customHeight="1">
       <c r="A418" s="17" t="inlineStr">
@@ -36879,6 +39784,12 @@
         </is>
       </c>
       <c r="S418" s="18" t="n"/>
+      <c r="T418" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U418" s="46" t="n"/>
     </row>
     <row r="419" ht="48" customHeight="1">
       <c r="A419" s="17" t="inlineStr">
@@ -36965,6 +39876,12 @@
         </is>
       </c>
       <c r="S419" s="18" t="n"/>
+      <c r="T419" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U419" s="46" t="n"/>
     </row>
     <row r="420" ht="48" customHeight="1">
       <c r="A420" s="17" t="inlineStr">
@@ -37051,6 +39968,12 @@
         </is>
       </c>
       <c r="S420" s="18" t="n"/>
+      <c r="T420" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U420" s="46" t="n"/>
     </row>
     <row r="421" ht="48" customHeight="1">
       <c r="A421" s="17" t="inlineStr">
@@ -37137,6 +40060,12 @@
         </is>
       </c>
       <c r="S421" s="18" t="n"/>
+      <c r="T421" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U421" s="46" t="n"/>
     </row>
     <row r="422" ht="48" customHeight="1">
       <c r="A422" s="17" t="inlineStr">
@@ -37223,6 +40152,16 @@
         </is>
       </c>
       <c r="S422" s="18" t="n"/>
+      <c r="T422" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U422" s="46" t="inlineStr">
+        <is>
+          <t>规则B：干预比较要求前后两段各不少于3点（前段11点，后段2点）</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="48" customHeight="1">
       <c r="A423" s="17" t="inlineStr">
@@ -37309,6 +40248,12 @@
         </is>
       </c>
       <c r="S423" s="18" t="n"/>
+      <c r="T423" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U423" s="46" t="n"/>
     </row>
     <row r="424" ht="48" customHeight="1">
       <c r="A424" s="17" t="inlineStr">
@@ -37395,6 +40340,12 @@
         </is>
       </c>
       <c r="S424" s="18" t="n"/>
+      <c r="T424" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U424" s="46" t="n"/>
     </row>
     <row r="425" ht="48" customHeight="1">
       <c r="A425" s="17" t="inlineStr">
@@ -37481,6 +40432,12 @@
         </is>
       </c>
       <c r="S425" s="18" t="n"/>
+      <c r="T425" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U425" s="46" t="n"/>
     </row>
     <row r="426" ht="48" customHeight="1">
       <c r="A426" s="17" t="inlineStr">
@@ -37567,6 +40524,12 @@
         </is>
       </c>
       <c r="S426" s="18" t="n"/>
+      <c r="T426" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U426" s="46" t="n"/>
     </row>
     <row r="427" ht="48" customHeight="1">
       <c r="A427" s="17" t="inlineStr">
@@ -37653,6 +40616,12 @@
         </is>
       </c>
       <c r="S427" s="18" t="n"/>
+      <c r="T427" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U427" s="46" t="n"/>
     </row>
     <row r="428" ht="48" customHeight="1">
       <c r="A428" s="17" t="inlineStr">
@@ -37739,6 +40708,12 @@
         </is>
       </c>
       <c r="S428" s="18" t="n"/>
+      <c r="T428" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U428" s="46" t="n"/>
     </row>
     <row r="429" ht="48" customHeight="1">
       <c r="A429" s="17" t="inlineStr">
@@ -37825,6 +40800,12 @@
         </is>
       </c>
       <c r="S429" s="18" t="n"/>
+      <c r="T429" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U429" s="46" t="n"/>
     </row>
     <row r="430" ht="60" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
@@ -37911,6 +40892,12 @@
         </is>
       </c>
       <c r="S430" s="3" t="n"/>
+      <c r="T430" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U430" s="45" t="n"/>
     </row>
     <row r="431" ht="60" customHeight="1">
       <c r="A431" s="7" t="inlineStr">
@@ -37997,6 +40984,12 @@
         </is>
       </c>
       <c r="S431" s="8" t="n"/>
+      <c r="T431" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U431" s="46" t="n"/>
     </row>
     <row r="432" ht="60" customHeight="1">
       <c r="A432" s="7" t="inlineStr">
@@ -38083,6 +41076,12 @@
         </is>
       </c>
       <c r="S432" s="8" t="n"/>
+      <c r="T432" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U432" s="46" t="n"/>
     </row>
     <row r="433" ht="48" customHeight="1">
       <c r="A433" s="12" t="inlineStr">
@@ -38173,6 +41172,12 @@
           <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。Fox基线9点均值32.2，与表1一致；图文不一致：基线第7次图上为45秒，超出表1范围15–40。干预18点均值149.7、范围70–250，与表1一致。按图取值。</t>
         </is>
       </c>
+      <c r="T433" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U433" s="45" t="n"/>
     </row>
     <row r="434" ht="48" customHeight="1">
       <c r="A434" s="17" t="inlineStr">
@@ -38263,6 +41268,12 @@
           <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。基线同D0432（第7次45秒超出表1范围）。维持4点均值182.5、范围170–190，与表1一致。</t>
         </is>
       </c>
+      <c r="T434" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U434" s="46" t="n"/>
     </row>
     <row r="435" ht="36" customHeight="1">
       <c r="A435" s="17" t="inlineStr">
@@ -38353,6 +41364,12 @@
           <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。Fox基线9点均值3.56，与表1均值3.60一致；图文不一致：基线第4次图上为5，超出表1范围2–4（正文范围支持图示）。干预18点均值8.17、范围6–10，与表1（8.20，6–10）一致。按图取值。</t>
         </is>
       </c>
+      <c r="T435" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U435" s="46" t="n"/>
     </row>
     <row r="436" ht="36" customHeight="1">
       <c r="A436" s="17" t="inlineStr">
@@ -38443,6 +41460,12 @@
           <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。基线同D0434。维持4点均值7.25、范围7–8，与表1（7.20，7–8）一致。</t>
         </is>
       </c>
+      <c r="T436" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U436" s="46" t="n"/>
     </row>
     <row r="437" ht="36" customHeight="1">
       <c r="A437" s="17" t="inlineStr">
@@ -38529,6 +41552,12 @@
         </is>
       </c>
       <c r="S437" s="18" t="n"/>
+      <c r="T437" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U437" s="46" t="n"/>
     </row>
     <row r="438" ht="36" customHeight="1">
       <c r="A438" s="17" t="inlineStr">
@@ -38615,6 +41644,12 @@
         </is>
       </c>
       <c r="S438" s="18" t="n"/>
+      <c r="T438" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U438" s="46" t="n"/>
     </row>
     <row r="439" ht="48" customHeight="1">
       <c r="A439" s="17" t="inlineStr">
@@ -38705,6 +41740,12 @@
           <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。图文不一致：Sam基线12点均值20.8、范围15–25，表1报告28.7（15–40）；干预15点均值134.3、范围55–250，表1报告133.3（55–200）。表1中Sam基线的均值、SD、范围与Fox高度相似，可能有抄录错误。按图取值。</t>
         </is>
       </c>
+      <c r="T439" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U439" s="46" t="n"/>
     </row>
     <row r="440" ht="48" customHeight="1">
       <c r="A440" s="17" t="inlineStr">
@@ -38795,6 +41836,12 @@
           <t>Claude补提取（以图为准）：从PDF第14页Fig. 1内嵌原图（1406×1791像素）逐像素检测实心圆，按各面板纵轴刻度标签换算，读数均落在5秒的整倍数上。基线同D0438。图文不一致：维持4点均值187.5、范围170–200，表1报告170（160–180）。按图取值。</t>
         </is>
       </c>
+      <c r="T440" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U440" s="46" t="n"/>
     </row>
     <row r="441" ht="36" customHeight="1">
       <c r="A441" s="17" t="inlineStr">
@@ -38881,6 +41928,12 @@
         </is>
       </c>
       <c r="S441" s="18" t="n"/>
+      <c r="T441" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U441" s="46" t="n"/>
     </row>
     <row r="442" ht="36" customHeight="1">
       <c r="A442" s="17" t="inlineStr">
@@ -38967,6 +42020,12 @@
         </is>
       </c>
       <c r="S442" s="18" t="n"/>
+      <c r="T442" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U442" s="46" t="n"/>
     </row>
     <row r="443" ht="36" customHeight="1">
       <c r="A443" s="17" t="inlineStr">
@@ -39053,6 +42112,12 @@
         </is>
       </c>
       <c r="S443" s="18" t="n"/>
+      <c r="T443" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U443" s="46" t="n"/>
     </row>
     <row r="444" ht="36" customHeight="1">
       <c r="A444" s="17" t="inlineStr">
@@ -39139,6 +42204,12 @@
         </is>
       </c>
       <c r="S444" s="18" t="n"/>
+      <c r="T444" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U444" s="46" t="n"/>
     </row>
     <row r="445" ht="48" customHeight="1">
       <c r="A445" s="17" t="inlineStr">
@@ -39225,6 +42296,12 @@
         </is>
       </c>
       <c r="S445" s="18" t="n"/>
+      <c r="T445" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U445" s="46" t="n"/>
     </row>
     <row r="446" ht="48" customHeight="1">
       <c r="A446" s="17" t="inlineStr">
@@ -39311,6 +42388,12 @@
         </is>
       </c>
       <c r="S446" s="18" t="n"/>
+      <c r="T446" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U446" s="46" t="n"/>
     </row>
     <row r="447" ht="36" customHeight="1">
       <c r="A447" s="17" t="inlineStr">
@@ -39397,6 +42480,12 @@
         </is>
       </c>
       <c r="S447" s="18" t="n"/>
+      <c r="T447" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U447" s="46" t="n"/>
     </row>
     <row r="448" ht="36" customHeight="1">
       <c r="A448" s="17" t="inlineStr">
@@ -39483,6 +42572,12 @@
         </is>
       </c>
       <c r="S448" s="18" t="n"/>
+      <c r="T448" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U448" s="46" t="n"/>
     </row>
     <row r="449" ht="36" customHeight="1">
       <c r="A449" s="17" t="inlineStr">
@@ -39573,6 +42668,12 @@
           <t>Claude补提取（以图为准）：从PDF第16页Fig. 2内嵌原图（1406×1618像素）逐像素检测黑色方块（发起）和浅灰圆点（回应），按纵轴刻度标签换算，读数均为整数；被浅灰圆点覆盖的方块按图上位置读取。基线17点与D0449相同。图文不一致：干预10点均值7.0，表1报告7.70（范围5–9与图一致），无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
+      <c r="T449" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U449" s="46" t="n"/>
     </row>
     <row r="450" ht="36" customHeight="1">
       <c r="A450" s="17" t="inlineStr">
@@ -39659,6 +42760,12 @@
         </is>
       </c>
       <c r="S450" s="18" t="n"/>
+      <c r="T450" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U450" s="46" t="n"/>
     </row>
     <row r="451" ht="60" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
@@ -39749,6 +42856,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取黑色实心方块（Student with ASD）的PDF坐标，按各面板0与100位置换算后取整；缺失的观测为学生缺勤（图注）。Participant One面板：基线4点均为0，干预30点均值87.4%、最小值53%。图文不一致：正文写被试1基线1%（0–5%）、干预范围47–100%，与图上Participant Two面板的数值对应，被试1、2在正文中疑似对调。按图（面板标签）取值。</t>
         </is>
       </c>
+      <c r="T451" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U451" s="45" t="n"/>
     </row>
     <row r="452" ht="60" customHeight="1">
       <c r="A452" s="7" t="inlineStr">
@@ -39836,6 +42949,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T452" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U452" s="46" t="n"/>
     </row>
     <row r="453" ht="60" customHeight="1">
       <c r="A453" s="7" t="inlineStr">
@@ -39926,6 +43045,12 @@
           <t>Claude补提取（以图为准）：Fig. 1为PDF矢量图，读取黑色实心方块（Student with ASD）的PDF坐标，按各面板0与100位置换算后取整；缺失的观测为学生缺勤（图注）。Participant Two面板：基线4点均值1.25%（0–5%），干预30点均值87.2%、最小值47%。图文不一致：正文写被试2基线0%、干预范围53–100%，与图上Participant One面板对应，疑似对调。按图（面板标签）取值。两名被试同为三年级学生，对调对合并效应量和按年龄段分组没有影响。</t>
         </is>
       </c>
+      <c r="T453" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U453" s="46" t="n"/>
     </row>
     <row r="454" ht="60" customHeight="1">
       <c r="A454" s="7" t="inlineStr">
@@ -40013,6 +43138,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T454" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U454" s="46" t="n"/>
     </row>
     <row r="455" ht="60" customHeight="1">
       <c r="A455" s="7" t="inlineStr">
@@ -40099,6 +43230,12 @@
         </is>
       </c>
       <c r="S455" s="8" t="n"/>
+      <c r="T455" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U455" s="46" t="n"/>
     </row>
     <row r="456" ht="60" customHeight="1">
       <c r="A456" s="7" t="inlineStr">
@@ -40185,6 +43322,12 @@
         </is>
       </c>
       <c r="S456" s="8" t="n"/>
+      <c r="T456" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U456" s="46" t="n"/>
     </row>
     <row r="457" ht="60" customHeight="1">
       <c r="A457" s="7" t="inlineStr">
@@ -40271,6 +43414,12 @@
         </is>
       </c>
       <c r="S457" s="8" t="n"/>
+      <c r="T457" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U457" s="46" t="n"/>
     </row>
     <row r="458" ht="60" customHeight="1">
       <c r="A458" s="7" t="inlineStr">
@@ -40357,6 +43506,12 @@
         </is>
       </c>
       <c r="S458" s="8" t="n"/>
+      <c r="T458" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U458" s="46" t="n"/>
     </row>
     <row r="459" ht="60" customHeight="1">
       <c r="A459" s="7" t="inlineStr">
@@ -40443,6 +43598,12 @@
         </is>
       </c>
       <c r="S459" s="8" t="n"/>
+      <c r="T459" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U459" s="46" t="n"/>
     </row>
     <row r="460" ht="60" customHeight="1">
       <c r="A460" s="7" t="inlineStr">
@@ -40529,6 +43690,12 @@
         </is>
       </c>
       <c r="S460" s="8" t="n"/>
+      <c r="T460" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U460" s="46" t="n"/>
     </row>
     <row r="461" ht="60" customHeight="1">
       <c r="A461" s="7" t="inlineStr">
@@ -40615,6 +43782,12 @@
         </is>
       </c>
       <c r="S461" s="8" t="n"/>
+      <c r="T461" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U461" s="46" t="n"/>
     </row>
     <row r="462" ht="60" customHeight="1">
       <c r="A462" s="7" t="inlineStr">
@@ -40701,6 +43874,12 @@
         </is>
       </c>
       <c r="S462" s="8" t="n"/>
+      <c r="T462" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U462" s="46" t="n"/>
     </row>
     <row r="463" ht="36" customHeight="1">
       <c r="A463" s="12" t="inlineStr">
@@ -40787,6 +43966,12 @@
         </is>
       </c>
       <c r="S463" s="13" t="n"/>
+      <c r="T463" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U463" s="45" t="n"/>
     </row>
     <row r="464" ht="36" customHeight="1">
       <c r="A464" s="17" t="inlineStr">
@@ -40873,6 +44058,12 @@
         </is>
       </c>
       <c r="S464" s="18" t="n"/>
+      <c r="T464" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U464" s="46" t="n"/>
     </row>
     <row r="465" ht="36" customHeight="1">
       <c r="A465" s="17" t="inlineStr">
@@ -40959,6 +44150,12 @@
         </is>
       </c>
       <c r="S465" s="18" t="n"/>
+      <c r="T465" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U465" s="46" t="n"/>
     </row>
     <row r="466" ht="36" customHeight="1">
       <c r="A466" s="17" t="inlineStr">
@@ -41045,6 +44242,12 @@
         </is>
       </c>
       <c r="S466" s="18" t="n"/>
+      <c r="T466" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U466" s="46" t="n"/>
     </row>
     <row r="467" ht="36" customHeight="1">
       <c r="A467" s="17" t="inlineStr">
@@ -41131,6 +44334,12 @@
         </is>
       </c>
       <c r="S467" s="18" t="n"/>
+      <c r="T467" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U467" s="46" t="n"/>
     </row>
     <row r="468" ht="36" customHeight="1">
       <c r="A468" s="17" t="inlineStr">
@@ -41217,6 +44426,12 @@
         </is>
       </c>
       <c r="S468" s="18" t="n"/>
+      <c r="T468" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U468" s="46" t="n"/>
     </row>
     <row r="469" ht="36" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
@@ -41303,6 +44518,12 @@
         </is>
       </c>
       <c r="S469" s="3" t="n"/>
+      <c r="T469" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U469" s="45" t="n"/>
     </row>
     <row r="470" ht="36" customHeight="1">
       <c r="A470" s="7" t="inlineStr">
@@ -41389,6 +44610,12 @@
         </is>
       </c>
       <c r="S470" s="8" t="n"/>
+      <c r="T470" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U470" s="46" t="n"/>
     </row>
     <row r="471" ht="36" customHeight="1">
       <c r="A471" s="7" t="inlineStr">
@@ -41475,6 +44702,12 @@
         </is>
       </c>
       <c r="S471" s="8" t="n"/>
+      <c r="T471" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U471" s="46" t="n"/>
     </row>
     <row r="472" ht="36" customHeight="1">
       <c r="A472" s="7" t="inlineStr">
@@ -41561,6 +44794,12 @@
         </is>
       </c>
       <c r="S472" s="8" t="n"/>
+      <c r="T472" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U472" s="46" t="n"/>
     </row>
     <row r="473" ht="27" customHeight="1">
       <c r="A473" s="7" t="inlineStr">
@@ -41647,6 +44886,12 @@
         </is>
       </c>
       <c r="S473" s="8" t="n"/>
+      <c r="T473" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U473" s="46" t="n"/>
     </row>
     <row r="474" ht="27" customHeight="1">
       <c r="A474" s="7" t="inlineStr">
@@ -41733,6 +44978,12 @@
         </is>
       </c>
       <c r="S474" s="8" t="n"/>
+      <c r="T474" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U474" s="46" t="n"/>
     </row>
     <row r="475" ht="36" customHeight="1">
       <c r="A475" s="7" t="inlineStr">
@@ -41802,6 +45053,16 @@
           <t>待审核：干预子阶段边界与正文定义的对应关系不明，且音乐情境替代技能的图示范围与正文不符，需核实分段及读值。</t>
         </is>
       </c>
+      <c r="T475" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U475" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="36" customHeight="1">
       <c r="A476" s="7" t="inlineStr">
@@ -41887,6 +45148,16 @@
       <c r="S476" s="8" t="inlineStr">
         <is>
           <t>前段仅1个观察点，无法检验基线趋势。</t>
+        </is>
+      </c>
+      <c r="T476" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U476" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
         </is>
       </c>
     </row>
@@ -41958,6 +45229,16 @@
           <t>待审核：图中干预标题位置与正文三个提示子阶段的定义存在歧义，无法确定首个干预阶段应包含哪些观察点。</t>
         </is>
       </c>
+      <c r="T477" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U477" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="36" customHeight="1">
       <c r="A478" s="7" t="inlineStr">
@@ -42043,6 +45324,16 @@
       <c r="S478" s="8" t="inlineStr">
         <is>
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
+        </is>
+      </c>
+      <c r="T478" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U478" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
         </is>
       </c>
     </row>
@@ -42114,6 +45405,16 @@
           <t>待审核：图中干预标题位置与正文三个提示子阶段的定义存在歧义，无法确定首个干预阶段应包含哪些观察点。</t>
         </is>
       </c>
+      <c r="T479" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U479" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="27" customHeight="1">
       <c r="A480" s="7" t="inlineStr">
@@ -42199,6 +45500,16 @@
       <c r="S480" s="8" t="inlineStr">
         <is>
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
+        </is>
+      </c>
+      <c r="T480" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U480" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段2点）</t>
         </is>
       </c>
     </row>
@@ -42270,6 +45581,16 @@
           <t>待审核：图中干预标题位置与正文三个提示子阶段的定义存在歧义，无法确定首个干预阶段应包含哪些观察点。</t>
         </is>
       </c>
+      <c r="T481" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U481" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="36" customHeight="1">
       <c r="A482" s="7" t="inlineStr">
@@ -42355,6 +45676,16 @@
       <c r="S482" s="8" t="inlineStr">
         <is>
           <t>前段仅1个观察点，无法检验基线趋势。</t>
+        </is>
+      </c>
+      <c r="T482" s="46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U482" s="46" t="inlineStr">
+        <is>
+          <t>规则B：前段（基线）要求不少于3点（前段1点）</t>
         </is>
       </c>
     </row>
@@ -42426,6 +45757,16 @@
           <t>待审核：中心活动基线图示值与正文范围冲突，同时干预子阶段边界存在歧义，需核实基线和前后段对应关系。</t>
         </is>
       </c>
+      <c r="T483" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U483" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="36" customHeight="1">
       <c r="A484" s="7" t="inlineStr">
@@ -42495,6 +45836,16 @@
           <t>待审核：中心活动基线图示值与正文报告范围不一致，尚不能确定错误来源，需核实该基线后再确认比较。</t>
         </is>
       </c>
+      <c r="T484" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U484" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="27" customHeight="1">
       <c r="A485" s="7" t="inlineStr">
@@ -42564,6 +45915,16 @@
           <t>待审核：集体活动基线图示点与正文范围及均值不符，可能存在未画点，同时干预子阶段边界尚未确认。</t>
         </is>
       </c>
+      <c r="T485" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U485" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="27" customHeight="1">
       <c r="A486" s="7" t="inlineStr">
@@ -42633,6 +45994,16 @@
           <t>待审核：集体活动图中可见的基线点与正文报告范围及均值不一致，可能存在未画点，不能据正文补齐。</t>
         </is>
       </c>
+      <c r="T486" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U486" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="36" customHeight="1">
       <c r="A487" s="12" t="inlineStr">
@@ -42719,6 +46090,12 @@
         </is>
       </c>
       <c r="S487" s="13" t="n"/>
+      <c r="T487" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U487" s="45" t="n"/>
     </row>
     <row r="488" ht="36" customHeight="1">
       <c r="A488" s="17" t="inlineStr">
@@ -42805,6 +46182,12 @@
         </is>
       </c>
       <c r="S488" s="18" t="n"/>
+      <c r="T488" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U488" s="46" t="n"/>
     </row>
     <row r="489" ht="36" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
@@ -42891,6 +46274,12 @@
         </is>
       </c>
       <c r="S489" s="18" t="n"/>
+      <c r="T489" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U489" s="46" t="n"/>
     </row>
     <row r="490" ht="36" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
@@ -42977,6 +46366,12 @@
         </is>
       </c>
       <c r="S490" s="18" t="n"/>
+      <c r="T490" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U490" s="46" t="n"/>
     </row>
     <row r="491" ht="36" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
@@ -43063,6 +46458,12 @@
         </is>
       </c>
       <c r="S491" s="18" t="n"/>
+      <c r="T491" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U491" s="46" t="n"/>
     </row>
     <row r="492" ht="36" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
@@ -43149,6 +46550,12 @@
         </is>
       </c>
       <c r="S492" s="18" t="n"/>
+      <c r="T492" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U492" s="46" t="n"/>
     </row>
     <row r="493" ht="36" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
@@ -43235,6 +46642,12 @@
         </is>
       </c>
       <c r="S493" s="18" t="n"/>
+      <c r="T493" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U493" s="46" t="n"/>
     </row>
     <row r="494" ht="36" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
@@ -43321,6 +46734,12 @@
         </is>
       </c>
       <c r="S494" s="18" t="n"/>
+      <c r="T494" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U494" s="46" t="n"/>
     </row>
     <row r="495" ht="36" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
@@ -43407,6 +46826,12 @@
         </is>
       </c>
       <c r="S495" s="18" t="n"/>
+      <c r="T495" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U495" s="46" t="n"/>
     </row>
     <row r="496" ht="36" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
@@ -43493,6 +46918,12 @@
         </is>
       </c>
       <c r="S496" s="18" t="n"/>
+      <c r="T496" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U496" s="46" t="n"/>
     </row>
     <row r="497" ht="36" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
@@ -43579,6 +47010,12 @@
         </is>
       </c>
       <c r="S497" s="18" t="n"/>
+      <c r="T497" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U497" s="46" t="n"/>
     </row>
     <row r="498" ht="36" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
@@ -43665,6 +47102,12 @@
         </is>
       </c>
       <c r="S498" s="18" t="n"/>
+      <c r="T498" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U498" s="46" t="n"/>
     </row>
     <row r="499" ht="36" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
@@ -43751,6 +47194,12 @@
         </is>
       </c>
       <c r="S499" s="3" t="n"/>
+      <c r="T499" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U499" s="45" t="n"/>
     </row>
     <row r="500" ht="36" customHeight="1">
       <c r="A500" s="7" t="inlineStr">
@@ -43837,6 +47286,12 @@
         </is>
       </c>
       <c r="S500" s="8" t="n"/>
+      <c r="T500" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U500" s="46" t="n"/>
     </row>
     <row r="501" ht="48" customHeight="1">
       <c r="A501" s="7" t="inlineStr">
@@ -43923,6 +47378,12 @@
         </is>
       </c>
       <c r="S501" s="8" t="n"/>
+      <c r="T501" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U501" s="46" t="n"/>
     </row>
     <row r="502" ht="36" customHeight="1">
       <c r="A502" s="7" t="inlineStr">
@@ -44009,6 +47470,12 @@
         </is>
       </c>
       <c r="S502" s="8" t="n"/>
+      <c r="T502" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U502" s="46" t="n"/>
     </row>
     <row r="503" ht="36" customHeight="1">
       <c r="A503" s="7" t="inlineStr">
@@ -44095,6 +47562,12 @@
         </is>
       </c>
       <c r="S503" s="8" t="n"/>
+      <c r="T503" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U503" s="46" t="n"/>
     </row>
     <row r="504" ht="36" customHeight="1">
       <c r="A504" s="7" t="inlineStr">
@@ -44181,6 +47654,12 @@
         </is>
       </c>
       <c r="S504" s="8" t="n"/>
+      <c r="T504" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U504" s="46" t="n"/>
     </row>
     <row r="505" ht="36" customHeight="1">
       <c r="A505" s="7" t="inlineStr">
@@ -44267,6 +47746,12 @@
         </is>
       </c>
       <c r="S505" s="8" t="n"/>
+      <c r="T505" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U505" s="46" t="n"/>
     </row>
     <row r="506" ht="48" customHeight="1">
       <c r="A506" s="7" t="inlineStr">
@@ -44353,6 +47838,12 @@
         </is>
       </c>
       <c r="S506" s="8" t="n"/>
+      <c r="T506" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U506" s="46" t="n"/>
     </row>
     <row r="507" ht="36" customHeight="1">
       <c r="A507" s="7" t="inlineStr">
@@ -44439,6 +47930,12 @@
         </is>
       </c>
       <c r="S507" s="8" t="n"/>
+      <c r="T507" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U507" s="46" t="n"/>
     </row>
     <row r="508" ht="36" customHeight="1">
       <c r="A508" s="7" t="inlineStr">
@@ -44525,6 +48022,12 @@
         </is>
       </c>
       <c r="S508" s="8" t="n"/>
+      <c r="T508" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U508" s="46" t="n"/>
     </row>
     <row r="509" ht="48" customHeight="1">
       <c r="A509" s="7" t="inlineStr">
@@ -44611,6 +48114,12 @@
         </is>
       </c>
       <c r="S509" s="8" t="n"/>
+      <c r="T509" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U509" s="46" t="n"/>
     </row>
     <row r="510" ht="48" customHeight="1">
       <c r="A510" s="7" t="inlineStr">
@@ -44697,6 +48206,12 @@
         </is>
       </c>
       <c r="S510" s="8" t="n"/>
+      <c r="T510" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U510" s="46" t="n"/>
     </row>
     <row r="511" ht="36" customHeight="1">
       <c r="A511" s="12" t="inlineStr">
@@ -44784,6 +48299,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T511" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U511" s="45" t="n"/>
     </row>
     <row r="512" ht="36" customHeight="1">
       <c r="A512" s="17" t="inlineStr">
@@ -44871,6 +48392,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T512" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U512" s="46" t="n"/>
     </row>
     <row r="513" ht="36" customHeight="1">
       <c r="A513" s="17" t="inlineStr">
@@ -44961,6 +48488,12 @@
           <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。图文不一致：Lena基线5点为4,4,0,1,1（均值2.0），正文写“0–4次，平均3次”，无法定位，按图取值。干预7点合计182、均值26.0、范围9–55，与正文一致。</t>
         </is>
       </c>
+      <c r="T513" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U513" s="46" t="n"/>
     </row>
     <row r="514" ht="36" customHeight="1">
       <c r="A514" s="17" t="inlineStr">
@@ -45047,6 +48580,12 @@
         </is>
       </c>
       <c r="S514" s="18" t="n"/>
+      <c r="T514" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U514" s="46" t="n"/>
     </row>
     <row r="515" ht="36" customHeight="1">
       <c r="A515" s="17" t="inlineStr">
@@ -45137,6 +48676,12 @@
           <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。图文不一致：Andrew干预第4点（第12次）图上约为1，低于正文报告的下限2（正文范围2–53）；干预12点均值19.4，正文约20。按图取值。</t>
         </is>
       </c>
+      <c r="T515" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U515" s="46" t="n"/>
     </row>
     <row r="516" ht="36" customHeight="1">
       <c r="A516" s="17" t="inlineStr">
@@ -45224,6 +48769,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T516" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U516" s="46" t="n"/>
     </row>
     <row r="517" ht="36" customHeight="1">
       <c r="A517" s="17" t="inlineStr">
@@ -45314,6 +48865,12 @@
           <t>Claude补提取（以图为准）：从PDF第11页Figure 2内嵌原图（753×557像素，分辨率低，1个单位约1.5像素）检测实心圆，按各面板纵轴刻度换算并扣除0值点的系统偏移（约0.45）；空心圆（New Therapist）不计入。读数精度约±1，落在两个整数中间的点参照正文的均值或范围取整。Cory干预11点均值14.2、范围4–23，与正文（平均14，4–23）一致；最后一点图上约22.4，按正文上限取23。原先所说的均值不一致按此读数不存在。</t>
         </is>
       </c>
+      <c r="T517" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U517" s="46" t="n"/>
     </row>
     <row r="518" ht="36" customHeight="1">
       <c r="A518" s="17" t="inlineStr">
@@ -45401,6 +48958,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T518" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U518" s="46" t="n"/>
     </row>
     <row r="519" ht="36" customHeight="1">
       <c r="A519" s="2" t="inlineStr">
@@ -45487,6 +49050,12 @@
         </is>
       </c>
       <c r="S519" s="3" t="n"/>
+      <c r="T519" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U519" s="45" t="n"/>
     </row>
     <row r="520" ht="60" customHeight="1">
       <c r="A520" s="7" t="inlineStr">
@@ -45573,6 +49142,12 @@
         </is>
       </c>
       <c r="S520" s="8" t="n"/>
+      <c r="T520" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U520" s="46" t="n"/>
     </row>
     <row r="521" ht="36" customHeight="1">
       <c r="A521" s="7" t="inlineStr">
@@ -45659,6 +49234,12 @@
         </is>
       </c>
       <c r="S521" s="8" t="n"/>
+      <c r="T521" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U521" s="46" t="n"/>
     </row>
     <row r="522" ht="36" customHeight="1">
       <c r="A522" s="7" t="inlineStr">
@@ -45745,6 +49326,12 @@
         </is>
       </c>
       <c r="S522" s="8" t="n"/>
+      <c r="T522" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U522" s="46" t="n"/>
     </row>
     <row r="523" ht="36" customHeight="1">
       <c r="A523" s="7" t="inlineStr">
@@ -45831,6 +49418,12 @@
         </is>
       </c>
       <c r="S523" s="8" t="n"/>
+      <c r="T523" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U523" s="46" t="n"/>
     </row>
     <row r="524" ht="60" customHeight="1">
       <c r="A524" s="7" t="inlineStr">
@@ -45917,6 +49510,12 @@
         </is>
       </c>
       <c r="S524" s="8" t="n"/>
+      <c r="T524" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U524" s="46" t="n"/>
     </row>
     <row r="525" ht="36" customHeight="1">
       <c r="A525" s="7" t="inlineStr">
@@ -46004,6 +49603,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T525" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U525" s="46" t="n"/>
     </row>
     <row r="526" ht="36" customHeight="1">
       <c r="A526" s="7" t="inlineStr">
@@ -46091,6 +49696,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T526" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U526" s="46" t="n"/>
     </row>
     <row r="527" ht="36" customHeight="1">
       <c r="A527" s="7" t="inlineStr">
@@ -46177,6 +49788,12 @@
         </is>
       </c>
       <c r="S527" s="8" t="n"/>
+      <c r="T527" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U527" s="46" t="n"/>
     </row>
     <row r="528" ht="60" customHeight="1">
       <c r="A528" s="7" t="inlineStr">
@@ -46263,6 +49880,12 @@
         </is>
       </c>
       <c r="S528" s="8" t="n"/>
+      <c r="T528" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U528" s="46" t="n"/>
     </row>
     <row r="529" ht="36" customHeight="1">
       <c r="A529" s="7" t="inlineStr">
@@ -46349,6 +49972,12 @@
         </is>
       </c>
       <c r="S529" s="8" t="n"/>
+      <c r="T529" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U529" s="46" t="n"/>
     </row>
     <row r="530" ht="36" customHeight="1">
       <c r="A530" s="7" t="inlineStr">
@@ -46435,6 +50064,12 @@
         </is>
       </c>
       <c r="S530" s="8" t="n"/>
+      <c r="T530" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U530" s="46" t="n"/>
     </row>
     <row r="531" ht="48" customHeight="1">
       <c r="A531" s="12" t="inlineStr">
@@ -46522,6 +50157,12 @@
           <t>前段为Adaptation of the playground，不作为原始基线检验趋势。</t>
         </is>
       </c>
+      <c r="T531" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U531" s="45" t="n"/>
     </row>
     <row r="532" ht="48" customHeight="1">
       <c r="A532" s="17" t="inlineStr">
@@ -46591,6 +50232,16 @@
           <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第12个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
+      <c r="T532" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U532" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="533" ht="60" customHeight="1">
       <c r="A533" s="17" t="inlineStr">
@@ -46660,6 +50311,16 @@
           <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第15、18个观察点的图示值超出正文报告上限，需核实两点后确认比较序列。</t>
         </is>
       </c>
+      <c r="T533" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U533" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="48" customHeight="1">
       <c r="A534" s="17" t="inlineStr">
@@ -46729,6 +50390,16 @@
           <t>【待审核】17 Kern 2006的Figure 1为扫描图，数据点模糊难以提取，Ben、Phillip、Lucas三行暂不提取。　【Claude第二轮：未提取】图为扫描件，数据点小而密集、贴近横轴，按用户要求“实在模糊、看不清就空着”，本行不填。　原备注：待审核：教师介入阶段第4个观察点的图示值超出正文报告上限，图文范围冲突，需核实对应数据。</t>
         </is>
       </c>
+      <c r="T534" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U534" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="535" ht="36" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
@@ -46815,6 +50486,12 @@
         </is>
       </c>
       <c r="S535" s="3" t="n"/>
+      <c r="T535" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U535" s="45" t="n"/>
     </row>
     <row r="536" ht="36" customHeight="1">
       <c r="A536" s="7" t="inlineStr">
@@ -46901,6 +50578,12 @@
         </is>
       </c>
       <c r="S536" s="8" t="n"/>
+      <c r="T536" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U536" s="46" t="n"/>
     </row>
     <row r="537" ht="36" customHeight="1">
       <c r="A537" s="7" t="inlineStr">
@@ -46987,6 +50670,12 @@
         </is>
       </c>
       <c r="S537" s="8" t="n"/>
+      <c r="T537" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U537" s="46" t="n"/>
     </row>
     <row r="538" ht="36" customHeight="1">
       <c r="A538" s="7" t="inlineStr">
@@ -47073,6 +50762,12 @@
         </is>
       </c>
       <c r="S538" s="8" t="n"/>
+      <c r="T538" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U538" s="46" t="n"/>
     </row>
     <row r="539" ht="36" customHeight="1">
       <c r="A539" s="7" t="inlineStr">
@@ -47160,6 +50855,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T539" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U539" s="46" t="n"/>
     </row>
     <row r="540" ht="36" customHeight="1">
       <c r="A540" s="7" t="inlineStr">
@@ -47247,6 +50948,12 @@
           <t>基线数值恒定，τ-b与p无定义；无基线趋势可校正。</t>
         </is>
       </c>
+      <c r="T540" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U540" s="46" t="n"/>
     </row>
     <row r="541" ht="60" customHeight="1">
       <c r="A541" s="7" t="inlineStr">
@@ -47333,6 +51040,12 @@
         </is>
       </c>
       <c r="S541" s="8" t="n"/>
+      <c r="T541" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U541" s="46" t="n"/>
     </row>
     <row r="542" ht="60" customHeight="1">
       <c r="A542" s="7" t="inlineStr">
@@ -47419,6 +51132,12 @@
         </is>
       </c>
       <c r="S542" s="8" t="n"/>
+      <c r="T542" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U542" s="46" t="n"/>
     </row>
     <row r="543" ht="48" customHeight="1">
       <c r="A543" s="7" t="inlineStr">
@@ -47505,6 +51224,12 @@
         </is>
       </c>
       <c r="S543" s="8" t="n"/>
+      <c r="T543" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U543" s="46" t="n"/>
     </row>
     <row r="544" ht="48" customHeight="1">
       <c r="A544" s="7" t="inlineStr">
@@ -47591,6 +51316,12 @@
         </is>
       </c>
       <c r="S544" s="8" t="n"/>
+      <c r="T544" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U544" s="46" t="n"/>
     </row>
     <row r="545" ht="60" customHeight="1">
       <c r="A545" s="7" t="inlineStr">
@@ -47677,6 +51408,12 @@
         </is>
       </c>
       <c r="S545" s="8" t="n"/>
+      <c r="T545" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U545" s="46" t="n"/>
     </row>
     <row r="546" ht="60" customHeight="1">
       <c r="A546" s="7" t="inlineStr">
@@ -47763,6 +51500,12 @@
         </is>
       </c>
       <c r="S546" s="8" t="n"/>
+      <c r="T546" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U546" s="46" t="n"/>
     </row>
     <row r="547" ht="48" customHeight="1">
       <c r="A547" s="7" t="inlineStr">
@@ -47849,6 +51592,12 @@
         </is>
       </c>
       <c r="S547" s="8" t="n"/>
+      <c r="T547" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U547" s="46" t="n"/>
     </row>
     <row r="548" ht="48" customHeight="1">
       <c r="A548" s="7" t="inlineStr">
@@ -47935,6 +51684,12 @@
         </is>
       </c>
       <c r="S548" s="8" t="n"/>
+      <c r="T548" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U548" s="46" t="n"/>
     </row>
     <row r="549" ht="60" customHeight="1">
       <c r="A549" s="7" t="inlineStr">
@@ -48021,6 +51776,12 @@
         </is>
       </c>
       <c r="S549" s="8" t="n"/>
+      <c r="T549" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U549" s="46" t="n"/>
     </row>
     <row r="550" ht="60" customHeight="1">
       <c r="A550" s="7" t="inlineStr">
@@ -48107,6 +51868,12 @@
         </is>
       </c>
       <c r="S550" s="8" t="n"/>
+      <c r="T550" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U550" s="46" t="n"/>
     </row>
     <row r="551" ht="48" customHeight="1">
       <c r="A551" s="7" t="inlineStr">
@@ -48193,6 +51960,12 @@
         </is>
       </c>
       <c r="S551" s="8" t="n"/>
+      <c r="T551" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U551" s="46" t="n"/>
     </row>
     <row r="552" ht="48" customHeight="1">
       <c r="A552" s="7" t="inlineStr">
@@ -48279,6 +52052,12 @@
         </is>
       </c>
       <c r="S552" s="8" t="n"/>
+      <c r="T552" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U552" s="46" t="n"/>
     </row>
     <row r="553" ht="36" customHeight="1">
       <c r="A553" s="12" t="inlineStr">
@@ -48369,6 +52148,12 @@
           <t>Claude补提取：从PDF第18页内嵌图像逐像素检测圆点，按纵轴刻度标签换算。会话号对应不影响Tau-U，只按阶段内先后取值。核对正文：基线M=7、范围5–13（图为7.3、5–13）；干预M=31、范围16–55（图为31.1、16–55），一致。</t>
         </is>
       </c>
+      <c r="T553" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U553" s="45" t="n"/>
     </row>
     <row r="554" ht="36" customHeight="1">
       <c r="A554" s="17" t="inlineStr">
@@ -48459,6 +52244,12 @@
           <t>Claude补提取：方法同D0552。核对正文：基线M=4.8、范围1–11（图为4.8、1–11）；干预M=29.9、范围22–41（图为29.9、22–41），一致。</t>
         </is>
       </c>
+      <c r="T554" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U554" s="46" t="n"/>
     </row>
     <row r="555" ht="36" customHeight="1">
       <c r="A555" s="17" t="inlineStr">
@@ -48549,6 +52340,12 @@
           <t>Claude补提取（以图为准）：从PDF第18页内嵌图像逐像素检测Brian面板圆点，按纵轴刻度标签换算（同D0552）；基线第3、4次和第5、6次两两相邻重叠，按合并重心和形状拆分为1,2和6,5。会话号对应不影响Tau-U。图文不一致：基线9点均值3.33，正文报告3.8（范围1–8与图一致），无法定位，按图取值。干预11点均值23.6、范围6–51，与正文一致。</t>
         </is>
       </c>
+      <c r="T555" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U555" s="46" t="n"/>
     </row>
     <row r="556" ht="36" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
@@ -48635,6 +52432,12 @@
         </is>
       </c>
       <c r="S556" s="3" t="n"/>
+      <c r="T556" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U556" s="45" t="n"/>
     </row>
     <row r="557" ht="36" customHeight="1">
       <c r="A557" s="7" t="inlineStr">
@@ -48721,6 +52524,12 @@
         </is>
       </c>
       <c r="S557" s="8" t="n"/>
+      <c r="T557" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U557" s="46" t="n"/>
     </row>
     <row r="558" ht="48" customHeight="1">
       <c r="A558" s="7" t="inlineStr">
@@ -48807,6 +52616,12 @@
         </is>
       </c>
       <c r="S558" s="8" t="n"/>
+      <c r="T558" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U558" s="46" t="n"/>
     </row>
     <row r="559" ht="48" customHeight="1">
       <c r="A559" s="12" t="inlineStr">
@@ -48876,6 +52691,16 @@
           <t>待审核：研究包含训练、强化及组合干预等多个阶段，主要比较尚未确定，且图与表2的部分阶段均值、范围不一致。</t>
         </is>
       </c>
+      <c r="T559" s="45" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U559" s="45" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="560" ht="48" customHeight="1">
       <c r="A560" s="17" t="inlineStr">
@@ -48945,6 +52770,16 @@
           <t>待审核：研究包含训练、强化及组合干预等多个阶段，主要比较尚未确定，且图与表2的部分阶段均值、范围不一致。</t>
         </is>
       </c>
+      <c r="T560" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U560" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="561" ht="48" customHeight="1">
       <c r="A561" s="17" t="inlineStr">
@@ -49014,6 +52849,16 @@
           <t>待审核：研究包含训练、强化及组合干预等多个阶段，主要比较尚未确定，且图与表2的部分阶段均值、范围不一致。</t>
         </is>
       </c>
+      <c r="T561" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U561" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="48" customHeight="1">
       <c r="A562" s="17" t="inlineStr">
@@ -49083,6 +52928,16 @@
           <t>待审核：研究包含训练、强化及组合干预等多个阶段，主要比较尚未确定，且图与表2的部分阶段均值、范围不一致。</t>
         </is>
       </c>
+      <c r="T562" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U562" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="48" customHeight="1">
       <c r="A563" s="17" t="inlineStr">
@@ -49152,6 +53007,16 @@
           <t>待审核：多阶段比较尚未确定，无游戏选择的叉号不能视为零值，部分泛化点与主序列重叠，需核实配对及观测点。</t>
         </is>
       </c>
+      <c r="T563" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U563" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="564" ht="48" customHeight="1">
       <c r="A564" s="17" t="inlineStr">
@@ -49221,6 +53086,16 @@
           <t>待审核：多阶段比较尚未确定，无游戏选择的叉号不能视为零值，部分泛化点与主序列重叠，需核实配对及观测点。</t>
         </is>
       </c>
+      <c r="T564" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U564" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="48" customHeight="1">
       <c r="A565" s="17" t="inlineStr">
@@ -49290,6 +53165,16 @@
           <t>待审核：多阶段比较尚未确定，无游戏选择的叉号不能视为零值，部分泛化点与主序列重叠，需核实配对及观测点。</t>
         </is>
       </c>
+      <c r="T565" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U565" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="566" ht="48" customHeight="1">
       <c r="A566" s="17" t="inlineStr">
@@ -49359,6 +53244,16 @@
           <t>待审核：多阶段比较尚未确定，无游戏选择的叉号不能视为零值，部分泛化点与主序列重叠，需核实配对及观测点。</t>
         </is>
       </c>
+      <c r="T566" s="46" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="U566" s="46" t="inlineStr">
+        <is>
+          <t>数值空缺，待作者决定比较方式或待审核</t>
+        </is>
+      </c>
     </row>
     <row r="567" ht="36" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
@@ -49445,6 +53340,12 @@
         </is>
       </c>
       <c r="S567" s="3" t="n"/>
+      <c r="T567" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U567" s="45" t="n"/>
     </row>
     <row r="568" ht="36" customHeight="1">
       <c r="A568" s="7" t="inlineStr">
@@ -49531,6 +53432,12 @@
         </is>
       </c>
       <c r="S568" s="8" t="n"/>
+      <c r="T568" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U568" s="46" t="n"/>
     </row>
     <row r="569" ht="36" customHeight="1">
       <c r="A569" s="7" t="inlineStr">
@@ -49617,6 +53524,12 @@
         </is>
       </c>
       <c r="S569" s="8" t="n"/>
+      <c r="T569" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U569" s="46" t="n"/>
     </row>
     <row r="570" ht="36" customHeight="1">
       <c r="A570" s="7" t="inlineStr">
@@ -49703,6 +53616,12 @@
         </is>
       </c>
       <c r="S570" s="8" t="n"/>
+      <c r="T570" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U570" s="46" t="n"/>
     </row>
     <row r="571" ht="48" customHeight="1">
       <c r="A571" s="7" t="inlineStr">
@@ -49789,6 +53708,12 @@
         </is>
       </c>
       <c r="S571" s="8" t="n"/>
+      <c r="T571" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U571" s="46" t="n"/>
     </row>
     <row r="572" ht="48" customHeight="1">
       <c r="A572" s="7" t="inlineStr">
@@ -49875,6 +53800,12 @@
         </is>
       </c>
       <c r="S572" s="8" t="n"/>
+      <c r="T572" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U572" s="46" t="n"/>
     </row>
     <row r="573" ht="36" customHeight="1">
       <c r="A573" s="12" t="inlineStr">
@@ -49961,6 +53892,12 @@
         </is>
       </c>
       <c r="S573" s="13" t="n"/>
+      <c r="T573" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U573" s="45" t="n"/>
     </row>
     <row r="574" ht="48" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
@@ -50047,6 +53984,12 @@
         </is>
       </c>
       <c r="S574" s="3" t="n"/>
+      <c r="T574" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U574" s="45" t="n"/>
     </row>
     <row r="575" ht="48" customHeight="1">
       <c r="A575" s="7" t="inlineStr">
@@ -50133,6 +54076,12 @@
         </is>
       </c>
       <c r="S575" s="8" t="n"/>
+      <c r="T575" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U575" s="46" t="n"/>
     </row>
     <row r="576" ht="48" customHeight="1">
       <c r="A576" s="7" t="inlineStr">
@@ -50219,6 +54168,12 @@
         </is>
       </c>
       <c r="S576" s="8" t="n"/>
+      <c r="T576" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U576" s="46" t="n"/>
     </row>
     <row r="577" ht="48" customHeight="1">
       <c r="A577" s="7" t="inlineStr">
@@ -50305,6 +54260,12 @@
         </is>
       </c>
       <c r="S577" s="8" t="n"/>
+      <c r="T577" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U577" s="46" t="n"/>
     </row>
     <row r="578" ht="48" customHeight="1">
       <c r="A578" s="7" t="inlineStr">
@@ -50391,6 +54352,12 @@
         </is>
       </c>
       <c r="S578" s="8" t="n"/>
+      <c r="T578" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U578" s="46" t="n"/>
     </row>
     <row r="579" ht="48" customHeight="1">
       <c r="A579" s="7" t="inlineStr">
@@ -50477,6 +54444,12 @@
         </is>
       </c>
       <c r="S579" s="8" t="n"/>
+      <c r="T579" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U579" s="46" t="n"/>
     </row>
     <row r="580" ht="48" customHeight="1">
       <c r="A580" s="7" t="inlineStr">
@@ -50563,6 +54536,12 @@
         </is>
       </c>
       <c r="S580" s="8" t="n"/>
+      <c r="T580" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U580" s="46" t="n"/>
     </row>
     <row r="581" ht="48" customHeight="1">
       <c r="A581" s="7" t="inlineStr">
@@ -50649,6 +54628,12 @@
         </is>
       </c>
       <c r="S581" s="8" t="n"/>
+      <c r="T581" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U581" s="46" t="n"/>
     </row>
     <row r="582" ht="48" customHeight="1">
       <c r="A582" s="7" t="inlineStr">
@@ -50735,6 +54720,12 @@
         </is>
       </c>
       <c r="S582" s="8" t="n"/>
+      <c r="T582" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U582" s="46" t="n"/>
     </row>
     <row r="583" ht="48" customHeight="1">
       <c r="A583" s="7" t="inlineStr">
@@ -50821,6 +54812,12 @@
         </is>
       </c>
       <c r="S583" s="8" t="n"/>
+      <c r="T583" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U583" s="46" t="n"/>
     </row>
     <row r="584" ht="48" customHeight="1">
       <c r="A584" s="7" t="inlineStr">
@@ -50907,6 +54904,12 @@
         </is>
       </c>
       <c r="S584" s="8" t="n"/>
+      <c r="T584" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U584" s="46" t="n"/>
     </row>
     <row r="585" ht="48" customHeight="1">
       <c r="A585" s="7" t="inlineStr">
@@ -50993,6 +54996,12 @@
         </is>
       </c>
       <c r="S585" s="8" t="n"/>
+      <c r="T585" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U585" s="46" t="n"/>
     </row>
     <row r="586" ht="48" customHeight="1">
       <c r="A586" s="7" t="inlineStr">
@@ -51079,6 +55088,12 @@
         </is>
       </c>
       <c r="S586" s="8" t="n"/>
+      <c r="T586" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U586" s="46" t="n"/>
     </row>
     <row r="587" ht="48" customHeight="1">
       <c r="A587" s="7" t="inlineStr">
@@ -51165,6 +55180,12 @@
         </is>
       </c>
       <c r="S587" s="8" t="n"/>
+      <c r="T587" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U587" s="46" t="n"/>
     </row>
     <row r="588" ht="36" customHeight="1">
       <c r="A588" s="12" t="inlineStr">
@@ -51251,6 +55272,12 @@
         </is>
       </c>
       <c r="S588" s="13" t="n"/>
+      <c r="T588" s="45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U588" s="45" t="n"/>
     </row>
     <row r="589" ht="36" customHeight="1">
       <c r="A589" s="17" t="inlineStr">
@@ -51337,6 +55364,12 @@
         </is>
       </c>
       <c r="S589" s="18" t="n"/>
+      <c r="T589" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U589" s="46" t="n"/>
     </row>
     <row r="590" ht="36" customHeight="1">
       <c r="A590" s="17" t="inlineStr">
@@ -51423,6 +55456,12 @@
         </is>
       </c>
       <c r="S590" s="18" t="n"/>
+      <c r="T590" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U590" s="46" t="n"/>
     </row>
     <row r="591" ht="36" customHeight="1">
       <c r="A591" s="17" t="inlineStr">
@@ -51509,6 +55548,12 @@
         </is>
       </c>
       <c r="S591" s="18" t="n"/>
+      <c r="T591" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U591" s="46" t="n"/>
     </row>
     <row r="592" ht="36" customHeight="1">
       <c r="A592" s="17" t="inlineStr">
@@ -51595,6 +55640,12 @@
         </is>
       </c>
       <c r="S592" s="18" t="n"/>
+      <c r="T592" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U592" s="46" t="n"/>
     </row>
     <row r="593" ht="36" customHeight="1">
       <c r="A593" s="17" t="inlineStr">
@@ -51681,6 +55732,12 @@
         </is>
       </c>
       <c r="S593" s="18" t="n"/>
+      <c r="T593" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U593" s="46" t="n"/>
     </row>
     <row r="594" ht="36" customHeight="1">
       <c r="A594" s="17" t="inlineStr">
@@ -51767,6 +55824,12 @@
         </is>
       </c>
       <c r="S594" s="18" t="n"/>
+      <c r="T594" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U594" s="46" t="n"/>
     </row>
     <row r="595" ht="36" customHeight="1">
       <c r="A595" s="17" t="inlineStr">
@@ -51853,6 +55916,12 @@
         </is>
       </c>
       <c r="S595" s="18" t="n"/>
+      <c r="T595" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U595" s="46" t="n"/>
     </row>
     <row r="596" ht="36" customHeight="1">
       <c r="A596" s="17" t="inlineStr">
@@ -51943,6 +56012,12 @@
           <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。干预期图上16点，合计221，221÷16=13.81，与正文均值13.81完全一致，说明作者也按16点计算；正文“小翰缺席2次”与数据点数的矛盾属叙述问题，按图取16点。</t>
         </is>
       </c>
+      <c r="T596" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U596" s="46" t="n"/>
     </row>
     <row r="597" ht="36" customHeight="1">
       <c r="A597" s="17" t="inlineStr">
@@ -52033,6 +56108,12 @@
           <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。图文不一致：维持期图上5点均值16.4，正文报告18.4，无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
+      <c r="T597" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U597" s="46" t="n"/>
     </row>
     <row r="598" ht="36" customHeight="1">
       <c r="A598" s="17" t="inlineStr">
@@ -52123,6 +56204,12 @@
           <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。干预期图上16点，合计717，717÷16=44.81，与正文均值44.81完全一致；正文“缺席2次”与点数的矛盾同D0595，按图取16点。</t>
         </is>
       </c>
+      <c r="T598" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U598" s="46" t="n"/>
     </row>
     <row r="599" ht="36" customHeight="1">
       <c r="A599" s="17" t="inlineStr">
@@ -52213,6 +56300,12 @@
           <t>Claude补提取（以图为准）：从PDF第5页内嵌原图（2362×3668像素）逐像素检测圆点（发起）和方块（回应），按纵轴刻度（每单位约11.9像素）换算。基线7点：发起0,1,0,2,1,0,1（均值0.71），回应2,2,1,1,2,1,1（均值1.43），均落在正文报告的基线均值范围内（发起0.67–1，回应1.33–1.60）；基线两条线多处重叠，第7次两个符号重合于1，依据正文均值范围确定。图文不一致：维持期图上5点均值37.4，正文报告38，无法定位具体哪个点，按图取值。</t>
         </is>
       </c>
+      <c r="T599" s="46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="U599" s="46" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52229,7 +56322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52436,6 +56529,46 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>纳入计算规则（作者决定，规则B）</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>前段（基线或对照段）必须不少于3点；干预比较的后段也必须不少于3点；维持、泛化比较的后段允许1–2点。不满足的行在“是否纳入计算”列标“否”，原因写在“不纳入或待定原因”列。数值保留不删。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>其他剔除</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>017-A整篇剔除（作者决定）。025-A的15行单次前后测剔除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>数值空缺的行（022-A平行游戏、03 Blair、24 Morrison、17 Kern的3行）标“待定”。022-A独自游戏、030-A前段趋势检验、多效应量合并方式、A-B-A-B计算方式等仍待作者决定，暂未体现在本列。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
